--- a/web/exports/revision-prix.xlsx
+++ b/web/exports/revision-prix.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I27" s="6" t="n"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I61" s="6" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I64" s="6" t="n"/>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I65" s="6" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I68" s="6" t="n"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I69" s="6" t="n"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I70" s="6" t="n"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I84" s="6" t="n"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I85" s="6" t="n"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I86" s="6" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I87" s="6" t="n"/>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I89" s="6" t="n"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I115" s="6" t="n"/>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I121" s="6" t="n"/>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I158" s="6" t="n"/>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I173" s="6" t="n"/>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I174" s="6" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I175" s="6" t="n"/>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H188" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I188" s="6" t="n"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I189" s="6" t="n"/>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="H192" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I192" s="6" t="n"/>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I193" s="6" t="n"/>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H198" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I198" s="6" t="n"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I199" s="6" t="n"/>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H200" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I200" s="6" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="H202" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I202" s="6" t="n"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I203" s="6" t="n"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="H218" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I218" s="6" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I235" s="6" t="n"/>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="H238" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I238" s="6" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I239" s="6" t="n"/>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I245" s="6" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I281" s="6" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="H282" s="15" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I282" s="6" t="n"/>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="H283" s="9" t="inlineStr">
         <is>
-          <t>Liste IFDC 2026</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I283" s="6" t="n"/>
@@ -11233,7 +11233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Source du prix — « Liste IFDC 2026 » si le prix vient du fichier de prix fourni,</t>
+          <t>Source du prix — « Liste supplier 2026 » si le prix vient du fichier de prix fourni,</t>
         </is>
       </c>
     </row>

--- a/web/exports/revision-prix.xlsx
+++ b/web/exports/revision-prix.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K284"/>
+  <dimension ref="A1:K293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -561,14 +561,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>IF-8012</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige — Canapé</t>
+          <t>Zénith — Canapé</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,7 +573,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>229.99</v>
+        <v>200</v>
       </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="4" t="n"/>
@@ -592,7 +588,7 @@
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>0.17× la médiane de « Canapés » (1 370 $)</t>
+          <t>0.11× la médiane de « Canapés » (1 770 $) ; moins cher que le causeuse du même ensemble (1 500 $)</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
@@ -602,254 +598,218 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Zénith — Canapé</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Canapés</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr"/>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Teddy Bear Blanc — Banc</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Bancs</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I3" s="6" t="n"/>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>0.15× la médiane de « Canapés » (1 370 $) ; moins cher que le causeuse du même ensemble (1 500 $)</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Canapé Christophe — velours noir — Causeuse</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Causeuses</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+      <c r="A4" s="15" t="inlineStr"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Bureau Outremont — métal noir</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Bureaux</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I4" s="6" t="n"/>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>0.23× la médiane de « Causeuses » (1 500 $)</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr"/>
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>IF-8012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Canapé Chabanel — cuir beige — Causeuse</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Causeuses</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>229.99</v>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Bureau - 70"</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Bureaux</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>510</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>510</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>0.15× la médiane de « Causeuses » (1 500 $)</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>IF-1056</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ensemble salle à manger 5 pièces</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Ensembles de salle à manger</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-0.4286</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Liste du fournisseur</t>
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Bureau — Gris</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Bureaux</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>0.21× la médiane de « Ensembles de salle à manger » (950 $)</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IF-174</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Lit Everett — blanc</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Lits</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>-0.44004</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Liste du fournisseur</t>
+      <c r="A7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Bureau — Gris (2)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Bureaux</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>0.24× la médiane de « Lits » (587 $)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>IF-175</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Lit Dante — noir</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Lits</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>129.99</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>-0.4091363636363636</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Liste du fournisseur</t>
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Bureau De Coin Cote Droit Ou Gauche</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bureaux</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>449</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>449</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>0.22× la médiane de « Lits » (587 $)</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -859,25 +819,29 @@
       <c r="A9" s="9" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Banc</t>
+          <t>Bureau Christophe — bois gris</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Bancs</t>
+          <t>Bureaux</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>360</v>
-      </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="11" t="n"/>
+        <v>390</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>390</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -892,7 +856,7 @@
       <c r="A10" s="15" t="inlineStr"/>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Bureau Outremont — métal noir</t>
+          <t>Bureau - 42" L</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -901,16 +865,16 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
@@ -929,29 +893,25 @@
       <c r="A11" s="9" t="inlineStr"/>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Bureau - 70"</t>
+          <t>ATlas — Canapé</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>510</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>510</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>2140</v>
+      </c>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
       <c r="G11" s="12" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -966,29 +926,25 @@
       <c r="A12" s="15" t="inlineStr"/>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Bureau — Gris</t>
+          <t>Nexus — Canapé</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>480</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>480</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17" t="n"/>
       <c r="G12" s="18" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -1000,32 +956,36 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>IF-8030</t>
+        </is>
+      </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Bureau — Gris (2)</t>
+          <t>(Fabric-Power)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>480</v>
+        <v>1999.98</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0</v>
+        <v>0.99998</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -1040,29 +1000,25 @@
       <c r="A14" s="15" t="inlineStr"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Bureau De Coin Cote Droit Ou Gauche</t>
+          <t>Elite — Canapé</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>449</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>449</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17" t="n"/>
       <c r="G14" s="18" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -1077,29 +1033,25 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Bureau Christophe — bois gris</t>
+          <t>Royal — Canapé</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>390</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>390</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="12" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
@@ -1114,29 +1066,25 @@
       <c r="A16" s="15" t="inlineStr"/>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Bureau - 42" L</t>
+          <t>Véga — Canapé</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Bureaux</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="17" t="n"/>
       <c r="G16" s="18" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
@@ -1151,7 +1099,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>ATlas — Canapé</t>
+          <t>Opéra — Canapé</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1160,12 +1108,12 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2140</v>
+        <v>1800</v>
       </c>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
@@ -1184,7 +1132,7 @@
       <c r="A18" s="15" t="inlineStr"/>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Nexus — Canapé</t>
+          <t>Skyline — Canapé</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -1193,12 +1141,12 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E18" s="16" t="n"/>
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="18" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
@@ -1217,7 +1165,7 @@
       <c r="A19" s="9" t="inlineStr"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Elite — Canapé</t>
+          <t>Sérénity — Canapé</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1250,7 +1198,7 @@
       <c r="A20" s="15" t="inlineStr"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Royal — Canapé</t>
+          <t>Nuvola — Canapé</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -1283,7 +1231,7 @@
       <c r="A21" s="9" t="inlineStr"/>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Véga — Canapé</t>
+          <t>Volta — Canapé</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1292,12 +1240,12 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1800</v>
+        <v>1740</v>
       </c>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -1316,7 +1264,7 @@
       <c r="A22" s="15" t="inlineStr"/>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Opéra — Canapé</t>
+          <t>Nexo — Canapé</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -1325,12 +1273,12 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1800</v>
+        <v>980</v>
       </c>
       <c r="E22" s="16" t="n"/>
       <c r="F22" s="17" t="n"/>
       <c r="G22" s="18" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
@@ -1349,7 +1297,7 @@
       <c r="A23" s="9" t="inlineStr"/>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Skyline — Canapé</t>
+          <t>Milo — Canapé</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1358,12 +1306,12 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1800</v>
+        <v>980</v>
       </c>
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -1379,10 +1327,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr"/>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>IF 8120</t>
+        </is>
+      </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Sérénity — Canapé</t>
+          <t>Canapé Casgrain — cuir noir — Canapé</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -1391,12 +1343,12 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E24" s="16" t="n"/>
       <c r="F24" s="17" t="n"/>
       <c r="G24" s="18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
@@ -1415,7 +1367,7 @@
       <c r="A25" s="9" t="inlineStr"/>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Nuvola — Canapé</t>
+          <t>Hudson — Canapé</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1424,12 +1376,12 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1800</v>
+        <v>860</v>
       </c>
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="12" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -1448,7 +1400,7 @@
       <c r="A26" s="15" t="inlineStr"/>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Volta — Canapé</t>
+          <t>Depot — Canapé</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -1457,12 +1409,12 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1740</v>
+        <v>860</v>
       </c>
       <c r="E26" s="16" t="n"/>
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="18" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
@@ -1478,14 +1430,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>IF-8030</t>
-        </is>
-      </c>
+      <c r="A27" s="9" t="inlineStr"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>(Fabric-Power)</t>
+          <t>Clarence — Canapé</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1494,20 +1442,16 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>-9.999999999990905e-06</v>
-      </c>
+        <v>840</v>
+      </c>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="11" t="n"/>
       <c r="G27" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I27" s="6" t="n"/>
@@ -1519,10 +1463,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr"/>
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Nexo — Canapé</t>
+          <t>Canapé Christophe — velours noir — Canapé</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -1531,12 +1479,12 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>980</v>
+        <v>700</v>
       </c>
       <c r="E28" s="16" t="n"/>
       <c r="F28" s="17" t="n"/>
       <c r="G28" s="18" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
@@ -1552,10 +1500,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr"/>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>IF-8012</t>
+        </is>
+      </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Milo — Canapé</t>
+          <t>Canapé Chabanel — cuir beige — Canapé</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1564,12 +1516,12 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>980</v>
+        <v>459.98</v>
       </c>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="11" t="n"/>
       <c r="G29" s="12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
@@ -1588,21 +1540,21 @@
       <c r="A30" s="15" t="inlineStr"/>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Hudson — Canapé</t>
+          <t>Prestige — Causeuse</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>860</v>
+        <v>2000</v>
       </c>
       <c r="E30" s="16" t="n"/>
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="18" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
@@ -1621,21 +1573,21 @@
       <c r="A31" s="9" t="inlineStr"/>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Depot — Canapé</t>
+          <t>Elite — Causeuse</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>860</v>
+        <v>1700</v>
       </c>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="12" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
@@ -1654,21 +1606,21 @@
       <c r="A32" s="15" t="inlineStr"/>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Clarence — Canapé</t>
+          <t>Royal — Causeuse</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>840</v>
+        <v>1700</v>
       </c>
       <c r="E32" s="16" t="n"/>
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="18" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
@@ -1684,28 +1636,24 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A33" s="9" t="inlineStr"/>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir — Canapé</t>
+          <t>Véga — Causeuse</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>450</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="12" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -1721,28 +1669,24 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A34" s="15" t="inlineStr"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Canapé</t>
+          <t>Opéra — Causeuse</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>350</v>
+        <v>1700</v>
       </c>
       <c r="E34" s="16" t="n"/>
       <c r="F34" s="17" t="n"/>
       <c r="G34" s="18" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
@@ -1761,7 +1705,7 @@
       <c r="A35" s="9" t="inlineStr"/>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Prestige — Causeuse</t>
+          <t>Sérénity — Causeuse</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -1770,12 +1714,12 @@
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="12" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -1794,7 +1738,7 @@
       <c r="A36" s="15" t="inlineStr"/>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Elite — Causeuse</t>
+          <t>Nuvola — Causeuse</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -1827,7 +1771,7 @@
       <c r="A37" s="9" t="inlineStr"/>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Royal — Causeuse</t>
+          <t>ATlas — Causeuse</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -1836,12 +1780,12 @@
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1700</v>
+        <v>1560</v>
       </c>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="11" t="n"/>
       <c r="G37" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -1860,7 +1804,7 @@
       <c r="A38" s="15" t="inlineStr"/>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Véga — Causeuse</t>
+          <t>Nexus — Causeuse</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -1869,12 +1813,12 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="E38" s="16" t="n"/>
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
@@ -1893,7 +1837,7 @@
       <c r="A39" s="9" t="inlineStr"/>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Opéra — Causeuse</t>
+          <t>Skyline — Causeuse</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -1902,12 +1846,12 @@
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="11" t="n"/>
       <c r="G39" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -1926,7 +1870,7 @@
       <c r="A40" s="15" t="inlineStr"/>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Sérénity — Causeuse</t>
+          <t>Zénith — Causeuse</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -1935,12 +1879,12 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="E40" s="16" t="n"/>
       <c r="F40" s="17" t="n"/>
       <c r="G40" s="18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
@@ -1959,7 +1903,7 @@
       <c r="A41" s="9" t="inlineStr"/>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Nuvola — Causeuse</t>
+          <t>Volta — Causeuse</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1968,12 +1912,12 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="12" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -1992,7 +1936,7 @@
       <c r="A42" s="15" t="inlineStr"/>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>ATlas — Causeuse</t>
+          <t>Nexo — Causeuse</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -2001,12 +1945,12 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>1560</v>
+        <v>760</v>
       </c>
       <c r="E42" s="16" t="n"/>
       <c r="F42" s="17" t="n"/>
       <c r="G42" s="18" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
@@ -2025,7 +1969,7 @@
       <c r="A43" s="9" t="inlineStr"/>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Nexus — Causeuse</t>
+          <t>Milo — Causeuse</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -2034,12 +1978,12 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1500</v>
+        <v>760</v>
       </c>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="11" t="n"/>
       <c r="G43" s="12" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -2055,10 +1999,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr"/>
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Skyline — Causeuse</t>
+          <t>Canapé Christophe — velours noir — Causeuse</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -2067,12 +2015,12 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="E44" s="16" t="n"/>
       <c r="F44" s="17" t="n"/>
       <c r="G44" s="18" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
@@ -2091,7 +2039,7 @@
       <c r="A45" s="9" t="inlineStr"/>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Zénith — Causeuse</t>
+          <t>Hudson — Causeuse</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -2100,12 +2048,12 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1500</v>
+        <v>660</v>
       </c>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="12" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -2124,7 +2072,7 @@
       <c r="A46" s="15" t="inlineStr"/>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Volta — Causeuse</t>
+          <t>Clarence — Causeuse</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -2133,12 +2081,12 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>1400</v>
+        <v>660</v>
       </c>
       <c r="E46" s="16" t="n"/>
       <c r="F46" s="17" t="n"/>
       <c r="G46" s="18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
@@ -2157,7 +2105,7 @@
       <c r="A47" s="9" t="inlineStr"/>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Nexo — Causeuse</t>
+          <t>Depot — Causeuse</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -2166,12 +2114,12 @@
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>760</v>
+        <v>660</v>
       </c>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
@@ -2187,10 +2135,14 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr"/>
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>IF-8012</t>
+        </is>
+      </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Milo — Causeuse</t>
+          <t>Canapé Chabanel — cuir beige — Causeuse</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -2199,12 +2151,12 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>760</v>
+        <v>459.98</v>
       </c>
       <c r="E48" s="16" t="n"/>
       <c r="F48" s="17" t="n"/>
       <c r="G48" s="18" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
@@ -2223,21 +2175,21 @@
       <c r="A49" s="9" t="inlineStr"/>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Hudson — Causeuse</t>
+          <t>Nexo — Chaise</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
       <c r="E49" s="10" t="n"/>
       <c r="F49" s="11" t="n"/>
       <c r="G49" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
@@ -2253,28 +2205,36 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr"/>
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>C-1285</t>
+        </is>
+      </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Clarence — Causeuse</t>
+          <t>Chaise Casgrain — velours beige</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>660</v>
-      </c>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="17" t="n"/>
+        <v>350</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" s="18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I50" s="6" t="n"/>
@@ -2286,28 +2246,36 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr"/>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>C-1453</t>
+        </is>
+      </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Depot — Causeuse</t>
+          <t>Chaise en velours crème — Beige (2)</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>660</v>
-      </c>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="11" t="n"/>
+        <v>300</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>0.1538461538461539</v>
+      </c>
       <c r="G51" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I51" s="6" t="n"/>
@@ -2321,12 +2289,12 @@
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>T-1275</t>
+          <t>C-1263</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Gaspé — velours beige — Chaise</t>
+          <t>Chaise cadre chrome poli</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -2335,16 +2303,20 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>659.99</v>
-      </c>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="17" t="n"/>
+        <v>290</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G52" s="18" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I52" s="6" t="n"/>
@@ -2358,12 +2330,12 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>T-1275</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Casgrain — velours gris — Chaise</t>
+          <t>Gaspé — velours beige — Chaise</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -2372,12 +2344,12 @@
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>599.99</v>
+        <v>290</v>
       </c>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="11" t="n"/>
       <c r="G53" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
@@ -2400,7 +2372,7 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Waverly — velours gris — Chaise</t>
+          <t>Casgrain — velours gris — Chaise</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -2409,12 +2381,12 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>599.99</v>
+        <v>290</v>
       </c>
       <c r="E54" s="16" t="n"/>
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="18" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
@@ -2430,10 +2402,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr"/>
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>T-1274</t>
+        </is>
+      </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Nexo — Chaise</t>
+          <t>Waverly — velours gris — Chaise</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -2442,12 +2418,12 @@
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>460</v>
+        <v>290</v>
       </c>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="11" t="n"/>
       <c r="G55" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
@@ -2463,14 +2439,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>T-1415</t>
-        </is>
-      </c>
+      <c r="A56" s="15" t="inlineStr"/>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris — Chaise</t>
+          <t>Monaco Dining Set — Chaise</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
@@ -2479,12 +2451,12 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>449.99</v>
+        <v>270</v>
       </c>
       <c r="E56" s="16" t="n"/>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
@@ -2500,14 +2472,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>T-1402</t>
-        </is>
-      </c>
+      <c r="A57" s="9" t="inlineStr"/>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris — Chaise</t>
+          <t>Chaise en pattes chromées</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -2516,16 +2484,20 @@
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>299.99</v>
-      </c>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="11" t="n"/>
+        <v>260</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G57" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I57" s="6" t="n"/>
@@ -2540,7 +2512,7 @@
       <c r="A58" s="15" t="inlineStr"/>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Monaco Dining Set — Chaise</t>
+          <t>Chaise avec pattes chromées</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -2549,16 +2521,20 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>270</v>
-      </c>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="17" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>220</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G58" s="18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I58" s="6" t="n"/>
@@ -2570,10 +2546,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr"/>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>T-1402</t>
+        </is>
+      </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Chaise en pattes chromées</t>
+          <t>Chaise Christophe — métal gris — Chaise</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -2582,20 +2562,16 @@
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="11" t="n"/>
       <c r="G59" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I59" s="6" t="n"/>
@@ -2607,10 +2583,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr"/>
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>C-1546</t>
+        </is>
+      </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Chaise avec pattes chromées</t>
+          <t>Chaise moderne</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -2619,20 +2599,20 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E60" s="16" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F60" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I60" s="6" t="n"/>
@@ -2646,12 +2626,12 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>C-1285</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Chaise Casgrain — velours beige</t>
+          <t>Meuble Iberville — métal noir — Chaise</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -2660,20 +2640,16 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>175</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="11" t="n"/>
       <c r="G61" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I61" s="6" t="n"/>
@@ -2761,12 +2737,12 @@
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>C-1453</t>
+          <t>C-1416</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Chaise en velours crème — Beige (2)</t>
+          <t>Chaise moderne en PU</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
@@ -2778,10 +2754,10 @@
         <v>150</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="F64" s="17" t="n">
-        <v>-0.4230769230769231</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>4</v>
@@ -2802,12 +2778,12 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>C-1263</t>
+          <t>T-1415</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Chaise cadre chrome poli</t>
+          <t>Meuble Boyer — métal gris — Chaise</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -2816,20 +2792,16 @@
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>145</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>290</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="11" t="n"/>
       <c r="G65" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I65" s="6" t="n"/>
@@ -2843,12 +2815,12 @@
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>T-1079 / C-1084</t>
+          <t>C-1541</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Gaspé — tissu gris — Chaise</t>
+          <t>Chaise moderne en PU gris</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -2857,16 +2829,20 @@
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="17" t="n"/>
+        <v>145</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="F66" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G66" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I66" s="6" t="n"/>
@@ -2880,12 +2856,12 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Marquette — verre blanc — Chaise</t>
+          <t>Meuble Beaubien — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -2894,12 +2870,12 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="E67" s="10" t="n"/>
       <c r="F67" s="11" t="n"/>
       <c r="G67" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -2917,12 +2893,12 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>C-1546</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Chaise moderne</t>
+          <t>Meuble Papineau — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -2931,20 +2907,16 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="F68" s="17" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="17" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I68" s="6" t="n"/>
@@ -2958,12 +2930,12 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>C-1416</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Chaise moderne en PU</t>
+          <t>Meuble Fabre — velours beige — Chaise</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -2972,20 +2944,16 @@
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>140</v>
-      </c>
-      <c r="F69" s="11" t="n">
-        <v>-0.4642857142857143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="11" t="n"/>
       <c r="G69" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I69" s="6" t="n"/>
@@ -2999,12 +2967,12 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>C-1541</t>
+          <t>T-1540</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Chaise moderne en PU gris</t>
+          <t>Meuble Chabanel — métal gris — Chaise</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -3013,20 +2981,16 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="E70" s="16" t="n">
         <v>145</v>
       </c>
-      <c r="F70" s="17" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="17" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I70" s="6" t="n"/>
@@ -3040,12 +3004,12 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>T-1449 &amp; C-1712</t>
+          <t>T-1079 / C-1084</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Saint-Urbain — bois gris — Chaise</t>
+          <t>Gaspé — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -3054,12 +3018,12 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
@@ -3075,32 +3039,32 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr"/>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>T-1442 / C-1878</t>
+        </is>
+      </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>New York D/M – Commode avec miroir</t>
+          <t>Marquette — verre blanc — Chaise</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>1660</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>1660</v>
-      </c>
-      <c r="F72" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="17" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I72" s="6" t="n"/>
@@ -3112,24 +3076,28 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr"/>
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>T-1449 &amp; C-1712</t>
+        </is>
+      </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Commode</t>
+          <t>Saint-Urbain — bois gris — Chaise</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="12" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
@@ -3148,7 +3116,7 @@
       <c r="A74" s="15" t="inlineStr"/>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Commode</t>
+          <t>New York D/M – Commode avec miroir</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -3157,16 +3125,20 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="E74" s="16" t="n"/>
-      <c r="F74" s="17" t="n"/>
+        <v>1660</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>1660</v>
+      </c>
+      <c r="F74" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G74" s="18" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I74" s="6" t="n"/>
@@ -3181,7 +3153,7 @@
       <c r="A75" s="9" t="inlineStr"/>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Commode</t>
+          <t>Harper "Seville" — Commode</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -3190,12 +3162,12 @@
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>720</v>
+        <v>1030</v>
       </c>
       <c r="E75" s="10" t="n"/>
       <c r="F75" s="11" t="n"/>
       <c r="G75" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
@@ -3214,7 +3186,7 @@
       <c r="A76" s="15" t="inlineStr"/>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Commode</t>
+          <t>Chambre Moderne Blanche — Commode</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -3223,12 +3195,12 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>720</v>
+        <v>800</v>
       </c>
       <c r="E76" s="16" t="n"/>
       <c r="F76" s="17" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
@@ -3247,7 +3219,7 @@
       <c r="A77" s="9" t="inlineStr"/>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Amelia-Black — Commode</t>
+          <t>Ava Jordyn – Gris — Commode</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -3256,12 +3228,12 @@
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="11" t="n"/>
       <c r="G77" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
@@ -3280,7 +3252,7 @@
       <c r="A78" s="15" t="inlineStr"/>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Madisson 100 — Commode</t>
+          <t>Jordyn – Blanc — Commode</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -3289,12 +3261,12 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="E78" s="16" t="n"/>
       <c r="F78" s="17" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
@@ -3313,7 +3285,7 @@
       <c r="A79" s="9" t="inlineStr"/>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Dylan — Commode</t>
+          <t>Amelia-Black — Commode</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -3322,12 +3294,12 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -3346,7 +3318,7 @@
       <c r="A80" s="15" t="inlineStr"/>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Commode</t>
+          <t>Madisson 100 — Commode</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -3355,12 +3327,12 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="E80" s="16" t="n"/>
       <c r="F80" s="17" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
@@ -3379,7 +3351,7 @@
       <c r="A81" s="9" t="inlineStr"/>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Commode</t>
+          <t>Dylan — Commode</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -3388,12 +3360,12 @@
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="E81" s="10" t="n"/>
       <c r="F81" s="11" t="n"/>
       <c r="G81" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -3412,7 +3384,7 @@
       <c r="A82" s="15" t="inlineStr"/>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Commode</t>
+          <t>Pompéi – Gris métallisé — Commode</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -3421,12 +3393,12 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="E82" s="16" t="n"/>
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
@@ -3445,7 +3417,7 @@
       <c r="A83" s="9" t="inlineStr"/>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Olivia “Austin — Commode</t>
+          <t>Lucia — Blanc — Commode</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -3454,12 +3426,12 @@
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="11" t="n"/>
       <c r="G83" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
@@ -3475,36 +3447,28 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>T-1540</t>
-        </is>
-      </c>
+      <c r="A84" s="15" t="inlineStr"/>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Meuble Chabanel — métal gris</t>
+          <t>Luna Riley – Finition argentée — Commode</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>1149.99</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="F84" s="17" t="n">
-        <v>6.930965517241379</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="17" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I84" s="6" t="n"/>
@@ -3516,36 +3480,28 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>T-1545</t>
-        </is>
-      </c>
+      <c r="A85" s="9" t="inlineStr"/>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Meuble Iberville — métal noir</t>
+          <t>Olivia “Austin — Commode</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>939.99</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="F85" s="11" t="n">
-        <v>4.222166666666666</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="11" t="n"/>
       <c r="G85" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I85" s="6" t="n"/>
@@ -3559,12 +3515,12 @@
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1442</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Meuble Beaubien — tissu gris</t>
+          <t>Meuble Cartier — verre gris</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -3573,16 +3529,16 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>649.99</v>
+        <v>999.98</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>145</v>
+        <v>1000</v>
       </c>
       <c r="F86" s="17" t="n">
-        <v>3.482689655172414</v>
+        <v>-1.999999999998181e-05</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
@@ -3598,14 +3554,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>T-1510</t>
-        </is>
-      </c>
+      <c r="A87" s="9" t="inlineStr"/>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Meuble Papineau — tissu gris</t>
+          <t>Vase décoratif circulaire noir – Design moderne</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -3614,20 +3566,20 @@
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>649.99</v>
+        <v>45.99</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>145</v>
+        <v>45.99</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3.482689655172414</v>
+        <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I87" s="6" t="n"/>
@@ -3639,36 +3591,32 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>T-1510</t>
-        </is>
-      </c>
+      <c r="A88" s="15" t="inlineStr"/>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Meuble Fabre — velours beige</t>
+          <t>Chambre Moderne Blanche</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>649.99</v>
+        <v>5000</v>
       </c>
       <c r="E88" s="16" t="n">
-        <v>145</v>
+        <v>370</v>
       </c>
       <c r="F88" s="17" t="n">
-        <v>3.482689655172414</v>
+        <v>12.51351351351351</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
@@ -3680,36 +3628,32 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>T-1442</t>
-        </is>
-      </c>
+      <c r="A89" s="9" t="inlineStr"/>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Meuble Cartier — verre gris</t>
+          <t>Ava Jordyn – Gris</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>499.99</v>
+        <v>4200</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>-0.50001</v>
+        <v>11</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I89" s="6" t="n"/>
@@ -3724,7 +3668,7 @@
       <c r="A90" s="15" t="inlineStr"/>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche</t>
+          <t>Jordyn – Blanc</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -3733,16 +3677,16 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="F90" s="17" t="n">
-        <v>12.51351351351351</v>
+        <v>11</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
@@ -3761,7 +3705,7 @@
       <c r="A91" s="9" t="inlineStr"/>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris</t>
+          <t>Logan – Silver</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -3770,16 +3714,16 @@
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>4200</v>
+        <v>3200</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>11</v>
+        <v>2.636363636363636</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
@@ -3798,7 +3742,7 @@
       <c r="A92" s="15" t="inlineStr"/>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc</t>
+          <t>Amelia-Black</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -3807,16 +3751,16 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>4200</v>
+        <v>3000</v>
       </c>
       <c r="E92" s="16" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="F92" s="17" t="n">
-        <v>11</v>
+        <v>7.108108108108108</v>
       </c>
       <c r="G92" s="18" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
@@ -3835,7 +3779,7 @@
       <c r="A93" s="9" t="inlineStr"/>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Logan – Silver</t>
+          <t>Pompéi – Gris métallisé</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -3844,16 +3788,16 @@
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>880</v>
+        <v>240</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2.636363636363636</v>
+        <v>9.416666666666666</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
@@ -3872,7 +3816,7 @@
       <c r="A94" s="15" t="inlineStr"/>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Amelia-Black</t>
+          <t>Madisson 100</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -3881,16 +3825,16 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>3000</v>
+        <v>2299.98</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>370</v>
+        <v>220</v>
       </c>
       <c r="F94" s="17" t="n">
-        <v>7.108108108108108</v>
+        <v>9.454454545454546</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
@@ -3909,7 +3853,7 @@
       <c r="A95" s="9" t="inlineStr"/>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -3918,16 +3862,16 @@
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>9.416666666666666</v>
+        <v>9.476190476190476</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
@@ -3946,7 +3890,7 @@
       <c r="A96" s="15" t="inlineStr"/>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Madisson 100</t>
+          <t>Harper "Seville"</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -3955,16 +3899,16 @@
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>2299.98</v>
+        <v>2015</v>
       </c>
       <c r="E96" s="16" t="n">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="F96" s="17" t="n">
-        <v>9.454454545454546</v>
+        <v>6.070175438596491</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
@@ -3983,7 +3927,7 @@
       <c r="A97" s="9" t="inlineStr"/>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Luna Riley – Finition argentée</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -3992,16 +3936,16 @@
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>2200</v>
+        <v>1999</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>9.476190476190476</v>
+        <v>8.086363636363636</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
@@ -4020,7 +3964,7 @@
       <c r="A98" s="15" t="inlineStr"/>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Harper "Seville"</t>
+          <t>Olivia “Austin</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -4029,16 +3973,16 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>2015</v>
+        <v>1920</v>
       </c>
       <c r="E98" s="16" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="F98" s="17" t="n">
-        <v>6.070175438596491</v>
+        <v>8.142857142857142</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
@@ -4057,7 +4001,7 @@
       <c r="A99" s="9" t="inlineStr"/>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée</t>
+          <t>Lit Queen / Chene Rustique / Tiroir</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -4066,16 +4010,16 @@
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1999</v>
+        <v>1828</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>220</v>
+        <v>1828</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>8.086363636363636</v>
+        <v>0</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -4094,7 +4038,7 @@
       <c r="A100" s="15" t="inlineStr"/>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Olivia “Austin</t>
+          <t>Lit Queen avec Rangement</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -4103,16 +4047,16 @@
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>1920</v>
+        <v>1828</v>
       </c>
       <c r="E100" s="16" t="n">
-        <v>210</v>
+        <v>1828</v>
       </c>
       <c r="F100" s="17" t="n">
-        <v>8.142857142857142</v>
+        <v>0</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
@@ -4131,7 +4075,7 @@
       <c r="A101" s="9" t="inlineStr"/>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Lit Queen / Chene Rustique / Tiroir</t>
+          <t>Lit Queen / Beige / Chene Gris</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -4140,16 +4084,16 @@
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>1828</v>
+        <v>1608</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>1828</v>
+        <v>1608</v>
       </c>
       <c r="F101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
@@ -4165,10 +4109,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr"/>
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>I-5230Q</t>
+        </is>
+      </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Lit Queen avec Rangement</t>
+          <t>Ensemble Chambre</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -4177,16 +4125,16 @@
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>1828</v>
+        <v>1608</v>
       </c>
       <c r="E102" s="16" t="n">
-        <v>1828</v>
+        <v>1608</v>
       </c>
       <c r="F102" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
@@ -4205,7 +4153,7 @@
       <c r="A103" s="9" t="inlineStr"/>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Lit Queen / Beige / Chene Gris</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -4214,16 +4162,16 @@
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>1608</v>
+        <v>1320</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>1608</v>
+        <v>1320</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
@@ -4239,14 +4187,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t>I-5230Q</t>
-        </is>
-      </c>
+      <c r="A104" s="15" t="inlineStr"/>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Ensemble Chambre</t>
+          <t>Lucia — Blanc</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -4255,20 +4199,16 @@
         </is>
       </c>
       <c r="D104" s="16" t="n">
-        <v>1608</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>1608</v>
-      </c>
-      <c r="F104" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>1299</v>
+      </c>
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="17" t="n"/>
       <c r="G104" s="18" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I104" s="6" t="n"/>
@@ -4283,7 +4223,7 @@
       <c r="A105" s="9" t="inlineStr"/>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chêne Blanchi Rustique</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -4292,16 +4232,16 @@
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>1320</v>
+        <v>1258</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>1320</v>
+        <v>1258</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -4320,25 +4260,29 @@
       <c r="A106" s="15" t="inlineStr"/>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Lucia — Blanc</t>
+          <t>Monaco Dining Set</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D106" s="16" t="n">
-        <v>1299</v>
-      </c>
-      <c r="E106" s="16" t="n"/>
-      <c r="F106" s="17" t="n"/>
+        <v>2999.98</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>10.11103703703704</v>
+      </c>
       <c r="G106" s="18" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I106" s="6" t="n"/>
@@ -4350,32 +4294,32 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr"/>
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>T-1274</t>
+        </is>
+      </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Chêne Blanchi Rustique</t>
+          <t>Ensemble de salle à manger Casgrain — velours gris</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1258</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>1258</v>
-      </c>
-      <c r="F107" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>2939.98</v>
+      </c>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="11" t="n"/>
       <c r="G107" s="12" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I107" s="6" t="n"/>
@@ -4387,10 +4331,14 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="15" t="inlineStr"/>
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>T-1274</t>
+        </is>
+      </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Monaco Dining Set</t>
+          <t>Ensemble de salle à manger Waverly — velours gris</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -4399,20 +4347,16 @@
         </is>
       </c>
       <c r="D108" s="16" t="n">
-        <v>2999.98</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>270</v>
-      </c>
-      <c r="F108" s="17" t="n">
-        <v>10.11103703703704</v>
-      </c>
+        <v>2939.98</v>
+      </c>
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="17" t="n"/>
       <c r="G108" s="18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I108" s="6" t="n"/>
@@ -4424,10 +4368,14 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr"/>
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>IF-1620</t>
+        </is>
+      </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Table A Manger - Noyer Brun</t>
+          <t>Meuble Drolet — tissu</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -4436,20 +4384,20 @@
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1899.99</v>
+        <v>2399.98</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1899.99</v>
+        <v>2299.98</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0</v>
+        <v>0.04347863894468647</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I109" s="6" t="n"/>
@@ -4461,14 +4409,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>T-1275</t>
-        </is>
-      </c>
+      <c r="A110" s="15" t="inlineStr"/>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Gaspé — velours beige</t>
+          <t>Table A Manger - Noyer Brun</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -4477,16 +4421,20 @@
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>1709.99</v>
-      </c>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="17" t="n"/>
+        <v>1899.99</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G110" s="18" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I110" s="6" t="n"/>
@@ -4500,12 +4448,12 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>T-1415</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Casgrain — velours gris</t>
+          <t>Meuble Boyer — métal gris</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -4514,12 +4462,12 @@
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>1469.99</v>
+        <v>1799.98</v>
       </c>
       <c r="E111" s="10" t="n"/>
       <c r="F111" s="11" t="n"/>
       <c r="G111" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
@@ -4537,12 +4485,12 @@
     <row r="112">
       <c r="A112" s="15" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>T-1540</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Waverly — velours gris</t>
+          <t>Meuble Chabanel — métal gris</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -4551,12 +4499,12 @@
         </is>
       </c>
       <c r="D112" s="16" t="n">
-        <v>1469.99</v>
+        <v>1539.98</v>
       </c>
       <c r="E112" s="16" t="n"/>
       <c r="F112" s="17" t="n"/>
       <c r="G112" s="18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
@@ -4574,12 +4522,12 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>T-1811 / C-1835</t>
+          <t>T-1402</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Drolet</t>
+          <t>Chaise Christophe — métal gris</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -4588,20 +4536,16 @@
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>1280</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>170</v>
-      </c>
-      <c r="F113" s="11" t="n">
-        <v>6.529411764705882</v>
-      </c>
+        <v>1399.98</v>
+      </c>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="11" t="n"/>
       <c r="G113" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I113" s="6" t="n"/>
@@ -4615,12 +4559,12 @@
     <row r="114">
       <c r="A114" s="15" t="inlineStr">
         <is>
-          <t>T-1811 / C-1826</t>
+          <t>T-1811 / C-1835</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Christophe</t>
+          <t>Ensemble de salle à manger Drolet</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -4656,12 +4600,12 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>IF-1620</t>
+          <t>T-1811 / C-1826</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Meuble Drolet — tissu</t>
+          <t>Ensemble de salle à manger Christophe</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -4670,20 +4614,20 @@
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>1199.99</v>
+        <v>1280</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>2299.98</v>
+        <v>170</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>-0.4782606805276567</v>
+        <v>6.529411764705882</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I115" s="6" t="n"/>
@@ -4697,12 +4641,12 @@
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Marquette — verre blanc</t>
+          <t>Meuble Iberville — métal noir</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -4711,12 +4655,12 @@
         </is>
       </c>
       <c r="D116" s="16" t="n">
-        <v>1000</v>
+        <v>1099.98</v>
       </c>
       <c r="E116" s="16" t="n"/>
       <c r="F116" s="17" t="n"/>
       <c r="G116" s="18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
@@ -4734,12 +4678,12 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>T-1415</t>
+          <t>T-1442 / C-1878</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris</t>
+          <t>Ensemble de salle à manger Marquette — verre blanc</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -4748,12 +4692,12 @@
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>899.99</v>
+        <v>1000</v>
       </c>
       <c r="E117" s="10" t="n"/>
       <c r="F117" s="11" t="n"/>
       <c r="G117" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
@@ -4771,12 +4715,12 @@
     <row r="118">
       <c r="A118" s="15" t="inlineStr">
         <is>
-          <t>T-1402</t>
+          <t>T-1448</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris</t>
+          <t>Meuble Lachine — verre beige</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -4785,16 +4729,20 @@
         </is>
       </c>
       <c r="D118" s="16" t="n">
-        <v>699.99</v>
-      </c>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="17" t="n"/>
+        <v>939.98</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F118" s="17" t="n">
+        <v>-0.5480865384615384</v>
+      </c>
       <c r="G118" s="18" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I118" s="6" t="n"/>
@@ -4882,12 +4830,12 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>T-1448</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Meuble Lachine — verre beige</t>
+          <t>Meuble Beaubien — tissu gris</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
@@ -4896,20 +4844,16 @@
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>469.99</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F121" s="11" t="n">
-        <v>-0.7740432692307693</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="11" t="n"/>
       <c r="G121" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I121" s="6" t="n"/>
@@ -4921,10 +4865,14 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="inlineStr"/>
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Table et 4 chaises</t>
+          <t>Meuble Papineau — tissu gris</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -4933,20 +4881,16 @@
         </is>
       </c>
       <c r="D122" s="16" t="n">
-        <v>299</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>299</v>
-      </c>
-      <c r="F122" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="17" t="n"/>
       <c r="G122" s="18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I122" s="6" t="n"/>
@@ -4958,10 +4902,14 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr"/>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Table et 4 chaises (2)</t>
+          <t>Meuble Fabre — velours beige</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -4970,20 +4918,16 @@
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="F123" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E123" s="10" t="n"/>
+      <c r="F123" s="11" t="n"/>
       <c r="G123" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I123" s="6" t="n"/>
@@ -4995,10 +4939,14 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="15" t="inlineStr"/>
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>IF-1056</t>
+        </is>
+      </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Table et 4 chaises (3)</t>
+          <t>Ensemble salle à manger 5 pièces</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -5007,20 +4955,20 @@
         </is>
       </c>
       <c r="D124" s="16" t="n">
-        <v>299</v>
+        <v>399.98</v>
       </c>
       <c r="E124" s="16" t="n">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="F124" s="17" t="n">
-        <v>0</v>
+        <v>0.1428000000000001</v>
       </c>
       <c r="G124" s="18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I124" s="6" t="n"/>
@@ -5035,25 +4983,25 @@
       <c r="A125" s="9" t="inlineStr"/>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Table et 4 chaises</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>4200</v>
+        <v>299</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>900</v>
+        <v>299</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>3.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
@@ -5072,25 +5020,25 @@
       <c r="A126" s="15" t="inlineStr"/>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Véga</t>
+          <t>Table et 4 chaises (2)</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D126" s="16" t="n">
-        <v>4200</v>
+        <v>299</v>
       </c>
       <c r="E126" s="16" t="n">
-        <v>900</v>
+        <v>299</v>
       </c>
       <c r="F126" s="17" t="n">
-        <v>3.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G126" s="18" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
@@ -5109,25 +5057,25 @@
       <c r="A127" s="9" t="inlineStr"/>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Nexus</t>
+          <t>Table et 4 chaises (3)</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>4200</v>
+        <v>299</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>900</v>
+        <v>299</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>3.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
@@ -5146,7 +5094,7 @@
       <c r="A128" s="15" t="inlineStr"/>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Zénith</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -5158,10 +5106,10 @@
         <v>4200</v>
       </c>
       <c r="E128" s="16" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="F128" s="17" t="n">
-        <v>20</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G128" s="18" t="n">
         <v>117</v>
@@ -5183,7 +5131,7 @@
       <c r="A129" s="9" t="inlineStr"/>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Sérénity</t>
+          <t>Véga</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
@@ -5220,7 +5168,7 @@
       <c r="A130" s="15" t="inlineStr"/>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Nexus</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -5229,16 +5177,16 @@
         </is>
       </c>
       <c r="D130" s="16" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E130" s="16" t="n">
         <v>900</v>
       </c>
       <c r="F130" s="17" t="n">
-        <v>3.444444444444445</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G130" s="18" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
@@ -5257,7 +5205,7 @@
       <c r="A131" s="9" t="inlineStr"/>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Opéra</t>
+          <t>Zénith</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
@@ -5266,16 +5214,16 @@
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3.444444444444445</v>
+        <v>20</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
@@ -5294,7 +5242,7 @@
       <c r="A132" s="15" t="inlineStr"/>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Skyline</t>
+          <t>Sérénity</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -5303,16 +5251,16 @@
         </is>
       </c>
       <c r="D132" s="16" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E132" s="16" t="n">
         <v>900</v>
       </c>
       <c r="F132" s="17" t="n">
-        <v>3.444444444444445</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G132" s="18" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
@@ -5328,10 +5276,14 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr"/>
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>IF 8120</t>
+        </is>
+      </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Nuvola</t>
+          <t>Canapé Casgrain — cuir noir</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
@@ -5340,20 +5292,16 @@
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F133" s="11" t="n">
-        <v>3.444444444444445</v>
-      </c>
+        <v>4199.98</v>
+      </c>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="11" t="n"/>
       <c r="G133" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I133" s="6" t="n"/>
@@ -5368,7 +5316,7 @@
       <c r="A134" s="15" t="inlineStr"/>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -5377,16 +5325,16 @@
         </is>
       </c>
       <c r="D134" s="16" t="n">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="E134" s="16" t="n">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="F134" s="17" t="n">
-        <v>3.418604651162791</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G134" s="18" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
@@ -5405,7 +5353,7 @@
       <c r="A135" s="9" t="inlineStr"/>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Opéra</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -5414,16 +5362,16 @@
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>460</v>
+        <v>900</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>3.782608695652174</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -5439,14 +5387,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="15" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A136" s="15" t="inlineStr"/>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir</t>
+          <t>Skyline</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -5455,16 +5399,20 @@
         </is>
       </c>
       <c r="D136" s="16" t="n">
-        <v>2099.99</v>
-      </c>
-      <c r="E136" s="16" t="n"/>
-      <c r="F136" s="17" t="n"/>
+        <v>4000</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>900</v>
+      </c>
+      <c r="F136" s="17" t="n">
+        <v>3.444444444444445</v>
+      </c>
       <c r="G136" s="18" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I136" s="6" t="n"/>
@@ -5479,7 +5427,7 @@
       <c r="A137" s="9" t="inlineStr"/>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Nuvola</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -5488,16 +5436,16 @@
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>2.75</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
@@ -5516,7 +5464,7 @@
       <c r="A138" s="15" t="inlineStr"/>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Clarence</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -5525,16 +5473,16 @@
         </is>
       </c>
       <c r="D138" s="16" t="n">
-        <v>1800</v>
+        <v>3800</v>
       </c>
       <c r="E138" s="16" t="n">
-        <v>500</v>
+        <v>860</v>
       </c>
       <c r="F138" s="17" t="n">
-        <v>2.6</v>
+        <v>3.418604651162791</v>
       </c>
       <c r="G138" s="18" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
@@ -5550,10 +5498,14 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr"/>
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Depot</t>
+          <t>Canapé Christophe — velours noir</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -5562,20 +5514,16 @@
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>480</v>
-      </c>
-      <c r="F139" s="11" t="n">
-        <v>2.75</v>
-      </c>
+        <v>2599.98</v>
+      </c>
+      <c r="E139" s="10" t="n"/>
+      <c r="F139" s="11" t="n"/>
       <c r="G139" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I139" s="6" t="n"/>
@@ -5587,14 +5535,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A140" s="15" t="inlineStr"/>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -5603,16 +5547,20 @@
         </is>
       </c>
       <c r="D140" s="16" t="n">
-        <v>1299.99</v>
-      </c>
-      <c r="E140" s="16" t="n"/>
-      <c r="F140" s="17" t="n"/>
+        <v>2200</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>460</v>
+      </c>
+      <c r="F140" s="17" t="n">
+        <v>3.782608695652174</v>
+      </c>
       <c r="G140" s="18" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I140" s="6" t="n"/>
@@ -5640,12 +5588,12 @@
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>1099.99</v>
+        <v>2199.98</v>
       </c>
       <c r="E141" s="10" t="n"/>
       <c r="F141" s="11" t="n"/>
       <c r="G141" s="12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
@@ -5664,25 +5612,29 @@
       <c r="A142" s="15" t="inlineStr"/>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Prestige — Fauteuil</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D142" s="16" t="n">
-        <v>1550</v>
-      </c>
-      <c r="E142" s="16" t="n"/>
-      <c r="F142" s="17" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="F142" s="17" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G142" s="18" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I142" s="6" t="n"/>
@@ -5697,25 +5649,29 @@
       <c r="A143" s="9" t="inlineStr"/>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>Elite — Fauteuil</t>
+          <t>Clarence</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="E143" s="10" t="n"/>
-      <c r="F143" s="11" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>2.6</v>
+      </c>
       <c r="G143" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I143" s="6" t="n"/>
@@ -5730,25 +5686,29 @@
       <c r="A144" s="15" t="inlineStr"/>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Royal — Fauteuil</t>
+          <t>Depot</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D144" s="16" t="n">
-        <v>900</v>
-      </c>
-      <c r="E144" s="16" t="n"/>
-      <c r="F144" s="17" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="F144" s="17" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G144" s="18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I144" s="6" t="n"/>
@@ -5763,7 +5723,7 @@
       <c r="A145" s="9" t="inlineStr"/>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>Véga — Fauteuil</t>
+          <t>Prestige — Fauteuil</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
@@ -5772,12 +5732,12 @@
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="E145" s="10" t="n"/>
       <c r="F145" s="11" t="n"/>
       <c r="G145" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
@@ -5793,10 +5753,14 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="15" t="inlineStr"/>
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>IF-8162</t>
+        </is>
+      </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Opéra — Fauteuil</t>
+          <t>Fauteuil inclinable électrique</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
@@ -5807,14 +5771,18 @@
       <c r="D146" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E146" s="16" t="n"/>
-      <c r="F146" s="17" t="n"/>
+      <c r="E146" s="16" t="n">
+        <v>900</v>
+      </c>
+      <c r="F146" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G146" s="18" t="n">
         <v>25</v>
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I146" s="6" t="n"/>
@@ -5829,7 +5797,7 @@
       <c r="A147" s="9" t="inlineStr"/>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Nexus — Fauteuil</t>
+          <t>Elite — Fauteuil</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
@@ -5862,7 +5830,7 @@
       <c r="A148" s="15" t="inlineStr"/>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Skyline — Fauteuil</t>
+          <t>Royal — Fauteuil</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -5895,7 +5863,7 @@
       <c r="A149" s="9" t="inlineStr"/>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Zénith — Fauteuil</t>
+          <t>Véga — Fauteuil</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
@@ -5928,7 +5896,7 @@
       <c r="A150" s="15" t="inlineStr"/>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Sérénity — Fauteuil</t>
+          <t>Opéra — Fauteuil</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
@@ -5961,7 +5929,7 @@
       <c r="A151" s="9" t="inlineStr"/>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>Nuvola — Fauteuil</t>
+          <t>Nexus — Fauteuil</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
@@ -5994,7 +5962,7 @@
       <c r="A152" s="15" t="inlineStr"/>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Volta — Fauteuil</t>
+          <t>Skyline — Fauteuil</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -6003,12 +5971,12 @@
         </is>
       </c>
       <c r="D152" s="16" t="n">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="E152" s="16" t="n"/>
       <c r="F152" s="17" t="n"/>
       <c r="G152" s="18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
@@ -6027,7 +5995,7 @@
       <c r="A153" s="9" t="inlineStr"/>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>Clarence — Fauteuil</t>
+          <t>Zénith — Fauteuil</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
@@ -6036,12 +6004,12 @@
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E153" s="10" t="n"/>
       <c r="F153" s="11" t="n"/>
       <c r="G153" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
@@ -6060,7 +6028,7 @@
       <c r="A154" s="15" t="inlineStr"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Fauteuil-Lit Convertible</t>
+          <t>Sérénity — Fauteuil</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -6069,20 +6037,16 @@
         </is>
       </c>
       <c r="D154" s="16" t="n">
-        <v>499</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>499</v>
-      </c>
-      <c r="F154" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="E154" s="16" t="n"/>
+      <c r="F154" s="17" t="n"/>
       <c r="G154" s="18" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I154" s="6" t="n"/>
@@ -6097,7 +6061,7 @@
       <c r="A155" s="9" t="inlineStr"/>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>Hudson — Fauteuil</t>
+          <t>Nuvola — Fauteuil</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -6106,12 +6070,12 @@
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="E155" s="10" t="n"/>
       <c r="F155" s="11" t="n"/>
       <c r="G155" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
@@ -6127,10 +6091,14 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="15" t="inlineStr"/>
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>IF 8120</t>
+        </is>
+      </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Depot — Fauteuil</t>
+          <t>Canapé Casgrain — cuir noir — Fauteuil</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
@@ -6139,12 +6107,12 @@
         </is>
       </c>
       <c r="D156" s="16" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="E156" s="16" t="n"/>
       <c r="F156" s="17" t="n"/>
       <c r="G156" s="18" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
@@ -6163,7 +6131,7 @@
       <c r="A157" s="9" t="inlineStr"/>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>Milo — Fauteuil</t>
+          <t>Volta — Fauteuil</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -6172,12 +6140,12 @@
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>460</v>
+        <v>860</v>
       </c>
       <c r="E157" s="10" t="n"/>
       <c r="F157" s="11" t="n"/>
       <c r="G157" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
@@ -6195,12 +6163,12 @@
     <row r="158">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>IF-8162</t>
+          <t>IF-8007</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Fauteuil inclinable électrique</t>
+          <t>Canapé Christophe — velours noir — Fauteuil</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -6209,20 +6177,16 @@
         </is>
       </c>
       <c r="D158" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>900</v>
-      </c>
-      <c r="F158" s="17" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E158" s="16" t="n"/>
+      <c r="F158" s="17" t="n"/>
       <c r="G158" s="18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I158" s="6" t="n"/>
@@ -6234,14 +6198,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A159" s="9" t="inlineStr"/>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir — Fauteuil</t>
+          <t>Clarence — Fauteuil</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -6250,12 +6210,12 @@
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E159" s="10" t="n"/>
       <c r="F159" s="11" t="n"/>
       <c r="G159" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
@@ -6271,14 +6231,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A160" s="15" t="inlineStr"/>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Fauteuil</t>
+          <t>Fauteuil-Lit Convertible</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
@@ -6287,16 +6243,20 @@
         </is>
       </c>
       <c r="D160" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="E160" s="16" t="n"/>
-      <c r="F160" s="17" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>499</v>
+      </c>
+      <c r="F160" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G160" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I160" s="6" t="n"/>
@@ -6308,14 +6268,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="inlineStr">
-        <is>
-          <t>IF-8012</t>
-        </is>
-      </c>
+      <c r="A161" s="9" t="inlineStr"/>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige — Fauteuil</t>
+          <t>Hudson — Fauteuil</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -6324,12 +6280,12 @@
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>229.99</v>
+        <v>480</v>
       </c>
       <c r="E161" s="10" t="n"/>
       <c r="F161" s="11" t="n"/>
       <c r="G161" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
@@ -6348,21 +6304,21 @@
       <c r="A162" s="15" t="inlineStr"/>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Lit</t>
+          <t>Depot — Fauteuil</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D162" s="16" t="n">
-        <v>1800</v>
+        <v>480</v>
       </c>
       <c r="E162" s="16" t="n"/>
       <c r="F162" s="17" t="n"/>
       <c r="G162" s="18" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
@@ -6381,21 +6337,21 @@
       <c r="A163" s="9" t="inlineStr"/>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Lit</t>
+          <t>Milo — Fauteuil</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>1800</v>
+        <v>460</v>
       </c>
       <c r="E163" s="10" t="n"/>
       <c r="F163" s="11" t="n"/>
       <c r="G163" s="12" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
@@ -6411,24 +6367,28 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="15" t="inlineStr"/>
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>IF-8012</t>
+        </is>
+      </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Lit</t>
+          <t>Canapé Chabanel — cuir beige — Fauteuil</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D164" s="16" t="n">
-        <v>1800</v>
+        <v>459.98</v>
       </c>
       <c r="E164" s="16" t="n"/>
       <c r="F164" s="17" t="n"/>
       <c r="G164" s="18" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
@@ -6447,7 +6407,7 @@
       <c r="A165" s="9" t="inlineStr"/>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>velours gris avec ailes</t>
+          <t>Ava Jordyn – Gris — Lit</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -6456,20 +6416,16 @@
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F165" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E165" s="10" t="n"/>
+      <c r="F165" s="11" t="n"/>
       <c r="G165" s="12" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I165" s="6" t="n"/>
@@ -6484,7 +6440,7 @@
       <c r="A166" s="15" t="inlineStr"/>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Madisson 100 — Lit</t>
+          <t>Jordyn – Blanc — Lit</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
@@ -6493,12 +6449,12 @@
         </is>
       </c>
       <c r="D166" s="16" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E166" s="16" t="n"/>
       <c r="F166" s="17" t="n"/>
       <c r="G166" s="18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
@@ -6517,7 +6473,7 @@
       <c r="A167" s="9" t="inlineStr"/>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>Logan – Silver — Lit</t>
+          <t>Chambre Moderne Blanche — Lit</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -6526,12 +6482,12 @@
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>880</v>
+        <v>1800</v>
       </c>
       <c r="E167" s="10" t="n"/>
       <c r="F167" s="11" t="n"/>
       <c r="G167" s="12" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
@@ -6547,10 +6503,14 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr"/>
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>IF-5793</t>
+        </is>
+      </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Lit plateforme moderne</t>
+          <t>Lit plateforme — Noir</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
@@ -6559,20 +6519,20 @@
         </is>
       </c>
       <c r="D168" s="16" t="n">
-        <v>840</v>
+        <v>1259.98</v>
       </c>
       <c r="E168" s="16" t="n">
-        <v>840</v>
+        <v>999</v>
       </c>
       <c r="F168" s="17" t="n">
-        <v>0</v>
+        <v>0.2612412412412413</v>
       </c>
       <c r="G168" s="18" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I168" s="6" t="n"/>
@@ -6584,10 +6544,14 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr"/>
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>IF-5790</t>
+        </is>
+      </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Lit</t>
+          <t>Lit plateforme — Gris</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
@@ -6596,16 +6560,20 @@
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>720</v>
-      </c>
-      <c r="E169" s="10" t="n"/>
-      <c r="F169" s="11" t="n"/>
+        <v>1259.98</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>0.2612412412412413</v>
+      </c>
       <c r="G169" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I169" s="6" t="n"/>
@@ -6617,10 +6585,14 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="15" t="inlineStr"/>
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>IF-5792</t>
+        </is>
+      </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Lit</t>
+          <t>Lit plateforme — Beige</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -6629,16 +6601,20 @@
         </is>
       </c>
       <c r="D170" s="16" t="n">
-        <v>700</v>
-      </c>
-      <c r="E170" s="16" t="n"/>
-      <c r="F170" s="17" t="n"/>
+        <v>1259.98</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>999</v>
+      </c>
+      <c r="F170" s="17" t="n">
+        <v>0.2612412412412413</v>
+      </c>
       <c r="G170" s="18" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I170" s="6" t="n"/>
@@ -6653,7 +6629,7 @@
       <c r="A171" s="9" t="inlineStr"/>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Lit</t>
+          <t>velours gris avec ailes</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -6662,16 +6638,20 @@
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>700</v>
-      </c>
-      <c r="E171" s="10" t="n"/>
-      <c r="F171" s="11" t="n"/>
+        <v>1100</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G171" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I171" s="6" t="n"/>
@@ -6683,10 +6663,14 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="15" t="inlineStr"/>
+      <c r="A172" s="15" t="inlineStr">
+        <is>
+          <t>IF-5120</t>
+        </is>
+      </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Lit avec rangement hydraulique</t>
+          <t>Lit contemporain en velours gris</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
@@ -6695,20 +6679,20 @@
         </is>
       </c>
       <c r="D172" s="16" t="n">
-        <v>700</v>
+        <v>1099.98</v>
       </c>
       <c r="E172" s="16" t="n">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="F172" s="17" t="n">
-        <v>0</v>
+        <v>4.238</v>
       </c>
       <c r="G172" s="18" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I172" s="6" t="n"/>
@@ -6722,12 +6706,12 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>IF-5793</t>
+          <t>IF-5940</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Lit plateforme — Noir</t>
+          <t>Lit moderne</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -6736,16 +6720,16 @@
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>699.99</v>
+        <v>999.98</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>999</v>
+        <v>900</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>-0.2993093093093093</v>
+        <v>0.1110888888888889</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
@@ -6761,14 +6745,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="15" t="inlineStr">
-        <is>
-          <t>IF-5790</t>
-        </is>
-      </c>
+      <c r="A174" s="15" t="inlineStr"/>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Lit plateforme — Gris</t>
+          <t>Madisson 100 — Lit</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
@@ -6777,20 +6757,16 @@
         </is>
       </c>
       <c r="D174" s="16" t="n">
-        <v>699.99</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>999</v>
-      </c>
-      <c r="F174" s="17" t="n">
-        <v>-0.2993093093093093</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="E174" s="16" t="n"/>
+      <c r="F174" s="17" t="n"/>
       <c r="G174" s="18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I174" s="6" t="n"/>
@@ -6802,14 +6778,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="inlineStr">
-        <is>
-          <t>IF-5792</t>
-        </is>
-      </c>
+      <c r="A175" s="9" t="inlineStr"/>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Lit plateforme — Beige</t>
+          <t>Logan – Silver — Lit</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -6818,20 +6790,16 @@
         </is>
       </c>
       <c r="D175" s="10" t="n">
-        <v>699.99</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>999</v>
-      </c>
-      <c r="F175" s="11" t="n">
-        <v>-0.2993093093093093</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="E175" s="10" t="n"/>
+      <c r="F175" s="11" t="n"/>
       <c r="G175" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I175" s="6" t="n"/>
@@ -6846,7 +6814,7 @@
       <c r="A176" s="15" t="inlineStr"/>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Lit en Velours</t>
+          <t>Lit plateforme moderne</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
@@ -6855,16 +6823,16 @@
         </is>
       </c>
       <c r="D176" s="16" t="n">
-        <v>699</v>
+        <v>840</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>699</v>
+        <v>840</v>
       </c>
       <c r="F176" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
@@ -6880,10 +6848,14 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr"/>
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>IF-5565</t>
+        </is>
+      </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>Lit Velours Gris avec Rangement</t>
+          <t>Lit plateforme — Beige (2)</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -6892,20 +6864,20 @@
         </is>
       </c>
       <c r="D177" s="10" t="n">
-        <v>699</v>
+        <v>839.98</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>699</v>
+        <v>840</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>0</v>
+        <v>-2.380952380950215e-05</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I177" s="6" t="n"/>
@@ -6917,10 +6889,14 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="15" t="inlineStr"/>
+      <c r="A178" s="15" t="inlineStr">
+        <is>
+          <t>IF-5560</t>
+        </is>
+      </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Amelia-Black — Lit</t>
+          <t>Lit Ahuntsic — velours gris</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
@@ -6929,16 +6905,20 @@
         </is>
       </c>
       <c r="D178" s="16" t="n">
-        <v>680</v>
-      </c>
-      <c r="E178" s="16" t="n"/>
-      <c r="F178" s="17" t="n"/>
+        <v>839.98</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>840</v>
+      </c>
+      <c r="F178" s="17" t="n">
+        <v>-2.380952380950215e-05</v>
+      </c>
       <c r="G178" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H178" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I178" s="6" t="n"/>
@@ -6953,7 +6933,7 @@
       <c r="A179" s="9" t="inlineStr"/>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>Lit Moderne Bas</t>
+          <t>Pompéi – Gris métallisé — Lit</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -6962,20 +6942,16 @@
         </is>
       </c>
       <c r="D179" s="10" t="n">
-        <v>650</v>
-      </c>
-      <c r="E179" s="10" t="n">
-        <v>650</v>
-      </c>
-      <c r="F179" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>720</v>
+      </c>
+      <c r="E179" s="10" t="n"/>
+      <c r="F179" s="11" t="n"/>
       <c r="G179" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I179" s="6" t="n"/>
@@ -6990,7 +6966,7 @@
       <c r="A180" s="15" t="inlineStr"/>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Lit Wing en Velours Noir</t>
+          <t>Harper "Seville" — Lit</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr">
@@ -6999,20 +6975,16 @@
         </is>
       </c>
       <c r="D180" s="16" t="n">
-        <v>650</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>650</v>
-      </c>
-      <c r="F180" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E180" s="16" t="n"/>
+      <c r="F180" s="17" t="n"/>
       <c r="G180" s="18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H180" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I180" s="6" t="n"/>
@@ -7027,7 +6999,7 @@
       <c r="A181" s="9" t="inlineStr"/>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>Lit Papineau — tissu</t>
+          <t>Teddy Bear Blanc — Lit</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -7036,20 +7008,16 @@
         </is>
       </c>
       <c r="D181" s="10" t="n">
-        <v>640</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>640</v>
-      </c>
-      <c r="F181" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E181" s="10" t="n"/>
+      <c r="F181" s="11" t="n"/>
       <c r="G181" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I181" s="6" t="n"/>
@@ -7064,7 +7032,7 @@
       <c r="A182" s="15" t="inlineStr"/>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Lit</t>
+          <t>Lit avec rangement hydraulique</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr">
@@ -7073,16 +7041,20 @@
         </is>
       </c>
       <c r="D182" s="16" t="n">
-        <v>640</v>
-      </c>
-      <c r="E182" s="16" t="n"/>
-      <c r="F182" s="17" t="n"/>
+        <v>700</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="F182" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G182" s="18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I182" s="6" t="n"/>
@@ -7097,7 +7069,7 @@
       <c r="A183" s="9" t="inlineStr"/>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>Lit avec tiroirs de rangement</t>
+          <t>Lit en Velours</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -7106,16 +7078,16 @@
         </is>
       </c>
       <c r="D183" s="10" t="n">
-        <v>599</v>
+        <v>699</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>599</v>
+        <v>699</v>
       </c>
       <c r="F183" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
@@ -7134,7 +7106,7 @@
       <c r="A184" s="15" t="inlineStr"/>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Velours Dusty Pink</t>
+          <t>Lit Velours Gris avec Rangement</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr">
@@ -7143,16 +7115,16 @@
         </is>
       </c>
       <c r="D184" s="16" t="n">
-        <v>575.99</v>
+        <v>699</v>
       </c>
       <c r="E184" s="16" t="n">
-        <v>575.99</v>
+        <v>699</v>
       </c>
       <c r="F184" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H184" s="15" t="inlineStr">
         <is>
@@ -7171,7 +7143,7 @@
       <c r="A185" s="9" t="inlineStr"/>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>Velours Bleu Royal</t>
+          <t>Amelia-Black — Lit</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -7180,20 +7152,16 @@
         </is>
       </c>
       <c r="D185" s="10" t="n">
-        <v>560</v>
-      </c>
-      <c r="E185" s="10" t="n">
-        <v>560</v>
-      </c>
-      <c r="F185" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="E185" s="10" t="n"/>
+      <c r="F185" s="11" t="n"/>
       <c r="G185" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I185" s="6" t="n"/>
@@ -7208,7 +7176,7 @@
       <c r="A186" s="15" t="inlineStr"/>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Lit</t>
+          <t>Lit Moderne Bas</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr">
@@ -7217,16 +7185,20 @@
         </is>
       </c>
       <c r="D186" s="16" t="n">
-        <v>560</v>
-      </c>
-      <c r="E186" s="16" t="n"/>
-      <c r="F186" s="17" t="n"/>
+        <v>650</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="F186" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G186" s="18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H186" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I186" s="6" t="n"/>
@@ -7241,7 +7213,7 @@
       <c r="A187" s="9" t="inlineStr"/>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>Luxora LED Storage Bed</t>
+          <t>Lit Wing en Velours Noir</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -7250,16 +7222,16 @@
         </is>
       </c>
       <c r="D187" s="10" t="n">
-        <v>559.98</v>
+        <v>650</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>559.98</v>
+        <v>650</v>
       </c>
       <c r="F187" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
@@ -7275,14 +7247,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="15" t="inlineStr">
-        <is>
-          <t>IF-5120</t>
-        </is>
-      </c>
+      <c r="A188" s="15" t="inlineStr"/>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Lit contemporain en velours gris</t>
+          <t>Lit Papineau — tissu</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr">
@@ -7291,20 +7259,20 @@
         </is>
       </c>
       <c r="D188" s="16" t="n">
-        <v>549.99</v>
+        <v>640</v>
       </c>
       <c r="E188" s="16" t="n">
-        <v>210</v>
+        <v>640</v>
       </c>
       <c r="F188" s="17" t="n">
-        <v>1.619</v>
+        <v>0</v>
       </c>
       <c r="G188" s="18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H188" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I188" s="6" t="n"/>
@@ -7316,14 +7284,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="9" t="inlineStr">
-        <is>
-          <t>IF-5940</t>
-        </is>
-      </c>
+      <c r="A189" s="9" t="inlineStr"/>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>Lit moderne</t>
+          <t>Luna Riley – Finition argentée — Lit</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
@@ -7332,20 +7296,16 @@
         </is>
       </c>
       <c r="D189" s="10" t="n">
-        <v>499.99</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F189" s="11" t="n">
-        <v>-0.4444555555555555</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="E189" s="10" t="n"/>
+      <c r="F189" s="11" t="n"/>
       <c r="G189" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I189" s="6" t="n"/>
@@ -7357,10 +7317,14 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="15" t="inlineStr"/>
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>IF-5295</t>
+        </is>
+      </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Lit en tissu gris avec rangement hydraulique</t>
+          <t>Lit plateforme — Gris (2)</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr">
@@ -7369,20 +7333,20 @@
         </is>
       </c>
       <c r="D190" s="16" t="n">
-        <v>499.99</v>
+        <v>599.98</v>
       </c>
       <c r="E190" s="16" t="n">
-        <v>499.99</v>
+        <v>580</v>
       </c>
       <c r="F190" s="17" t="n">
-        <v>0</v>
+        <v>0.034448275862069</v>
       </c>
       <c r="G190" s="18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H190" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I190" s="6" t="n"/>
@@ -7397,7 +7361,7 @@
       <c r="A191" s="9" t="inlineStr"/>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>Lit King en Velours Bleu</t>
+          <t>Lit avec tiroirs de rangement</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
@@ -7406,16 +7370,16 @@
         </is>
       </c>
       <c r="D191" s="10" t="n">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="F191" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
@@ -7431,14 +7395,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="15" t="inlineStr">
-        <is>
-          <t>IF-5565</t>
-        </is>
-      </c>
+      <c r="A192" s="15" t="inlineStr"/>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Lit plateforme — Beige (2)</t>
+          <t>Velours Dusty Pink</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr">
@@ -7447,20 +7407,20 @@
         </is>
       </c>
       <c r="D192" s="16" t="n">
-        <v>479.99</v>
+        <v>575.99</v>
       </c>
       <c r="E192" s="16" t="n">
-        <v>840</v>
+        <v>575.99</v>
       </c>
       <c r="F192" s="17" t="n">
-        <v>-0.4285833333333333</v>
+        <v>0</v>
       </c>
       <c r="G192" s="18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H192" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I192" s="6" t="n"/>
@@ -7472,14 +7432,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="inlineStr">
-        <is>
-          <t>IF-5560</t>
-        </is>
-      </c>
+      <c r="A193" s="9" t="inlineStr"/>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>Lit Ahuntsic — velours gris</t>
+          <t>Velours Bleu Royal</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
@@ -7488,20 +7444,20 @@
         </is>
       </c>
       <c r="D193" s="10" t="n">
-        <v>479.99</v>
+        <v>560</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>840</v>
+        <v>560</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>-0.4285833333333333</v>
+        <v>0</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I193" s="6" t="n"/>
@@ -7513,14 +7469,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>IF-5710</t>
-        </is>
-      </c>
+      <c r="A194" s="15" t="inlineStr"/>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Lit Jeanne-Mance — tissu gris</t>
+          <t>Lucia — Blanc — Lit</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr">
@@ -7529,20 +7481,16 @@
         </is>
       </c>
       <c r="D194" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="E194" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="F194" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="E194" s="16" t="n"/>
+      <c r="F194" s="17" t="n"/>
       <c r="G194" s="18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H194" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I194" s="6" t="n"/>
@@ -7557,7 +7505,7 @@
       <c r="A195" s="9" t="inlineStr"/>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>Lit en Velours Gris</t>
+          <t>Luxora LED Storage Bed</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
@@ -7566,16 +7514,16 @@
         </is>
       </c>
       <c r="D195" s="10" t="n">
-        <v>340</v>
+        <v>559.98</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>340</v>
+        <v>559.98</v>
       </c>
       <c r="F195" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
@@ -7591,10 +7539,14 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="15" t="inlineStr"/>
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>IF-5408</t>
+        </is>
+      </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Lit Queen en Velours Gris</t>
+          <t>Lit avec rangement</t>
         </is>
       </c>
       <c r="C196" s="15" t="inlineStr">
@@ -7603,20 +7555,20 @@
         </is>
       </c>
       <c r="D196" s="16" t="n">
-        <v>340</v>
+        <v>539.98</v>
       </c>
       <c r="E196" s="16" t="n">
-        <v>340</v>
+        <v>520</v>
       </c>
       <c r="F196" s="17" t="n">
-        <v>0</v>
+        <v>0.03842307692307696</v>
       </c>
       <c r="G196" s="18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H196" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I196" s="6" t="n"/>
@@ -7628,10 +7580,14 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="9" t="inlineStr"/>
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>IF-5407</t>
+        </is>
+      </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>Matelas Ortho Care – Confort Semi-Ferme</t>
+          <t>Lit Fabre — velours beige</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
@@ -7640,20 +7596,20 @@
         </is>
       </c>
       <c r="D197" s="10" t="n">
-        <v>320</v>
+        <v>539.98</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>0</v>
+        <v>0.03842307692307696</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I197" s="6" t="n"/>
@@ -7665,14 +7621,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="15" t="inlineStr">
-        <is>
-          <t>IF-5295</t>
-        </is>
-      </c>
+      <c r="A198" s="15" t="inlineStr"/>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Lit plateforme — Gris (2)</t>
+          <t>Lit en tissu gris avec rangement hydraulique</t>
         </is>
       </c>
       <c r="C198" s="15" t="inlineStr">
@@ -7681,20 +7633,20 @@
         </is>
       </c>
       <c r="D198" s="16" t="n">
-        <v>289.99</v>
+        <v>499.99</v>
       </c>
       <c r="E198" s="16" t="n">
-        <v>580</v>
+        <v>499.99</v>
       </c>
       <c r="F198" s="17" t="n">
-        <v>-0.5000172413793104</v>
+        <v>0</v>
       </c>
       <c r="G198" s="18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H198" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I198" s="6" t="n"/>
@@ -7706,14 +7658,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t>IF-5408</t>
-        </is>
-      </c>
+      <c r="A199" s="9" t="inlineStr"/>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>Lit avec rangement</t>
+          <t>Lit King en Velours Bleu</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
@@ -7722,20 +7670,20 @@
         </is>
       </c>
       <c r="D199" s="10" t="n">
-        <v>269.99</v>
+        <v>480</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>-0.4807884615384615</v>
+        <v>0</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I199" s="6" t="n"/>
@@ -7749,12 +7697,12 @@
     <row r="200">
       <c r="A200" s="15" t="inlineStr">
         <is>
-          <t>IF-5407</t>
+          <t>IF-5710</t>
         </is>
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Lit Fabre — velours beige</t>
+          <t>Lit Jeanne-Mance — tissu gris</t>
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr">
@@ -7763,20 +7711,20 @@
         </is>
       </c>
       <c r="D200" s="16" t="n">
-        <v>269.99</v>
+        <v>450</v>
       </c>
       <c r="E200" s="16" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="F200" s="17" t="n">
-        <v>-0.4807884615384615</v>
+        <v>0</v>
       </c>
       <c r="G200" s="18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H200" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I200" s="6" t="n"/>
@@ -7791,7 +7739,7 @@
       <c r="A201" s="9" t="inlineStr"/>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>Matelas OrthoPedic Deluxe – Confort moyen</t>
+          <t>Lit en Velours Gris</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
@@ -7800,16 +7748,16 @@
         </is>
       </c>
       <c r="D201" s="10" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="F201" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
@@ -7825,14 +7773,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="15" t="inlineStr">
-        <is>
-          <t>IF-176</t>
-        </is>
-      </c>
+      <c r="A202" s="15" t="inlineStr"/>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Lit Jarry — noir</t>
+          <t>Lit Queen en Velours Gris</t>
         </is>
       </c>
       <c r="C202" s="15" t="inlineStr">
@@ -7841,20 +7785,20 @@
         </is>
       </c>
       <c r="D202" s="16" t="n">
-        <v>149.99</v>
+        <v>340</v>
       </c>
       <c r="E202" s="16" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="F202" s="17" t="n">
-        <v>-0.3182272727272727</v>
+        <v>0</v>
       </c>
       <c r="G202" s="18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H202" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I202" s="6" t="n"/>
@@ -7866,14 +7810,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="9" t="inlineStr">
-        <is>
-          <t>IF-5430</t>
-        </is>
-      </c>
+      <c r="A203" s="9" t="inlineStr"/>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>Lit Verdun — tissu gris</t>
+          <t>Matelas Ortho Care – Confort Semi-Ferme</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
@@ -7882,20 +7822,20 @@
         </is>
       </c>
       <c r="D203" s="10" t="n">
-        <v>149.99</v>
+        <v>320</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>-0.40004</v>
+        <v>0</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I203" s="6" t="n"/>
@@ -7907,32 +7847,36 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="15" t="inlineStr"/>
+      <c r="A204" s="15" t="inlineStr">
+        <is>
+          <t>IF-176</t>
+        </is>
+      </c>
       <c r="B204" s="15" t="inlineStr">
         <is>
-          <t>Lit Superposé — Noir</t>
+          <t>Lit Jarry — noir</t>
         </is>
       </c>
       <c r="C204" s="15" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D204" s="16" t="n">
-        <v>780</v>
+        <v>299.98</v>
       </c>
       <c r="E204" s="16" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="F204" s="17" t="n">
-        <v>3.333333333333333</v>
+        <v>0.3635454545454546</v>
       </c>
       <c r="G204" s="18" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H204" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I204" s="6" t="n"/>
@@ -7944,32 +7888,36 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="9" t="inlineStr"/>
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>IF-5430</t>
+        </is>
+      </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>Lit Superposé — Blanc</t>
+          <t>Lit Verdun — tissu gris</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D205" s="10" t="n">
-        <v>750</v>
+        <v>299.98</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>3.166666666666667</v>
+        <v>0.1999200000000001</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I205" s="6" t="n"/>
@@ -7981,32 +7929,36 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="15" t="inlineStr"/>
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>IF-174</t>
+        </is>
+      </c>
       <c r="B206" s="15" t="inlineStr">
         <is>
-          <t>Lit Superposé — Gris</t>
+          <t>Lit Everett — blanc</t>
         </is>
       </c>
       <c r="C206" s="15" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D206" s="16" t="n">
-        <v>750</v>
+        <v>279.98</v>
       </c>
       <c r="E206" s="16" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F206" s="17" t="n">
-        <v>3.166666666666667</v>
+        <v>0.1199200000000001</v>
       </c>
       <c r="G206" s="18" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H206" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I206" s="6" t="n"/>
@@ -8018,32 +7970,36 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="9" t="inlineStr"/>
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>IF-175</t>
+        </is>
+      </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>SOFIA – Pillow Top | Série Cuivre</t>
+          <t>Lit Dante — noir</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D207" s="10" t="n">
-        <v>920</v>
+        <v>259.98</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>920</v>
+        <v>220</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>0</v>
+        <v>0.1817272727272728</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I207" s="6" t="n"/>
@@ -8058,25 +8014,25 @@
       <c r="A208" s="15" t="inlineStr"/>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>SOFIA – Tight Top | Série Cuivre</t>
+          <t>Matelas OrthoPedic Deluxe – Confort moyen</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D208" s="16" t="n">
-        <v>760</v>
+        <v>220</v>
       </c>
       <c r="E208" s="16" t="n">
-        <v>760</v>
+        <v>220</v>
       </c>
       <c r="F208" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H208" s="15" t="inlineStr">
         <is>
@@ -8095,25 +8051,25 @@
       <c r="A209" s="9" t="inlineStr"/>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>Matelas Bella Euro top – Copper Series</t>
+          <t>Lit Superposé — Noir</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D209" s="10" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>750</v>
+        <v>180</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
@@ -8132,22 +8088,22 @@
       <c r="A210" s="15" t="inlineStr"/>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Matelas Jeanne-Mance — tissu</t>
+          <t>Lit Superposé — Blanc</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D210" s="16" t="n">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="E210" s="16" t="n">
-        <v>740</v>
+        <v>180</v>
       </c>
       <c r="F210" s="17" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="G210" s="18" t="n">
         <v>21</v>
@@ -8169,25 +8125,25 @@
       <c r="A211" s="9" t="inlineStr"/>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>Matelas Christophe — tissu noir</t>
+          <t>Lit Superposé — Gris</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D211" s="10" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>690</v>
+        <v>180</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
@@ -8206,7 +8162,7 @@
       <c r="A212" s="15" t="inlineStr"/>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>Matelas Hailey Euro Deluxe 4</t>
+          <t>SOFIA – Pillow Top | Série Cuivre</t>
         </is>
       </c>
       <c r="C212" s="15" t="inlineStr">
@@ -8215,16 +8171,16 @@
         </is>
       </c>
       <c r="D212" s="16" t="n">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="E212" s="16" t="n">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="F212" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G212" s="18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H212" s="15" t="inlineStr">
         <is>
@@ -8243,7 +8199,7 @@
       <c r="A213" s="9" t="inlineStr"/>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>Matelas Alisha Hybrid – Gel Foam</t>
+          <t>SOFIA – Tight Top | Série Cuivre</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
@@ -8252,16 +8208,16 @@
         </is>
       </c>
       <c r="D213" s="10" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="F213" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
@@ -8280,7 +8236,7 @@
       <c r="A214" s="15" t="inlineStr"/>
       <c r="B214" s="15" t="inlineStr">
         <is>
-          <t>Matelas Fabre — tissu</t>
+          <t>Matelas Bella Euro top – Copper Series</t>
         </is>
       </c>
       <c r="C214" s="15" t="inlineStr">
@@ -8289,16 +8245,16 @@
         </is>
       </c>
       <c r="D214" s="16" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="E214" s="16" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="F214" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G214" s="18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H214" s="15" t="inlineStr">
         <is>
@@ -8317,7 +8273,7 @@
       <c r="A215" s="9" t="inlineStr"/>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>Matelas Breeze Cool Max – Fermeté moyenne</t>
+          <t>Matelas Jeanne-Mance — tissu</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
@@ -8326,16 +8282,16 @@
         </is>
       </c>
       <c r="D215" s="10" t="n">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="F215" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G215" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
@@ -8354,7 +8310,7 @@
       <c r="A216" s="15" t="inlineStr"/>
       <c r="B216" s="15" t="inlineStr">
         <is>
-          <t>Matelas DREAM-O-PEDIC &amp; Tissu bambou</t>
+          <t>Matelas Christophe — tissu noir</t>
         </is>
       </c>
       <c r="C216" s="15" t="inlineStr">
@@ -8363,16 +8319,16 @@
         </is>
       </c>
       <c r="D216" s="16" t="n">
-        <v>250</v>
+        <v>690</v>
       </c>
       <c r="E216" s="16" t="n">
-        <v>250</v>
+        <v>690</v>
       </c>
       <c r="F216" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G216" s="18" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H216" s="15" t="inlineStr">
         <is>
@@ -8391,7 +8347,7 @@
       <c r="A217" s="9" t="inlineStr"/>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>Matelas Rest-O-Pedic — | SEMI-FERME</t>
+          <t>Matelas Hailey Euro Deluxe 4</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
@@ -8400,16 +8356,16 @@
         </is>
       </c>
       <c r="D217" s="10" t="n">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="F217" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
@@ -8425,14 +8381,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="15" t="inlineStr">
-        <is>
-          <t>C-1253</t>
-        </is>
-      </c>
+      <c r="A218" s="15" t="inlineStr"/>
       <c r="B218" s="15" t="inlineStr">
         <is>
-          <t>Chaise en velours crème — Beige</t>
+          <t>Matelas Alisha Hybrid – Gel Foam</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
@@ -8441,20 +8393,20 @@
         </is>
       </c>
       <c r="D218" s="16" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="E218" s="16" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="F218" s="17" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="G218" s="18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H218" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I218" s="6" t="n"/>
@@ -8469,25 +8421,25 @@
       <c r="A219" s="9" t="inlineStr"/>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>Meuble Telé - 60" L</t>
+          <t>Matelas Fabre — tissu</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D219" s="10" t="n">
-        <v>398.98</v>
+        <v>440</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>398.98</v>
+        <v>440</v>
       </c>
       <c r="F219" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -8506,19 +8458,19 @@
       <c r="A220" s="15" t="inlineStr"/>
       <c r="B220" s="15" t="inlineStr">
         <is>
-          <t>Meuble Télé - 72" L — Brun (2)</t>
+          <t>Matelas Breeze Cool Max – Fermeté moyenne</t>
         </is>
       </c>
       <c r="C220" s="15" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D220" s="16" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E220" s="16" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F220" s="17" t="n">
         <v>0</v>
@@ -8540,32 +8492,36 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="9" t="inlineStr"/>
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>C-1253</t>
+        </is>
+      </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>Meuble Télé - 63" L</t>
+          <t>Chaise en velours crème — Beige</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D221" s="10" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="F221" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I221" s="6" t="n"/>
@@ -8580,25 +8536,25 @@
       <c r="A222" s="15" t="inlineStr"/>
       <c r="B222" s="15" t="inlineStr">
         <is>
-          <t>Meuble Télé - 72" L — Brun</t>
+          <t>Matelas DREAM-O-PEDIC &amp; Tissu bambou</t>
         </is>
       </c>
       <c r="C222" s="15" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D222" s="16" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E222" s="16" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="F222" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G222" s="18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H222" s="15" t="inlineStr">
         <is>
@@ -8617,25 +8573,25 @@
       <c r="A223" s="9" t="inlineStr"/>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>Meuble Télé - 60" L</t>
+          <t>Matelas Rest-O-Pedic — | SEMI-FERME</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D223" s="10" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="F223" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
@@ -8654,7 +8610,7 @@
       <c r="A224" s="15" t="inlineStr"/>
       <c r="B224" s="15" t="inlineStr">
         <is>
-          <t>Meuble Télé- 72" L</t>
+          <t>Meuble Telé - 60" L</t>
         </is>
       </c>
       <c r="C224" s="15" t="inlineStr">
@@ -8663,16 +8619,16 @@
         </is>
       </c>
       <c r="D224" s="16" t="n">
-        <v>290</v>
+        <v>398.98</v>
       </c>
       <c r="E224" s="16" t="n">
-        <v>290</v>
+        <v>398.98</v>
       </c>
       <c r="F224" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H224" s="15" t="inlineStr">
         <is>
@@ -8688,32 +8644,32 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="9" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A225" s="9" t="inlineStr"/>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Poufs et ottomane</t>
+          <t>Meuble Télé - 72" L — Brun (2)</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>Poufs et ottomanes</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D225" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="E225" s="10" t="n"/>
-      <c r="F225" s="11" t="n"/>
+        <v>395</v>
+      </c>
+      <c r="E225" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="F225" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G225" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I225" s="6" t="n"/>
@@ -8728,25 +8684,29 @@
       <c r="A226" s="15" t="inlineStr"/>
       <c r="B226" s="15" t="inlineStr">
         <is>
-          <t>Kova — Poufs et ottomane</t>
+          <t>Meuble Télé - 63" L</t>
         </is>
       </c>
       <c r="C226" s="15" t="inlineStr">
         <is>
-          <t>Poufs et ottomanes</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D226" s="16" t="n">
-        <v>280</v>
-      </c>
-      <c r="E226" s="16" t="n"/>
-      <c r="F226" s="17" t="n"/>
+        <v>380</v>
+      </c>
+      <c r="E226" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="F226" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G226" s="18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H226" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I226" s="6" t="n"/>
@@ -8761,25 +8721,25 @@
       <c r="A227" s="9" t="inlineStr"/>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Meuble Télé - 72" L — Brun</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D227" s="10" t="n">
-        <v>2500</v>
+        <v>350</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>2500</v>
+        <v>350</v>
       </c>
       <c r="F227" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
@@ -8798,25 +8758,25 @@
       <c r="A228" s="15" t="inlineStr"/>
       <c r="B228" s="15" t="inlineStr">
         <is>
-          <t>Vault</t>
+          <t>Meuble Télé - 60" L</t>
         </is>
       </c>
       <c r="C228" s="15" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D228" s="16" t="n">
-        <v>2500</v>
+        <v>310</v>
       </c>
       <c r="E228" s="16" t="n">
-        <v>2500</v>
+        <v>310</v>
       </c>
       <c r="F228" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G228" s="18" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H228" s="15" t="inlineStr">
         <is>
@@ -8835,25 +8795,25 @@
       <c r="A229" s="9" t="inlineStr"/>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Meuble Télé- 72" L</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D229" s="10" t="n">
-        <v>2400</v>
+        <v>290</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>2400</v>
+        <v>290</v>
       </c>
       <c r="F229" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
@@ -8872,29 +8832,25 @@
       <c r="A230" s="15" t="inlineStr"/>
       <c r="B230" s="15" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Kova — Poufs et ottomane</t>
         </is>
       </c>
       <c r="C230" s="15" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Poufs et ottomanes</t>
         </is>
       </c>
       <c r="D230" s="16" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E230" s="16" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F230" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="E230" s="16" t="n"/>
+      <c r="F230" s="17" t="n"/>
       <c r="G230" s="18" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="H230" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I230" s="6" t="n"/>
@@ -8906,32 +8862,32 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="inlineStr"/>
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>Solace</t>
+          <t>Canapé Christophe — velours noir — Poufs et ottomane</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Poufs et ottomanes</t>
         </is>
       </c>
       <c r="D231" s="10" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E231" s="10" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F231" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="E231" s="10" t="n"/>
+      <c r="F231" s="11" t="n"/>
       <c r="G231" s="12" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I231" s="6" t="n"/>
@@ -8943,10 +8899,14 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="15" t="inlineStr"/>
+      <c r="A232" s="15" t="inlineStr">
+        <is>
+          <t>IF-8500</t>
+        </is>
+      </c>
       <c r="B232" s="15" t="inlineStr">
         <is>
-          <t>Stash</t>
+          <t>Sectionnel inclinable</t>
         </is>
       </c>
       <c r="C232" s="15" t="inlineStr">
@@ -8955,20 +8915,20 @@
         </is>
       </c>
       <c r="D232" s="16" t="n">
-        <v>2300</v>
+        <v>3999.98</v>
       </c>
       <c r="E232" s="16" t="n">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="F232" s="17" t="n">
-        <v>0</v>
+        <v>-4.999999999995453e-06</v>
       </c>
       <c r="G232" s="18" t="n">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="H232" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I232" s="6" t="n"/>
@@ -8982,12 +8942,12 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>IF-9050 / IF-9051</t>
+          <t>IF-9090</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel canapé-lit</t>
+          <t>chaise longue gauche (LHF) — Gris</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
@@ -8996,20 +8956,20 @@
         </is>
       </c>
       <c r="D233" s="10" t="n">
-        <v>2200</v>
+        <v>3299.98</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>0</v>
+        <v>0.09999333333333334</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I233" s="6" t="n"/>
@@ -9023,12 +8983,12 @@
     <row r="234">
       <c r="A234" s="15" t="inlineStr">
         <is>
-          <t>IF-9085 / IF-9086</t>
+          <t>IF-9095</t>
         </is>
       </c>
       <c r="B234" s="15" t="inlineStr">
         <is>
-          <t>Sectionnel Drolet — bouclé gris</t>
+          <t>chaise longue gauche (LHF) — Noir</t>
         </is>
       </c>
       <c r="C234" s="15" t="inlineStr">
@@ -9037,20 +8997,20 @@
         </is>
       </c>
       <c r="D234" s="16" t="n">
-        <v>2200</v>
+        <v>2999.98</v>
       </c>
       <c r="E234" s="16" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="F234" s="17" t="n">
-        <v>0</v>
+        <v>-6.666666666660604e-06</v>
       </c>
       <c r="G234" s="18" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H234" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I234" s="6" t="n"/>
@@ -9062,14 +9022,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="9" t="inlineStr">
-        <is>
-          <t>IF-8500</t>
-        </is>
-      </c>
+      <c r="A235" s="9" t="inlineStr"/>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel inclinable</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
@@ -9078,20 +9034,20 @@
         </is>
       </c>
       <c r="D235" s="10" t="n">
-        <v>1999.99</v>
+        <v>2500</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>-0.5000025</v>
+        <v>0</v>
       </c>
       <c r="G235" s="12" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I235" s="6" t="n"/>
@@ -9106,7 +9062,7 @@
       <c r="A236" s="15" t="inlineStr"/>
       <c r="B236" s="15" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Vault</t>
         </is>
       </c>
       <c r="C236" s="15" t="inlineStr">
@@ -9115,16 +9071,16 @@
         </is>
       </c>
       <c r="D236" s="16" t="n">
-        <v>1998.99</v>
+        <v>2500</v>
       </c>
       <c r="E236" s="16" t="n">
-        <v>1998.99</v>
+        <v>2500</v>
       </c>
       <c r="F236" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G236" s="18" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H236" s="15" t="inlineStr">
         <is>
@@ -9140,14 +9096,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="9" t="inlineStr">
-        <is>
-          <t>IF-9075 / IF-9076</t>
-        </is>
-      </c>
+      <c r="A237" s="9" t="inlineStr"/>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel Iberville — tissu brun</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
@@ -9156,16 +9108,16 @@
         </is>
       </c>
       <c r="D237" s="10" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="F237" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G237" s="12" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
@@ -9181,14 +9133,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="15" t="inlineStr">
-        <is>
-          <t>IF-9090</t>
-        </is>
-      </c>
+      <c r="A238" s="15" t="inlineStr"/>
       <c r="B238" s="15" t="inlineStr">
         <is>
-          <t>chaise longue gauche (LHF) — Gris</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C238" s="15" t="inlineStr">
@@ -9197,20 +9145,20 @@
         </is>
       </c>
       <c r="D238" s="16" t="n">
-        <v>1649.99</v>
+        <v>2400</v>
       </c>
       <c r="E238" s="16" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F238" s="17" t="n">
-        <v>-0.4500033333333333</v>
+        <v>0</v>
       </c>
       <c r="G238" s="18" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="H238" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I238" s="6" t="n"/>
@@ -9222,14 +9170,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="inlineStr">
-        <is>
-          <t>IF-9095</t>
-        </is>
-      </c>
+      <c r="A239" s="9" t="inlineStr"/>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>chaise longue gauche (LHF) — Noir</t>
+          <t>Solace</t>
         </is>
       </c>
       <c r="C239" s="9" t="inlineStr">
@@ -9238,20 +9182,20 @@
         </is>
       </c>
       <c r="D239" s="10" t="n">
-        <v>1499.99</v>
+        <v>2400</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>-0.5000033333333334</v>
+        <v>0</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I239" s="6" t="n"/>
@@ -9263,10 +9207,14 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="15" t="inlineStr"/>
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>IF-9035</t>
+        </is>
+      </c>
       <c r="B240" s="15" t="inlineStr">
         <is>
-          <t>Kova — Sectionnel</t>
+          <t>Sectionnel Fabre — tissu gris</t>
         </is>
       </c>
       <c r="C240" s="15" t="inlineStr">
@@ -9275,16 +9223,20 @@
         </is>
       </c>
       <c r="D240" s="16" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E240" s="16" t="n"/>
-      <c r="F240" s="17" t="n"/>
+        <v>2399.98</v>
+      </c>
+      <c r="E240" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F240" s="17" t="n">
+        <v>-8.333333333325754e-06</v>
+      </c>
       <c r="G240" s="18" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H240" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I240" s="6" t="n"/>
@@ -9299,7 +9251,7 @@
       <c r="A241" s="9" t="inlineStr"/>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>Grey Refuge</t>
+          <t>Stash</t>
         </is>
       </c>
       <c r="C241" s="9" t="inlineStr">
@@ -9308,16 +9260,16 @@
         </is>
       </c>
       <c r="D241" s="10" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="F241" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G241" s="12" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
@@ -9333,10 +9285,14 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="15" t="inlineStr"/>
+      <c r="A242" s="15" t="inlineStr">
+        <is>
+          <t>IF-9050 / IF-9051</t>
+        </is>
+      </c>
       <c r="B242" s="15" t="inlineStr">
         <is>
-          <t>Black Refuge</t>
+          <t>Sectionnel canapé-lit</t>
         </is>
       </c>
       <c r="C242" s="15" t="inlineStr">
@@ -9345,16 +9301,16 @@
         </is>
       </c>
       <c r="D242" s="16" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="E242" s="16" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="F242" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G242" s="18" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H242" s="15" t="inlineStr">
         <is>
@@ -9370,10 +9326,14 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="9" t="inlineStr"/>
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>IF-9085 / IF-9086</t>
+        </is>
+      </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>Nido</t>
+          <t>Sectionnel Drolet — bouclé gris</t>
         </is>
       </c>
       <c r="C243" s="9" t="inlineStr">
@@ -9382,16 +9342,16 @@
         </is>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1398.99</v>
+        <v>2200</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1398.99</v>
+        <v>2200</v>
       </c>
       <c r="F243" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
@@ -9410,7 +9370,7 @@
       <c r="A244" s="15" t="inlineStr"/>
       <c r="B244" s="15" t="inlineStr">
         <is>
-          <t>Luno</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -9419,16 +9379,16 @@
         </is>
       </c>
       <c r="D244" s="16" t="n">
-        <v>1200</v>
+        <v>1998.99</v>
       </c>
       <c r="E244" s="16" t="n">
-        <v>1200</v>
+        <v>1998.99</v>
       </c>
       <c r="F244" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G244" s="18" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="H244" s="15" t="inlineStr">
         <is>
@@ -9446,12 +9406,12 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>IF-9035</t>
+          <t>IF-9075 / IF-9076</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel Fabre — tissu gris</t>
+          <t>Sectionnel Iberville — tissu brun</t>
         </is>
       </c>
       <c r="C245" s="9" t="inlineStr">
@@ -9460,20 +9420,20 @@
         </is>
       </c>
       <c r="D245" s="10" t="n">
-        <v>1199.99</v>
+        <v>1900</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>-0.5000041666666667</v>
+        <v>0</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I245" s="6" t="n"/>
@@ -9488,7 +9448,7 @@
       <c r="A246" s="15" t="inlineStr"/>
       <c r="B246" s="15" t="inlineStr">
         <is>
-          <t>Refuge</t>
+          <t>Kova — Sectionnel</t>
         </is>
       </c>
       <c r="C246" s="15" t="inlineStr">
@@ -9497,20 +9457,16 @@
         </is>
       </c>
       <c r="D246" s="16" t="n">
-        <v>1199.98</v>
-      </c>
-      <c r="E246" s="16" t="n">
-        <v>1199.98</v>
-      </c>
-      <c r="F246" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="E246" s="16" t="n"/>
+      <c r="F246" s="17" t="n"/>
       <c r="G246" s="18" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H246" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I246" s="6" t="n"/>
@@ -9525,7 +9481,7 @@
       <c r="A247" s="9" t="inlineStr"/>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>Sofa Lit - 8A14L83</t>
+          <t>Grey Refuge</t>
         </is>
       </c>
       <c r="C247" s="9" t="inlineStr">
@@ -9534,16 +9490,16 @@
         </is>
       </c>
       <c r="D247" s="10" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="F247" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
@@ -9562,7 +9518,7 @@
       <c r="A248" s="15" t="inlineStr"/>
       <c r="B248" s="15" t="inlineStr">
         <is>
-          <t>Sofa Lit</t>
+          <t>Black Refuge</t>
         </is>
       </c>
       <c r="C248" s="15" t="inlineStr">
@@ -9571,16 +9527,16 @@
         </is>
       </c>
       <c r="D248" s="16" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="E248" s="16" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="F248" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G248" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H248" s="15" t="inlineStr">
         <is>
@@ -9599,7 +9555,7 @@
       <c r="A249" s="9" t="inlineStr"/>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>Sofa Lit — Brun</t>
+          <t>Nido</t>
         </is>
       </c>
       <c r="C249" s="9" t="inlineStr">
@@ -9608,16 +9564,16 @@
         </is>
       </c>
       <c r="D249" s="10" t="n">
-        <v>1050</v>
+        <v>1398.99</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>1050</v>
+        <v>1398.99</v>
       </c>
       <c r="F249" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H249" s="9" t="inlineStr">
         <is>
@@ -9636,7 +9592,7 @@
       <c r="A250" s="15" t="inlineStr"/>
       <c r="B250" s="15" t="inlineStr">
         <is>
-          <t>Sofa Lit (2)</t>
+          <t>Luno</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -9645,16 +9601,16 @@
         </is>
       </c>
       <c r="D250" s="16" t="n">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="E250" s="16" t="n">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="F250" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G250" s="18" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H250" s="15" t="inlineStr">
         <is>
@@ -9673,7 +9629,7 @@
       <c r="A251" s="9" t="inlineStr"/>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>Sofa Lit — Gris</t>
+          <t>Refuge</t>
         </is>
       </c>
       <c r="C251" s="9" t="inlineStr">
@@ -9682,16 +9638,16 @@
         </is>
       </c>
       <c r="D251" s="10" t="n">
-        <v>1050</v>
+        <v>1199.98</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>1050</v>
+        <v>1199.98</v>
       </c>
       <c r="F251" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H251" s="9" t="inlineStr">
         <is>
@@ -9710,7 +9666,7 @@
       <c r="A252" s="15" t="inlineStr"/>
       <c r="B252" s="15" t="inlineStr">
         <is>
-          <t>Sofa-Lit</t>
+          <t>Sofa Lit - 8A14L83</t>
         </is>
       </c>
       <c r="C252" s="15" t="inlineStr">
@@ -9719,16 +9675,16 @@
         </is>
       </c>
       <c r="D252" s="16" t="n">
-        <v>999</v>
+        <v>1050</v>
       </c>
       <c r="E252" s="16" t="n">
-        <v>999</v>
+        <v>1050</v>
       </c>
       <c r="F252" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G252" s="18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H252" s="15" t="inlineStr">
         <is>
@@ -9747,7 +9703,7 @@
       <c r="A253" s="9" t="inlineStr"/>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Gris</t>
+          <t>Sofa Lit</t>
         </is>
       </c>
       <c r="C253" s="9" t="inlineStr">
@@ -9756,16 +9712,16 @@
         </is>
       </c>
       <c r="D253" s="10" t="n">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="E253" s="10" t="n">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="F253" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H253" s="9" t="inlineStr">
         <is>
@@ -9784,7 +9740,7 @@
       <c r="A254" s="15" t="inlineStr"/>
       <c r="B254" s="15" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Brun</t>
+          <t>Sofa Lit — Brun</t>
         </is>
       </c>
       <c r="C254" s="15" t="inlineStr">
@@ -9793,16 +9749,16 @@
         </is>
       </c>
       <c r="D254" s="16" t="n">
-        <v>798.99</v>
+        <v>1050</v>
       </c>
       <c r="E254" s="16" t="n">
-        <v>798.99</v>
+        <v>1050</v>
       </c>
       <c r="F254" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G254" s="18" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H254" s="15" t="inlineStr">
         <is>
@@ -9821,7 +9777,7 @@
       <c r="A255" s="9" t="inlineStr"/>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Brun (2)</t>
+          <t>Sofa Lit (2)</t>
         </is>
       </c>
       <c r="C255" s="9" t="inlineStr">
@@ -9830,16 +9786,16 @@
         </is>
       </c>
       <c r="D255" s="10" t="n">
-        <v>798.99</v>
+        <v>1050</v>
       </c>
       <c r="E255" s="10" t="n">
-        <v>798.99</v>
+        <v>1050</v>
       </c>
       <c r="F255" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H255" s="9" t="inlineStr">
         <is>
@@ -9858,25 +9814,29 @@
       <c r="A256" s="15" t="inlineStr"/>
       <c r="B256" s="15" t="inlineStr">
         <is>
-          <t>Amelia-Black — Tables de chevet</t>
+          <t>Sofa Lit — Gris</t>
         </is>
       </c>
       <c r="C256" s="15" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D256" s="16" t="n">
-        <v>370</v>
-      </c>
-      <c r="E256" s="16" t="n"/>
-      <c r="F256" s="17" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E256" s="16" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F256" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G256" s="18" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H256" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I256" s="6" t="n"/>
@@ -9891,25 +9851,29 @@
       <c r="A257" s="9" t="inlineStr"/>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Tables de chevet</t>
+          <t>Sofa-Lit</t>
         </is>
       </c>
       <c r="C257" s="9" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D257" s="10" t="n">
-        <v>370</v>
-      </c>
-      <c r="E257" s="10" t="n"/>
-      <c r="F257" s="11" t="n"/>
+        <v>999</v>
+      </c>
+      <c r="E257" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="F257" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G257" s="12" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I257" s="6" t="n"/>
@@ -9924,25 +9888,29 @@
       <c r="A258" s="15" t="inlineStr"/>
       <c r="B258" s="15" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Tables de chevet</t>
+          <t>Sofa Chaise Longue — Gris</t>
         </is>
       </c>
       <c r="C258" s="15" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D258" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="E258" s="16" t="n"/>
-      <c r="F258" s="17" t="n"/>
+        <v>800</v>
+      </c>
+      <c r="E258" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="F258" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G258" s="18" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H258" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I258" s="6" t="n"/>
@@ -9957,25 +9925,29 @@
       <c r="A259" s="9" t="inlineStr"/>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Tables de chevet</t>
+          <t>Sofa Chaise Longue — Brun</t>
         </is>
       </c>
       <c r="C259" s="9" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D259" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="E259" s="10" t="n"/>
-      <c r="F259" s="11" t="n"/>
+        <v>798.99</v>
+      </c>
+      <c r="E259" s="10" t="n">
+        <v>798.99</v>
+      </c>
+      <c r="F259" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G259" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I259" s="6" t="n"/>
@@ -9990,25 +9962,29 @@
       <c r="A260" s="15" t="inlineStr"/>
       <c r="B260" s="15" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Tables de chevet</t>
+          <t>Sofa Chaise Longue — Brun (2)</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D260" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="E260" s="16" t="n"/>
-      <c r="F260" s="17" t="n"/>
+        <v>798.99</v>
+      </c>
+      <c r="E260" s="16" t="n">
+        <v>798.99</v>
+      </c>
+      <c r="F260" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G260" s="18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H260" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I260" s="6" t="n"/>
@@ -10023,7 +9999,7 @@
       <c r="A261" s="9" t="inlineStr"/>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>Luccia – Table de chevet blanche</t>
+          <t>Amelia-Black — Tables de chevet</t>
         </is>
       </c>
       <c r="C261" s="9" t="inlineStr">
@@ -10032,20 +10008,16 @@
         </is>
       </c>
       <c r="D261" s="10" t="n">
-        <v>270</v>
-      </c>
-      <c r="E261" s="10" t="n">
-        <v>270</v>
-      </c>
-      <c r="F261" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="E261" s="10" t="n"/>
+      <c r="F261" s="11" t="n"/>
       <c r="G261" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I261" s="6" t="n"/>
@@ -10060,7 +10032,7 @@
       <c r="A262" s="15" t="inlineStr"/>
       <c r="B262" s="15" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Tables de chevet</t>
+          <t>Chambre Moderne Blanche — Tables de chevet</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
@@ -10069,12 +10041,12 @@
         </is>
       </c>
       <c r="D262" s="16" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="E262" s="16" t="n"/>
       <c r="F262" s="17" t="n"/>
       <c r="G262" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H262" s="15" t="inlineStr">
         <is>
@@ -10093,7 +10065,7 @@
       <c r="A263" s="9" t="inlineStr"/>
       <c r="B263" s="9" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Tables de chevet</t>
+          <t>Ava Jordyn – Gris — Tables de chevet</t>
         </is>
       </c>
       <c r="C263" s="9" t="inlineStr">
@@ -10102,12 +10074,12 @@
         </is>
       </c>
       <c r="D263" s="10" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="E263" s="10" t="n"/>
       <c r="F263" s="11" t="n"/>
       <c r="G263" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
@@ -10126,7 +10098,7 @@
       <c r="A264" s="15" t="inlineStr"/>
       <c r="B264" s="15" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Tables de chevet</t>
+          <t>Jordyn – Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C264" s="15" t="inlineStr">
@@ -10135,12 +10107,12 @@
         </is>
       </c>
       <c r="D264" s="16" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="E264" s="16" t="n"/>
       <c r="F264" s="17" t="n"/>
       <c r="G264" s="18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H264" s="15" t="inlineStr">
         <is>
@@ -10159,7 +10131,7 @@
       <c r="A265" s="9" t="inlineStr"/>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>Madisson 100 — Tables de chevet</t>
+          <t>Harper "Seville" — Tables de chevet</t>
         </is>
       </c>
       <c r="C265" s="9" t="inlineStr">
@@ -10168,12 +10140,12 @@
         </is>
       </c>
       <c r="D265" s="10" t="n">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="E265" s="10" t="n"/>
       <c r="F265" s="11" t="n"/>
       <c r="G265" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
@@ -10192,7 +10164,7 @@
       <c r="A266" s="15" t="inlineStr"/>
       <c r="B266" s="15" t="inlineStr">
         <is>
-          <t>Olivia “Austin — Tables de chevet</t>
+          <t>Luccia – Table de chevet blanche</t>
         </is>
       </c>
       <c r="C266" s="15" t="inlineStr">
@@ -10201,16 +10173,20 @@
         </is>
       </c>
       <c r="D266" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="E266" s="16" t="n"/>
-      <c r="F266" s="17" t="n"/>
+        <v>270</v>
+      </c>
+      <c r="E266" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="F266" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="G266" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H266" s="15" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I266" s="6" t="n"/>
@@ -10225,7 +10201,7 @@
       <c r="A267" s="9" t="inlineStr"/>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>Dylan — Tables de chevet</t>
+          <t>Lucia — Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C267" s="9" t="inlineStr">
@@ -10234,12 +10210,12 @@
         </is>
       </c>
       <c r="D267" s="10" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="E267" s="10" t="n"/>
       <c r="F267" s="11" t="n"/>
       <c r="G267" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
@@ -10258,7 +10234,7 @@
       <c r="A268" s="15" t="inlineStr"/>
       <c r="B268" s="15" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Tables de chevet</t>
+          <t>Pompéi – Gris métallisé — Tables de chevet</t>
         </is>
       </c>
       <c r="C268" s="15" t="inlineStr">
@@ -10267,12 +10243,12 @@
         </is>
       </c>
       <c r="D268" s="16" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E268" s="16" t="n"/>
       <c r="F268" s="17" t="n"/>
       <c r="G268" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H268" s="15" t="inlineStr">
         <is>
@@ -10291,21 +10267,21 @@
       <c r="A269" s="9" t="inlineStr"/>
       <c r="B269" s="9" t="inlineStr">
         <is>
-          <t>Monaco Dining Set — Tables de salle à manger</t>
+          <t>Luna Riley – Finition argentée — Tables de chevet</t>
         </is>
       </c>
       <c r="C269" s="9" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D269" s="10" t="n">
-        <v>1580</v>
+        <v>220</v>
       </c>
       <c r="E269" s="10" t="n"/>
       <c r="F269" s="11" t="n"/>
       <c r="G269" s="12" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
@@ -10321,28 +10297,24 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="15" t="inlineStr">
-        <is>
-          <t>T-1275</t>
-        </is>
-      </c>
+      <c r="A270" s="15" t="inlineStr"/>
       <c r="B270" s="15" t="inlineStr">
         <is>
-          <t>Gaspé — velours beige — Tables de salle à manger</t>
+          <t>Madisson 100 — Tables de chevet</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D270" s="16" t="n">
-        <v>659.99</v>
+        <v>220</v>
       </c>
       <c r="E270" s="16" t="n"/>
       <c r="F270" s="17" t="n"/>
       <c r="G270" s="18" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H270" s="15" t="inlineStr">
         <is>
@@ -10358,28 +10330,24 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>T-1811 / C-1835</t>
-        </is>
-      </c>
+      <c r="A271" s="9" t="inlineStr"/>
       <c r="B271" s="9" t="inlineStr">
         <is>
-          <t>Drolet — Tables de salle à manger</t>
+          <t>Olivia “Austin — Tables de chevet</t>
         </is>
       </c>
       <c r="C271" s="9" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D271" s="10" t="n">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="E271" s="10" t="n"/>
       <c r="F271" s="11" t="n"/>
       <c r="G271" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
@@ -10395,28 +10363,24 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr">
-        <is>
-          <t>T-1811 / C-1826</t>
-        </is>
-      </c>
+      <c r="A272" s="15" t="inlineStr"/>
       <c r="B272" s="15" t="inlineStr">
         <is>
-          <t>Christophe — Tables de salle à manger</t>
+          <t>Dylan — Tables de chevet</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D272" s="16" t="n">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="E272" s="16" t="n"/>
       <c r="F272" s="17" t="n"/>
       <c r="G272" s="18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H272" s="15" t="inlineStr">
         <is>
@@ -10432,28 +10396,24 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>T-1274</t>
-        </is>
-      </c>
+      <c r="A273" s="9" t="inlineStr"/>
       <c r="B273" s="9" t="inlineStr">
         <is>
-          <t>Casgrain — velours gris — Tables de salle à manger</t>
+          <t>Teddy Bear Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C273" s="9" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D273" s="10" t="n">
-        <v>599.99</v>
+        <v>200</v>
       </c>
       <c r="E273" s="10" t="n"/>
       <c r="F273" s="11" t="n"/>
       <c r="G273" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H273" s="9" t="inlineStr">
         <is>
@@ -10469,14 +10429,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="15" t="inlineStr">
-        <is>
-          <t>T-1274</t>
-        </is>
-      </c>
+      <c r="A274" s="15" t="inlineStr"/>
       <c r="B274" s="15" t="inlineStr">
         <is>
-          <t>Waverly — velours gris — Tables de salle à manger</t>
+          <t>Monaco Dining Set — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
@@ -10485,12 +10441,12 @@
         </is>
       </c>
       <c r="D274" s="16" t="n">
-        <v>599.99</v>
+        <v>1580</v>
       </c>
       <c r="E274" s="16" t="n"/>
       <c r="F274" s="17" t="n"/>
       <c r="G274" s="18" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H274" s="15" t="inlineStr">
         <is>
@@ -10508,12 +10464,12 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>T-1415</t>
+          <t>T-1540</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris — Tables de salle à manger</t>
+          <t>Meuble Chabanel — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C275" s="9" t="inlineStr">
@@ -10522,12 +10478,12 @@
         </is>
       </c>
       <c r="D275" s="10" t="n">
-        <v>449.99</v>
+        <v>1539.98</v>
       </c>
       <c r="E275" s="10" t="n"/>
       <c r="F275" s="11" t="n"/>
       <c r="G275" s="12" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H275" s="9" t="inlineStr">
         <is>
@@ -10545,12 +10501,12 @@
     <row r="276">
       <c r="A276" s="15" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>T-1275</t>
         </is>
       </c>
       <c r="B276" s="15" t="inlineStr">
         <is>
-          <t>Marquette — verre blanc — Tables de salle à manger</t>
+          <t>Gaspé — velours beige — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
@@ -10559,12 +10515,12 @@
         </is>
       </c>
       <c r="D276" s="16" t="n">
-        <v>420</v>
+        <v>1199.98</v>
       </c>
       <c r="E276" s="16" t="n"/>
       <c r="F276" s="17" t="n"/>
       <c r="G276" s="18" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H276" s="15" t="inlineStr">
         <is>
@@ -10582,12 +10538,12 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>T-1449 &amp; C-1712</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
         <is>
-          <t>Saint-Urbain — bois gris — Tables de salle à manger</t>
+          <t>Casgrain — velours gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C277" s="9" t="inlineStr">
@@ -10596,12 +10552,12 @@
         </is>
       </c>
       <c r="D277" s="10" t="n">
-        <v>300</v>
+        <v>1199.98</v>
       </c>
       <c r="E277" s="10" t="n"/>
       <c r="F277" s="11" t="n"/>
       <c r="G277" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H277" s="9" t="inlineStr">
         <is>
@@ -10619,12 +10575,12 @@
     <row r="278">
       <c r="A278" s="15" t="inlineStr">
         <is>
-          <t>T-1079 / C-1084</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B278" s="15" t="inlineStr">
         <is>
-          <t>Gaspé — tissu gris — Tables de salle à manger</t>
+          <t>Waverly — velours gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C278" s="15" t="inlineStr">
@@ -10633,12 +10589,12 @@
         </is>
       </c>
       <c r="D278" s="16" t="n">
-        <v>300</v>
+        <v>1199.98</v>
       </c>
       <c r="E278" s="16" t="n"/>
       <c r="F278" s="17" t="n"/>
       <c r="G278" s="18" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H278" s="15" t="inlineStr">
         <is>
@@ -10656,12 +10612,12 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>T-1402</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris — Tables de salle à manger</t>
+          <t>Meuble Iberville — métal noir — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C279" s="9" t="inlineStr">
@@ -10670,12 +10626,12 @@
         </is>
       </c>
       <c r="D279" s="10" t="n">
-        <v>299.99</v>
+        <v>1099.98</v>
       </c>
       <c r="E279" s="10" t="n"/>
       <c r="F279" s="11" t="n"/>
       <c r="G279" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H279" s="9" t="inlineStr">
         <is>
@@ -10691,32 +10647,32 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="15" t="inlineStr"/>
+      <c r="A280" s="15" t="inlineStr">
+        <is>
+          <t>T-1415</t>
+        </is>
+      </c>
       <c r="B280" s="15" t="inlineStr">
         <is>
-          <t>Ensemble de 2 tables modernes</t>
+          <t>Meuble Boyer — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D280" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="E280" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="F280" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>899.98</v>
+      </c>
+      <c r="E280" s="16" t="n"/>
+      <c r="F280" s="17" t="n"/>
       <c r="G280" s="18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H280" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I280" s="6" t="n"/>
@@ -10730,34 +10686,30 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>IF-3530</t>
+          <t>T-1811 / C-1835</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
         <is>
-          <t>Table basse moderne — Blanc</t>
+          <t>Drolet — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C281" s="9" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D281" s="10" t="n">
-        <v>119.99</v>
-      </c>
-      <c r="E281" s="10" t="n">
-        <v>240</v>
-      </c>
-      <c r="F281" s="11" t="n">
-        <v>-0.5000416666666667</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E281" s="10" t="n"/>
+      <c r="F281" s="11" t="n"/>
       <c r="G281" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I281" s="6" t="n"/>
@@ -10771,34 +10723,30 @@
     <row r="282">
       <c r="A282" s="15" t="inlineStr">
         <is>
-          <t>IF-2631</t>
+          <t>T-1811 / C-1826</t>
         </is>
       </c>
       <c r="B282" s="15" t="inlineStr">
         <is>
-          <t>Table basse</t>
+          <t>Christophe — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D282" s="16" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="E282" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="F282" s="17" t="n">
-        <v>-0.3334</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E282" s="16" t="n"/>
+      <c r="F282" s="17" t="n"/>
       <c r="G282" s="18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H282" s="15" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I282" s="6" t="n"/>
@@ -10812,34 +10760,30 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>IF-3225</t>
+          <t>T-1402</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
         <is>
-          <t>Table basse moderne — Beige</t>
+          <t>Chaise Christophe — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C283" s="9" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D283" s="10" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="E283" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F283" s="11" t="n">
-        <v>-0.3334</v>
-      </c>
+        <v>599.98</v>
+      </c>
+      <c r="E283" s="10" t="n"/>
+      <c r="F283" s="11" t="n"/>
       <c r="G283" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H283" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I283" s="6" t="n"/>
@@ -10851,37 +10795,382 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="15" t="inlineStr"/>
+      <c r="A284" s="15" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B284" s="15" t="inlineStr">
         <is>
-          <t>Vase décoratif circulaire noir – Design moderne</t>
+          <t>Meuble Beaubien — tissu gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C284" s="15" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D284" s="16" t="n">
-        <v>45.99</v>
-      </c>
-      <c r="E284" s="16" t="n">
-        <v>45.99</v>
-      </c>
-      <c r="F284" s="17" t="n">
-        <v>0</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E284" s="16" t="n"/>
+      <c r="F284" s="17" t="n"/>
       <c r="G284" s="18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H284" s="15" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I284" s="6" t="n"/>
       <c r="J284" s="19" t="inlineStr"/>
       <c r="K284" s="20" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>Meuble Papineau — tissu gris — Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="D285" s="10" t="n">
+        <v>439.98</v>
+      </c>
+      <c r="E285" s="10" t="n"/>
+      <c r="F285" s="11" t="n"/>
+      <c r="G285" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H285" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
+        </is>
+      </c>
+      <c r="I285" s="6" t="n"/>
+      <c r="J285" s="13" t="inlineStr"/>
+      <c r="K285" s="14" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="15" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
+      <c r="B286" s="15" t="inlineStr">
+        <is>
+          <t>Meuble Fabre — velours beige — Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="C286" s="15" t="inlineStr">
+        <is>
+          <t>Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="D286" s="16" t="n">
+        <v>439.98</v>
+      </c>
+      <c r="E286" s="16" t="n"/>
+      <c r="F286" s="17" t="n"/>
+      <c r="G286" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H286" s="15" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
+        </is>
+      </c>
+      <c r="I286" s="6" t="n"/>
+      <c r="J286" s="19" t="inlineStr"/>
+      <c r="K286" s="20" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>T-1442 / C-1878</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="inlineStr">
+        <is>
+          <t>Marquette — verre blanc — Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="D287" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="E287" s="10" t="n"/>
+      <c r="F287" s="11" t="n"/>
+      <c r="G287" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H287" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
+        </is>
+      </c>
+      <c r="I287" s="6" t="n"/>
+      <c r="J287" s="13" t="inlineStr"/>
+      <c r="K287" s="14" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="inlineStr">
+        <is>
+          <t>T-1449 &amp; C-1712</t>
+        </is>
+      </c>
+      <c r="B288" s="15" t="inlineStr">
+        <is>
+          <t>Saint-Urbain — bois gris — Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="C288" s="15" t="inlineStr">
+        <is>
+          <t>Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="D288" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="E288" s="16" t="n"/>
+      <c r="F288" s="17" t="n"/>
+      <c r="G288" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H288" s="15" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
+        </is>
+      </c>
+      <c r="I288" s="6" t="n"/>
+      <c r="J288" s="19" t="inlineStr"/>
+      <c r="K288" s="20" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>T-1079 / C-1084</t>
+        </is>
+      </c>
+      <c r="B289" s="9" t="inlineStr">
+        <is>
+          <t>Gaspé — tissu gris — Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>Tables de salle à manger</t>
+        </is>
+      </c>
+      <c r="D289" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E289" s="10" t="n"/>
+      <c r="F289" s="11" t="n"/>
+      <c r="G289" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H289" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
+        </is>
+      </c>
+      <c r="I289" s="6" t="n"/>
+      <c r="J289" s="13" t="inlineStr"/>
+      <c r="K289" s="14" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>IF-3530</t>
+        </is>
+      </c>
+      <c r="B290" s="15" t="inlineStr">
+        <is>
+          <t>Table basse moderne — Blanc</t>
+        </is>
+      </c>
+      <c r="C290" s="15" t="inlineStr">
+        <is>
+          <t>Tables de salon</t>
+        </is>
+      </c>
+      <c r="D290" s="16" t="n">
+        <v>239.98</v>
+      </c>
+      <c r="E290" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="F290" s="17" t="n">
+        <v>-8.333333333337597e-05</v>
+      </c>
+      <c r="G290" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H290" s="15" t="inlineStr">
+        <is>
+          <t>Liste du fournisseur</t>
+        </is>
+      </c>
+      <c r="I290" s="6" t="n"/>
+      <c r="J290" s="19" t="inlineStr"/>
+      <c r="K290" s="20" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr"/>
+      <c r="B291" s="9" t="inlineStr">
+        <is>
+          <t>Ensemble de 2 tables modernes</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>Tables de salon</t>
+        </is>
+      </c>
+      <c r="D291" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E291" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F291" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H291" s="9" t="inlineStr">
+        <is>
+          <t>Prix boutique actuel</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="n"/>
+      <c r="J291" s="13" t="inlineStr"/>
+      <c r="K291" s="14" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="inlineStr">
+        <is>
+          <t>IF-2631</t>
+        </is>
+      </c>
+      <c r="B292" s="15" t="inlineStr">
+        <is>
+          <t>Table basse</t>
+        </is>
+      </c>
+      <c r="C292" s="15" t="inlineStr">
+        <is>
+          <t>Tables de salon</t>
+        </is>
+      </c>
+      <c r="D292" s="16" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="E292" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="F292" s="17" t="n">
+        <v>0.3331999999999999</v>
+      </c>
+      <c r="G292" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H292" s="15" t="inlineStr">
+        <is>
+          <t>Liste du fournisseur</t>
+        </is>
+      </c>
+      <c r="I292" s="6" t="n"/>
+      <c r="J292" s="19" t="inlineStr"/>
+      <c r="K292" s="20" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>IF-3225</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr">
+        <is>
+          <t>Table basse moderne — Beige</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>Tables de salon</t>
+        </is>
+      </c>
+      <c r="D293" s="10" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="E293" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="F293" s="11" t="n">
+        <v>0.3331999999999999</v>
+      </c>
+      <c r="G293" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H293" s="9" t="inlineStr">
+        <is>
+          <t>Liste du fournisseur</t>
+        </is>
+      </c>
+      <c r="I293" s="6" t="n"/>
+      <c r="J293" s="13" t="inlineStr"/>
+      <c r="K293" s="14" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -11172,6 +11461,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K283" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11202,7 +11500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>283 produits. Les lignes surlignées demandent une vérification.</t>
+          <t>292 produits. Les lignes surlignées demandent une vérification.</t>
         </is>
       </c>
     </row>

--- a/web/exports/revision-prix.xlsx
+++ b/web/exports/revision-prix.xlsx
@@ -46,7 +46,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,17 +60,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE9E3"/>
+        <fgColor rgb="00FAFAF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFAF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -113,14 +108,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -564,21 +551,21 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Zénith — Canapé</t>
+          <t>Teddy Bear Blanc — Banc</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Canapés</t>
+          <t>Bancs</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -586,11 +573,7 @@
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>0.11× la médiane de « Canapés » (1 770 $) ; moins cher que le causeuse du même ensemble (1 500 $)</t>
-        </is>
-      </c>
+      <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
@@ -601,25 +584,29 @@
       <c r="A3" s="9" t="inlineStr"/>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Banc</t>
+          <t>Bureau Outremont — métal noir</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Bancs</t>
+          <t>Bureaux</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>360</v>
-      </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="11" t="n"/>
+        <v>700</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>700</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I3" s="6" t="n"/>
@@ -631,37 +618,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Bureau Outremont — métal noir</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Bureau - 70"</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Bureaux</t>
         </is>
       </c>
-      <c r="D4" s="16" t="n">
-        <v>700</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>700</v>
-      </c>
-      <c r="F4" s="17" t="n">
+      <c r="D4" s="3" t="n">
+        <v>510</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>510</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="G4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I4" s="6" t="n"/>
-      <c r="J4" s="19" t="inlineStr"/>
-      <c r="K4" s="20" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -671,7 +658,7 @@
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Bureau - 70"</t>
+          <t>Bureau — Gris</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -680,16 +667,16 @@
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
@@ -705,37 +692,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr"/>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Bureau — Gris</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Bureau — Gris (2)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Bureaux</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="19" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -745,7 +732,7 @@
       <c r="A7" s="9" t="inlineStr"/>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Bureau — Gris (2)</t>
+          <t>Bureau De Coin Cote Droit Ou Gauche</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -754,16 +741,16 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -779,37 +766,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr"/>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Bureau De Coin Cote Droit Ou Gauche</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bureau Christophe — bois gris</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Bureaux</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>449</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>449</v>
-      </c>
-      <c r="F8" s="17" t="n">
+      <c r="D8" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="19" t="inlineStr"/>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -819,7 +806,7 @@
       <c r="A9" s="9" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Bureau Christophe — bois gris</t>
+          <t>Bureau - 42" L</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -828,16 +815,16 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -853,37 +840,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr"/>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Bureau - 42" L</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Bureaux</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>Prix boutique actuel</t>
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ATlas — Canapé</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Canapés</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2140</v>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="19" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -893,7 +876,7 @@
       <c r="A11" s="9" t="inlineStr"/>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>ATlas — Canapé</t>
+          <t>Nexus — Canapé</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -902,12 +885,12 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>2140</v>
+        <v>2000</v>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -923,47 +906,51 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr"/>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Nexus — Canapé</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IF-8030</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(Fabric-Power)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="18" t="n">
+      <c r="D12" s="3" t="n">
+        <v>1999.98</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="19" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>IF-8030</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>(Fabric-Power)</t>
+          <t>Elite — Canapé</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -972,20 +959,16 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>1999.98</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0.99998</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
       <c r="G13" s="12" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -997,33 +980,33 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr"/>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Elite — Canapé</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Royal — Canapé</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="18" t="n">
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="19" t="inlineStr"/>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1033,7 +1016,7 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Royal — Canapé</t>
+          <t>Véga — Canapé</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1063,33 +1046,33 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Véga — Canapé</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Opéra — Canapé</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="18" t="n">
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1099,7 +1082,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Opéra — Canapé</t>
+          <t>Skyline — Canapé</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1129,33 +1112,33 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr"/>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Skyline — Canapé</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Zénith — Canapé</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="18" t="n">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="19" t="inlineStr"/>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1195,33 +1178,33 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Nuvola — Canapé</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="18" t="n">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="19" t="inlineStr"/>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1261,33 +1244,33 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr"/>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Nexo — Canapé</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="18" t="n">
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="19" t="inlineStr"/>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1327,37 +1310,37 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>IF 8120</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Canapé Casgrain — cuir noir — Canapé</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="18" t="n">
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I24" s="6" t="n"/>
-      <c r="J24" s="19" t="inlineStr"/>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1397,33 +1380,33 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr"/>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Depot — Canapé</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="3" t="n">
         <v>860</v>
       </c>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="18" t="n">
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I26" s="6" t="n"/>
-      <c r="J26" s="19" t="inlineStr"/>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1463,37 +1446,37 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>IF-8007</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Canapé Christophe — velours noir — Canapé</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Canapés</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="18" t="n">
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I28" s="6" t="n"/>
-      <c r="J28" s="19" t="inlineStr"/>
-      <c r="K28" s="20" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1537,33 +1520,33 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr"/>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Prestige — Causeuse</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="18" t="n">
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="H30" s="15" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I30" s="6" t="n"/>
-      <c r="J30" s="19" t="inlineStr"/>
-      <c r="K30" s="20" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1603,33 +1586,33 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr"/>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Royal — Causeuse</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="17" t="n"/>
-      <c r="G32" s="18" t="n">
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H32" s="15" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I32" s="6" t="n"/>
-      <c r="J32" s="19" t="inlineStr"/>
-      <c r="K32" s="20" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1669,33 +1652,33 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr"/>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Opéra — Causeuse</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="18" t="n">
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H34" s="15" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I34" s="6" t="n"/>
-      <c r="J34" s="19" t="inlineStr"/>
-      <c r="K34" s="20" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1735,33 +1718,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr"/>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Nuvola — Causeuse</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="18" t="n">
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I36" s="6" t="n"/>
-      <c r="J36" s="19" t="inlineStr"/>
-      <c r="K36" s="20" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1801,33 +1784,33 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr"/>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Nexus — Causeuse</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="18" t="n">
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I38" s="6" t="n"/>
-      <c r="J38" s="19" t="inlineStr"/>
-      <c r="K38" s="20" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1867,33 +1850,33 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr"/>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Zénith — Causeuse</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="18" t="n">
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I40" s="6" t="n"/>
-      <c r="J40" s="19" t="inlineStr"/>
-      <c r="K40" s="20" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1933,33 +1916,33 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr"/>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Nexo — Causeuse</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="3" t="n">
         <v>760</v>
       </c>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="18" t="n">
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I42" s="6" t="n"/>
-      <c r="J42" s="19" t="inlineStr"/>
-      <c r="K42" s="20" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -1999,37 +1982,37 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>IF-8007</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Canapé Christophe — velours noir — Causeuse</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="18" t="n">
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H44" s="15" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I44" s="6" t="n"/>
-      <c r="J44" s="19" t="inlineStr"/>
-      <c r="K44" s="20" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2069,33 +2052,33 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr"/>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Clarence — Causeuse</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="3" t="n">
         <v>660</v>
       </c>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="18" t="n">
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H46" s="15" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I46" s="6" t="n"/>
-      <c r="J46" s="19" t="inlineStr"/>
-      <c r="K46" s="20" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2135,37 +2118,37 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>IF-8012</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Canapé Chabanel — cuir beige — Causeuse</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Causeuses</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="3" t="n">
         <v>459.98</v>
       </c>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="18" t="n">
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H48" s="15" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I48" s="6" t="n"/>
-      <c r="J48" s="19" t="inlineStr"/>
-      <c r="K48" s="20" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2205,41 +2188,41 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C-1285</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Chaise Casgrain — velours beige</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="F50" s="17" t="n">
+      <c r="F50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="18" t="n">
+      <c r="G50" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I50" s="6" t="n"/>
-      <c r="J50" s="19" t="inlineStr"/>
-      <c r="K50" s="20" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2287,41 +2270,41 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C-1263</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Chaise cadre chrome poli</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="F52" s="17" t="n">
+      <c r="F52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="G52" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H52" s="15" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I52" s="6" t="n"/>
-      <c r="J52" s="19" t="inlineStr"/>
-      <c r="K52" s="20" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2365,37 +2348,37 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>T-1274</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Casgrain — velours gris — Chaise</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="17" t="n"/>
-      <c r="G54" s="18" t="n">
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H54" s="15" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I54" s="6" t="n"/>
-      <c r="J54" s="19" t="inlineStr"/>
-      <c r="K54" s="20" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr"/>
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2439,33 +2422,33 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr"/>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Monaco Dining Set — Chaise</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="17" t="n"/>
-      <c r="G56" s="18" t="n">
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H56" s="15" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I56" s="6" t="n"/>
-      <c r="J56" s="19" t="inlineStr"/>
-      <c r="K56" s="20" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2509,37 +2492,37 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="inlineStr"/>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Chaise avec pattes chromées</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="F58" s="17" t="n">
+      <c r="F58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="18" t="n">
+      <c r="G58" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I58" s="6" t="n"/>
-      <c r="J58" s="19" t="inlineStr"/>
-      <c r="K58" s="20" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2583,41 +2566,41 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C-1546</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Chaise moderne</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D60" s="16" t="n">
+      <c r="D60" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E60" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="F60" s="17" t="n">
+      <c r="F60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="18" t="n">
+      <c r="G60" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="15" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I60" s="6" t="n"/>
-      <c r="J60" s="19" t="inlineStr"/>
-      <c r="K60" s="20" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2661,37 +2644,37 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>T-1811 / C-1835</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Drolet — Chaise</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D62" s="16" t="n">
+      <c r="D62" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="17" t="n"/>
-      <c r="G62" s="18" t="n">
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="15" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I62" s="6" t="n"/>
-      <c r="J62" s="19" t="inlineStr"/>
-      <c r="K62" s="20" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2735,41 +2718,41 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C-1416</t>
         </is>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Chaise moderne en PU</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D64" s="16" t="n">
+      <c r="D64" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E64" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="F64" s="17" t="n">
+      <c r="F64" s="4" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="G64" s="18" t="n">
+      <c r="G64" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="15" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I64" s="6" t="n"/>
-      <c r="J64" s="19" t="inlineStr"/>
-      <c r="K64" s="20" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2813,41 +2796,41 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C-1541</t>
         </is>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Chaise moderne en PU gris</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D66" s="16" t="n">
+      <c r="D66" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E66" s="16" t="n">
+      <c r="E66" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="F66" s="17" t="n">
+      <c r="F66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="18" t="n">
+      <c r="G66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H66" s="15" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I66" s="6" t="n"/>
-      <c r="J66" s="19" t="inlineStr"/>
-      <c r="K66" s="20" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2891,37 +2874,37 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>T-1510</t>
         </is>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Meuble Papineau — tissu gris — Chaise</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D68" s="16" t="n">
+      <c r="D68" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="17" t="n"/>
-      <c r="G68" s="18" t="n">
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H68" s="15" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I68" s="6" t="n"/>
-      <c r="J68" s="19" t="inlineStr"/>
-      <c r="K68" s="20" t="inlineStr">
+      <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -2965,37 +2948,37 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="15" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>T-1540</t>
         </is>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Meuble Chabanel — métal gris — Chaise</t>
         </is>
       </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="17" t="n"/>
-      <c r="G70" s="18" t="n">
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H70" s="15" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I70" s="6" t="n"/>
-      <c r="J70" s="19" t="inlineStr"/>
-      <c r="K70" s="20" t="inlineStr">
+      <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3039,37 +3022,37 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>T-1442 / C-1878</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Marquette — verre blanc — Chaise</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Chaises</t>
         </is>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="17" t="n"/>
-      <c r="G72" s="18" t="n">
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="15" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I72" s="6" t="n"/>
-      <c r="J72" s="19" t="inlineStr"/>
-      <c r="K72" s="20" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3113,37 +3096,37 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="15" t="inlineStr"/>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>New York D/M – Commode avec miroir</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D74" s="16" t="n">
+      <c r="D74" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="E74" s="16" t="n">
+      <c r="E74" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="F74" s="17" t="n">
+      <c r="F74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="18" t="n">
+      <c r="G74" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="H74" s="15" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I74" s="6" t="n"/>
-      <c r="J74" s="19" t="inlineStr"/>
-      <c r="K74" s="20" t="inlineStr">
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3183,33 +3166,33 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="15" t="inlineStr"/>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Chambre Moderne Blanche — Commode</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E76" s="16" t="n"/>
-      <c r="F76" s="17" t="n"/>
-      <c r="G76" s="18" t="n">
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="H76" s="15" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I76" s="6" t="n"/>
-      <c r="J76" s="19" t="inlineStr"/>
-      <c r="K76" s="20" t="inlineStr">
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3249,33 +3232,33 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="15" t="inlineStr"/>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Jordyn – Blanc — Commode</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D78" s="16" t="n">
+      <c r="D78" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E78" s="16" t="n"/>
-      <c r="F78" s="17" t="n"/>
-      <c r="G78" s="18" t="n">
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="H78" s="15" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I78" s="6" t="n"/>
-      <c r="J78" s="19" t="inlineStr"/>
-      <c r="K78" s="20" t="inlineStr">
+      <c r="J78" s="7" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3315,33 +3298,33 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="15" t="inlineStr"/>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Madisson 100 — Commode</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D80" s="16" t="n">
+      <c r="D80" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E80" s="16" t="n"/>
-      <c r="F80" s="17" t="n"/>
-      <c r="G80" s="18" t="n">
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="H80" s="15" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I80" s="6" t="n"/>
-      <c r="J80" s="19" t="inlineStr"/>
-      <c r="K80" s="20" t="inlineStr">
+      <c r="J80" s="7" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3381,33 +3364,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="inlineStr"/>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Pompéi – Gris métallisé — Commode</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D82" s="16" t="n">
+      <c r="D82" s="3" t="n">
         <v>530</v>
       </c>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="17" t="n"/>
-      <c r="G82" s="18" t="n">
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H82" s="15" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I82" s="6" t="n"/>
-      <c r="J82" s="19" t="inlineStr"/>
-      <c r="K82" s="20" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3447,33 +3430,33 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="inlineStr"/>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Luna Riley – Finition argentée — Commode</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Commodes</t>
         </is>
       </c>
-      <c r="D84" s="16" t="n">
+      <c r="D84" s="3" t="n">
         <v>460</v>
       </c>
-      <c r="E84" s="16" t="n"/>
-      <c r="F84" s="17" t="n"/>
-      <c r="G84" s="18" t="n">
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H84" s="15" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I84" s="6" t="n"/>
-      <c r="J84" s="19" t="inlineStr"/>
-      <c r="K84" s="20" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3513,41 +3496,41 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="15" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>T-1442</t>
         </is>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Meuble Cartier — verre gris</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Décoration</t>
         </is>
       </c>
-      <c r="D86" s="16" t="n">
+      <c r="D86" s="3" t="n">
         <v>999.98</v>
       </c>
-      <c r="E86" s="16" t="n">
+      <c r="E86" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F86" s="17" t="n">
+      <c r="F86" s="4" t="n">
         <v>-1.999999999998181e-05</v>
       </c>
-      <c r="G86" s="18" t="n">
+      <c r="G86" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="H86" s="15" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I86" s="6" t="n"/>
-      <c r="J86" s="19" t="inlineStr"/>
-      <c r="K86" s="20" t="inlineStr">
+      <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3591,37 +3574,37 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="inlineStr"/>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Chambre Moderne Blanche</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D88" s="16" t="n">
+      <c r="D88" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="E88" s="16" t="n">
+      <c r="E88" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="F88" s="17" t="n">
+      <c r="F88" s="4" t="n">
         <v>12.51351351351351</v>
       </c>
-      <c r="G88" s="18" t="n">
+      <c r="G88" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="H88" s="15" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
-      <c r="J88" s="19" t="inlineStr"/>
-      <c r="K88" s="20" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3665,37 +3648,37 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr"/>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Jordyn – Blanc</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D90" s="16" t="n">
+      <c r="D90" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="E90" s="16" t="n">
+      <c r="E90" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="F90" s="17" t="n">
+      <c r="F90" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G90" s="18" t="n">
+      <c r="G90" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H90" s="15" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I90" s="6" t="n"/>
-      <c r="J90" s="19" t="inlineStr"/>
-      <c r="K90" s="20" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3739,37 +3722,37 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="inlineStr"/>
-      <c r="B92" s="15" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Amelia-Black</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D92" s="16" t="n">
+      <c r="D92" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="E92" s="16" t="n">
+      <c r="E92" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="F92" s="17" t="n">
+      <c r="F92" s="4" t="n">
         <v>7.108108108108108</v>
       </c>
-      <c r="G92" s="18" t="n">
+      <c r="G92" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="H92" s="15" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I92" s="6" t="n"/>
-      <c r="J92" s="19" t="inlineStr"/>
-      <c r="K92" s="20" t="inlineStr">
+      <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3813,37 +3796,37 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr"/>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Madisson 100</t>
         </is>
       </c>
-      <c r="C94" s="15" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D94" s="16" t="n">
+      <c r="D94" s="3" t="n">
         <v>2299.98</v>
       </c>
-      <c r="E94" s="16" t="n">
+      <c r="E94" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="F94" s="17" t="n">
+      <c r="F94" s="4" t="n">
         <v>9.454454545454546</v>
       </c>
-      <c r="G94" s="18" t="n">
+      <c r="G94" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="H94" s="15" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I94" s="6" t="n"/>
-      <c r="J94" s="19" t="inlineStr"/>
-      <c r="K94" s="20" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3887,37 +3870,37 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="15" t="inlineStr"/>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Harper "Seville"</t>
         </is>
       </c>
-      <c r="C96" s="15" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D96" s="16" t="n">
+      <c r="D96" s="3" t="n">
         <v>2015</v>
       </c>
-      <c r="E96" s="16" t="n">
+      <c r="E96" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="F96" s="17" t="n">
+      <c r="F96" s="4" t="n">
         <v>6.070175438596491</v>
       </c>
-      <c r="G96" s="18" t="n">
+      <c r="G96" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="H96" s="15" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I96" s="6" t="n"/>
-      <c r="J96" s="19" t="inlineStr"/>
-      <c r="K96" s="20" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -3961,37 +3944,37 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="inlineStr"/>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Olivia “Austin</t>
         </is>
       </c>
-      <c r="C98" s="15" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D98" s="16" t="n">
+      <c r="D98" s="3" t="n">
         <v>1920</v>
       </c>
-      <c r="E98" s="16" t="n">
+      <c r="E98" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="F98" s="17" t="n">
+      <c r="F98" s="4" t="n">
         <v>8.142857142857142</v>
       </c>
-      <c r="G98" s="18" t="n">
+      <c r="G98" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="H98" s="15" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I98" s="6" t="n"/>
-      <c r="J98" s="19" t="inlineStr"/>
-      <c r="K98" s="20" t="inlineStr">
+      <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4035,37 +4018,37 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="15" t="inlineStr"/>
-      <c r="B100" s="15" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Lit Queen avec Rangement</t>
         </is>
       </c>
-      <c r="C100" s="15" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D100" s="16" t="n">
+      <c r="D100" s="3" t="n">
         <v>1828</v>
       </c>
-      <c r="E100" s="16" t="n">
+      <c r="E100" s="3" t="n">
         <v>1828</v>
       </c>
-      <c r="F100" s="17" t="n">
+      <c r="F100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="18" t="n">
+      <c r="G100" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H100" s="15" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I100" s="6" t="n"/>
-      <c r="J100" s="19" t="inlineStr"/>
-      <c r="K100" s="20" t="inlineStr">
+      <c r="J100" s="7" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4109,41 +4092,41 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>I-5230Q</t>
         </is>
       </c>
-      <c r="B102" s="15" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Ensemble Chambre</t>
         </is>
       </c>
-      <c r="C102" s="15" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D102" s="16" t="n">
+      <c r="D102" s="3" t="n">
         <v>1608</v>
       </c>
-      <c r="E102" s="16" t="n">
+      <c r="E102" s="3" t="n">
         <v>1608</v>
       </c>
-      <c r="F102" s="17" t="n">
+      <c r="F102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="18" t="n">
+      <c r="G102" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="H102" s="15" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I102" s="6" t="n"/>
-      <c r="J102" s="19" t="inlineStr"/>
-      <c r="K102" s="20" t="inlineStr">
+      <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4187,33 +4170,33 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="inlineStr"/>
-      <c r="B104" s="15" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Lucia — Blanc</t>
         </is>
       </c>
-      <c r="C104" s="15" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Ensembles de chambre</t>
         </is>
       </c>
-      <c r="D104" s="16" t="n">
+      <c r="D104" s="3" t="n">
         <v>1299</v>
       </c>
-      <c r="E104" s="16" t="n"/>
-      <c r="F104" s="17" t="n"/>
-      <c r="G104" s="18" t="n">
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H104" s="15" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I104" s="6" t="n"/>
-      <c r="J104" s="19" t="inlineStr"/>
-      <c r="K104" s="20" t="inlineStr">
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4257,37 +4240,37 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="15" t="inlineStr"/>
-      <c r="B106" s="15" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Monaco Dining Set</t>
         </is>
       </c>
-      <c r="C106" s="15" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D106" s="16" t="n">
+      <c r="D106" s="3" t="n">
         <v>2999.98</v>
       </c>
-      <c r="E106" s="16" t="n">
+      <c r="E106" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="F106" s="17" t="n">
+      <c r="F106" s="4" t="n">
         <v>10.11103703703704</v>
       </c>
-      <c r="G106" s="18" t="n">
+      <c r="G106" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="H106" s="15" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I106" s="6" t="n"/>
-      <c r="J106" s="19" t="inlineStr"/>
-      <c r="K106" s="20" t="inlineStr">
+      <c r="J106" s="7" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4331,37 +4314,37 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="15" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>T-1274</t>
         </is>
       </c>
-      <c r="B108" s="15" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Ensemble de salle à manger Waverly — velours gris</t>
         </is>
       </c>
-      <c r="C108" s="15" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D108" s="16" t="n">
+      <c r="D108" s="3" t="n">
         <v>2939.98</v>
       </c>
-      <c r="E108" s="16" t="n"/>
-      <c r="F108" s="17" t="n"/>
-      <c r="G108" s="18" t="n">
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="H108" s="15" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I108" s="6" t="n"/>
-      <c r="J108" s="19" t="inlineStr"/>
-      <c r="K108" s="20" t="inlineStr">
+      <c r="J108" s="7" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4409,37 +4392,37 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="15" t="inlineStr"/>
-      <c r="B110" s="15" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Table A Manger - Noyer Brun</t>
         </is>
       </c>
-      <c r="C110" s="15" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D110" s="16" t="n">
+      <c r="D110" s="3" t="n">
         <v>1899.99</v>
       </c>
-      <c r="E110" s="16" t="n">
+      <c r="E110" s="3" t="n">
         <v>1899.99</v>
       </c>
-      <c r="F110" s="17" t="n">
+      <c r="F110" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="18" t="n">
+      <c r="G110" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="H110" s="15" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I110" s="6" t="n"/>
-      <c r="J110" s="19" t="inlineStr"/>
-      <c r="K110" s="20" t="inlineStr">
+      <c r="J110" s="7" t="inlineStr"/>
+      <c r="K110" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4483,37 +4466,37 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="15" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>T-1540</t>
         </is>
       </c>
-      <c r="B112" s="15" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Meuble Chabanel — métal gris</t>
         </is>
       </c>
-      <c r="C112" s="15" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D112" s="16" t="n">
+      <c r="D112" s="3" t="n">
         <v>1539.98</v>
       </c>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="17" t="n"/>
-      <c r="G112" s="18" t="n">
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="H112" s="15" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I112" s="6" t="n"/>
-      <c r="J112" s="19" t="inlineStr"/>
-      <c r="K112" s="20" t="inlineStr">
+      <c r="J112" s="7" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4557,41 +4540,41 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="15" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>T-1811 / C-1835</t>
         </is>
       </c>
-      <c r="B114" s="15" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Ensemble de salle à manger Drolet</t>
         </is>
       </c>
-      <c r="C114" s="15" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D114" s="16" t="n">
+      <c r="D114" s="3" t="n">
         <v>1280</v>
       </c>
-      <c r="E114" s="16" t="n">
+      <c r="E114" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="F114" s="17" t="n">
+      <c r="F114" s="4" t="n">
         <v>6.529411764705882</v>
       </c>
-      <c r="G114" s="18" t="n">
+      <c r="G114" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H114" s="15" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I114" s="6" t="n"/>
-      <c r="J114" s="19" t="inlineStr"/>
-      <c r="K114" s="20" t="inlineStr">
+      <c r="J114" s="7" t="inlineStr"/>
+      <c r="K114" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4639,37 +4622,37 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>T-1545</t>
         </is>
       </c>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Meuble Iberville — métal noir</t>
         </is>
       </c>
-      <c r="C116" s="15" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D116" s="16" t="n">
+      <c r="D116" s="3" t="n">
         <v>1099.98</v>
       </c>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="17" t="n"/>
-      <c r="G116" s="18" t="n">
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="H116" s="15" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I116" s="6" t="n"/>
-      <c r="J116" s="19" t="inlineStr"/>
-      <c r="K116" s="20" t="inlineStr">
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4713,41 +4696,41 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="15" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>T-1448</t>
         </is>
       </c>
-      <c r="B118" s="15" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Meuble Lachine — verre beige</t>
         </is>
       </c>
-      <c r="C118" s="15" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D118" s="16" t="n">
+      <c r="D118" s="3" t="n">
         <v>939.98</v>
       </c>
-      <c r="E118" s="16" t="n">
+      <c r="E118" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F118" s="17" t="n">
+      <c r="F118" s="4" t="n">
         <v>-0.5480865384615384</v>
       </c>
-      <c r="G118" s="18" t="n">
+      <c r="G118" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="H118" s="15" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I118" s="6" t="n"/>
-      <c r="J118" s="19" t="inlineStr"/>
-      <c r="K118" s="20" t="inlineStr">
+      <c r="J118" s="7" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4791,37 +4774,37 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="15" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>T-1079 / C-1084</t>
         </is>
       </c>
-      <c r="B120" s="15" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Ensemble de salle à manger Gaspé — tissu gris</t>
         </is>
       </c>
-      <c r="C120" s="15" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D120" s="16" t="n">
+      <c r="D120" s="3" t="n">
         <v>660</v>
       </c>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="17" t="n"/>
-      <c r="G120" s="18" t="n">
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H120" s="15" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I120" s="6" t="n"/>
-      <c r="J120" s="19" t="inlineStr"/>
-      <c r="K120" s="20" t="inlineStr">
+      <c r="J120" s="7" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4865,37 +4848,37 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>T-1510</t>
         </is>
       </c>
-      <c r="B122" s="15" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Meuble Papineau — tissu gris</t>
         </is>
       </c>
-      <c r="C122" s="15" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D122" s="16" t="n">
+      <c r="D122" s="3" t="n">
         <v>439.98</v>
       </c>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="17" t="n"/>
-      <c r="G122" s="18" t="n">
+      <c r="E122" s="3" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H122" s="15" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I122" s="6" t="n"/>
-      <c r="J122" s="19" t="inlineStr"/>
-      <c r="K122" s="20" t="inlineStr">
+      <c r="J122" s="7" t="inlineStr"/>
+      <c r="K122" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -4939,41 +4922,41 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="15" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>IF-1056</t>
         </is>
       </c>
-      <c r="B124" s="15" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Ensemble salle à manger 5 pièces</t>
         </is>
       </c>
-      <c r="C124" s="15" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D124" s="16" t="n">
+      <c r="D124" s="3" t="n">
         <v>399.98</v>
       </c>
-      <c r="E124" s="16" t="n">
+      <c r="E124" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="F124" s="17" t="n">
+      <c r="F124" s="4" t="n">
         <v>0.1428000000000001</v>
       </c>
-      <c r="G124" s="18" t="n">
+      <c r="G124" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H124" s="15" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I124" s="6" t="n"/>
-      <c r="J124" s="19" t="inlineStr"/>
-      <c r="K124" s="20" t="inlineStr">
+      <c r="J124" s="7" t="inlineStr"/>
+      <c r="K124" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5017,37 +5000,37 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="15" t="inlineStr"/>
-      <c r="B126" s="15" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Table et 4 chaises (2)</t>
         </is>
       </c>
-      <c r="C126" s="15" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salle à manger</t>
         </is>
       </c>
-      <c r="D126" s="16" t="n">
+      <c r="D126" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="E126" s="16" t="n">
+      <c r="E126" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="F126" s="17" t="n">
+      <c r="F126" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="18" t="n">
+      <c r="G126" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H126" s="15" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I126" s="6" t="n"/>
-      <c r="J126" s="19" t="inlineStr"/>
-      <c r="K126" s="20" t="inlineStr">
+      <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5091,37 +5074,37 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="15" t="inlineStr"/>
-      <c r="B128" s="15" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr"/>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Royal</t>
         </is>
       </c>
-      <c r="C128" s="15" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D128" s="16" t="n">
+      <c r="D128" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="E128" s="16" t="n">
+      <c r="E128" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F128" s="17" t="n">
+      <c r="F128" s="4" t="n">
         <v>3.666666666666667</v>
       </c>
-      <c r="G128" s="18" t="n">
+      <c r="G128" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H128" s="15" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I128" s="6" t="n"/>
-      <c r="J128" s="19" t="inlineStr"/>
-      <c r="K128" s="20" t="inlineStr">
+      <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5165,37 +5148,37 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="15" t="inlineStr"/>
-      <c r="B130" s="15" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr"/>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Nexus</t>
         </is>
       </c>
-      <c r="C130" s="15" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D130" s="16" t="n">
+      <c r="D130" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="E130" s="16" t="n">
+      <c r="E130" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F130" s="17" t="n">
+      <c r="F130" s="4" t="n">
         <v>3.666666666666667</v>
       </c>
-      <c r="G130" s="18" t="n">
+      <c r="G130" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H130" s="15" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I130" s="6" t="n"/>
-      <c r="J130" s="19" t="inlineStr"/>
-      <c r="K130" s="20" t="inlineStr">
+      <c r="J130" s="7" t="inlineStr"/>
+      <c r="K130" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5239,37 +5222,37 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="15" t="inlineStr"/>
-      <c r="B132" s="15" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr"/>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Sérénity</t>
         </is>
       </c>
-      <c r="C132" s="15" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D132" s="16" t="n">
+      <c r="D132" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="E132" s="16" t="n">
+      <c r="E132" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F132" s="17" t="n">
+      <c r="F132" s="4" t="n">
         <v>3.666666666666667</v>
       </c>
-      <c r="G132" s="18" t="n">
+      <c r="G132" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H132" s="15" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I132" s="6" t="n"/>
-      <c r="J132" s="19" t="inlineStr"/>
-      <c r="K132" s="20" t="inlineStr">
+      <c r="J132" s="7" t="inlineStr"/>
+      <c r="K132" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5313,37 +5296,37 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="15" t="inlineStr"/>
-      <c r="B134" s="15" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C134" s="15" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D134" s="16" t="n">
+      <c r="D134" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="E134" s="16" t="n">
+      <c r="E134" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F134" s="17" t="n">
+      <c r="F134" s="4" t="n">
         <v>3.444444444444445</v>
       </c>
-      <c r="G134" s="18" t="n">
+      <c r="G134" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="H134" s="15" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I134" s="6" t="n"/>
-      <c r="J134" s="19" t="inlineStr"/>
-      <c r="K134" s="20" t="inlineStr">
+      <c r="J134" s="7" t="inlineStr"/>
+      <c r="K134" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5387,37 +5370,37 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="15" t="inlineStr"/>
-      <c r="B136" s="15" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr"/>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Skyline</t>
         </is>
       </c>
-      <c r="C136" s="15" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D136" s="16" t="n">
+      <c r="D136" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="E136" s="16" t="n">
+      <c r="E136" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F136" s="17" t="n">
+      <c r="F136" s="4" t="n">
         <v>3.444444444444445</v>
       </c>
-      <c r="G136" s="18" t="n">
+      <c r="G136" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="H136" s="15" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I136" s="6" t="n"/>
-      <c r="J136" s="19" t="inlineStr"/>
-      <c r="K136" s="20" t="inlineStr">
+      <c r="J136" s="7" t="inlineStr"/>
+      <c r="K136" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5461,37 +5444,37 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="15" t="inlineStr"/>
-      <c r="B138" s="15" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr"/>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Volta</t>
         </is>
       </c>
-      <c r="C138" s="15" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D138" s="16" t="n">
+      <c r="D138" s="3" t="n">
         <v>3800</v>
       </c>
-      <c r="E138" s="16" t="n">
+      <c r="E138" s="3" t="n">
         <v>860</v>
       </c>
-      <c r="F138" s="17" t="n">
+      <c r="F138" s="4" t="n">
         <v>3.418604651162791</v>
       </c>
-      <c r="G138" s="18" t="n">
+      <c r="G138" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="H138" s="15" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I138" s="6" t="n"/>
-      <c r="J138" s="19" t="inlineStr"/>
-      <c r="K138" s="20" t="inlineStr">
+      <c r="J138" s="7" t="inlineStr"/>
+      <c r="K138" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5535,37 +5518,37 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="15" t="inlineStr"/>
-      <c r="B140" s="15" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr"/>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Milo</t>
         </is>
       </c>
-      <c r="C140" s="15" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D140" s="16" t="n">
+      <c r="D140" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E140" s="16" t="n">
+      <c r="E140" s="3" t="n">
         <v>460</v>
       </c>
-      <c r="F140" s="17" t="n">
+      <c r="F140" s="4" t="n">
         <v>3.782608695652174</v>
       </c>
-      <c r="G140" s="18" t="n">
+      <c r="G140" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="H140" s="15" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I140" s="6" t="n"/>
-      <c r="J140" s="19" t="inlineStr"/>
-      <c r="K140" s="20" t="inlineStr">
+      <c r="J140" s="7" t="inlineStr"/>
+      <c r="K140" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5609,37 +5592,37 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr"/>
-      <c r="B142" s="15" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr"/>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Hudson</t>
         </is>
       </c>
-      <c r="C142" s="15" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D142" s="16" t="n">
+      <c r="D142" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E142" s="16" t="n">
+      <c r="E142" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F142" s="17" t="n">
+      <c r="F142" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="G142" s="18" t="n">
+      <c r="G142" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H142" s="15" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I142" s="6" t="n"/>
-      <c r="J142" s="19" t="inlineStr"/>
-      <c r="K142" s="20" t="inlineStr">
+      <c r="J142" s="7" t="inlineStr"/>
+      <c r="K142" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5683,37 +5666,37 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="15" t="inlineStr"/>
-      <c r="B144" s="15" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr"/>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Depot</t>
         </is>
       </c>
-      <c r="C144" s="15" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>Ensembles de salon</t>
         </is>
       </c>
-      <c r="D144" s="16" t="n">
+      <c r="D144" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E144" s="16" t="n">
+      <c r="E144" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F144" s="17" t="n">
+      <c r="F144" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="G144" s="18" t="n">
+      <c r="G144" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H144" s="15" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I144" s="6" t="n"/>
-      <c r="J144" s="19" t="inlineStr"/>
-      <c r="K144" s="20" t="inlineStr">
+      <c r="J144" s="7" t="inlineStr"/>
+      <c r="K144" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5753,41 +5736,41 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="15" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>IF-8162</t>
         </is>
       </c>
-      <c r="B146" s="15" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Fauteuil inclinable électrique</t>
         </is>
       </c>
-      <c r="C146" s="15" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D146" s="16" t="n">
+      <c r="D146" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E146" s="16" t="n">
+      <c r="E146" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F146" s="17" t="n">
+      <c r="F146" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="18" t="n">
+      <c r="G146" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H146" s="15" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I146" s="6" t="n"/>
-      <c r="J146" s="19" t="inlineStr"/>
-      <c r="K146" s="20" t="inlineStr">
+      <c r="J146" s="7" t="inlineStr"/>
+      <c r="K146" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5827,33 +5810,33 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="15" t="inlineStr"/>
-      <c r="B148" s="15" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr"/>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Royal — Fauteuil</t>
         </is>
       </c>
-      <c r="C148" s="15" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D148" s="16" t="n">
+      <c r="D148" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E148" s="16" t="n"/>
-      <c r="F148" s="17" t="n"/>
-      <c r="G148" s="18" t="n">
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H148" s="15" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I148" s="6" t="n"/>
-      <c r="J148" s="19" t="inlineStr"/>
-      <c r="K148" s="20" t="inlineStr">
+      <c r="J148" s="7" t="inlineStr"/>
+      <c r="K148" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5893,33 +5876,33 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="15" t="inlineStr"/>
-      <c r="B150" s="15" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr"/>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Opéra — Fauteuil</t>
         </is>
       </c>
-      <c r="C150" s="15" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D150" s="16" t="n">
+      <c r="D150" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E150" s="16" t="n"/>
-      <c r="F150" s="17" t="n"/>
-      <c r="G150" s="18" t="n">
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H150" s="15" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I150" s="6" t="n"/>
-      <c r="J150" s="19" t="inlineStr"/>
-      <c r="K150" s="20" t="inlineStr">
+      <c r="J150" s="7" t="inlineStr"/>
+      <c r="K150" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -5959,33 +5942,33 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="15" t="inlineStr"/>
-      <c r="B152" s="15" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr"/>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Skyline — Fauteuil</t>
         </is>
       </c>
-      <c r="C152" s="15" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D152" s="16" t="n">
+      <c r="D152" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E152" s="16" t="n"/>
-      <c r="F152" s="17" t="n"/>
-      <c r="G152" s="18" t="n">
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H152" s="15" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I152" s="6" t="n"/>
-      <c r="J152" s="19" t="inlineStr"/>
-      <c r="K152" s="20" t="inlineStr">
+      <c r="J152" s="7" t="inlineStr"/>
+      <c r="K152" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6025,33 +6008,33 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="15" t="inlineStr"/>
-      <c r="B154" s="15" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr"/>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Sérénity — Fauteuil</t>
         </is>
       </c>
-      <c r="C154" s="15" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D154" s="16" t="n">
+      <c r="D154" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E154" s="16" t="n"/>
-      <c r="F154" s="17" t="n"/>
-      <c r="G154" s="18" t="n">
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H154" s="15" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I154" s="6" t="n"/>
-      <c r="J154" s="19" t="inlineStr"/>
-      <c r="K154" s="20" t="inlineStr">
+      <c r="J154" s="7" t="inlineStr"/>
+      <c r="K154" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6091,37 +6074,37 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="15" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>IF 8120</t>
         </is>
       </c>
-      <c r="B156" s="15" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Canapé Casgrain — cuir noir — Fauteuil</t>
         </is>
       </c>
-      <c r="C156" s="15" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D156" s="16" t="n">
+      <c r="D156" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E156" s="16" t="n"/>
-      <c r="F156" s="17" t="n"/>
-      <c r="G156" s="18" t="n">
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H156" s="15" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I156" s="6" t="n"/>
-      <c r="J156" s="19" t="inlineStr"/>
-      <c r="K156" s="20" t="inlineStr">
+      <c r="J156" s="7" t="inlineStr"/>
+      <c r="K156" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6161,37 +6144,37 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="15" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>IF-8007</t>
         </is>
       </c>
-      <c r="B158" s="15" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Canapé Christophe — velours noir — Fauteuil</t>
         </is>
       </c>
-      <c r="C158" s="15" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D158" s="16" t="n">
+      <c r="D158" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="E158" s="16" t="n"/>
-      <c r="F158" s="17" t="n"/>
-      <c r="G158" s="18" t="n">
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H158" s="15" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I158" s="6" t="n"/>
-      <c r="J158" s="19" t="inlineStr"/>
-      <c r="K158" s="20" t="inlineStr">
+      <c r="J158" s="7" t="inlineStr"/>
+      <c r="K158" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6231,37 +6214,37 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="15" t="inlineStr"/>
-      <c r="B160" s="15" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr"/>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Fauteuil-Lit Convertible</t>
         </is>
       </c>
-      <c r="C160" s="15" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D160" s="16" t="n">
+      <c r="D160" s="3" t="n">
         <v>499</v>
       </c>
-      <c r="E160" s="16" t="n">
+      <c r="E160" s="3" t="n">
         <v>499</v>
       </c>
-      <c r="F160" s="17" t="n">
+      <c r="F160" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G160" s="18" t="n">
+      <c r="G160" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H160" s="15" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I160" s="6" t="n"/>
-      <c r="J160" s="19" t="inlineStr"/>
-      <c r="K160" s="20" t="inlineStr">
+      <c r="J160" s="7" t="inlineStr"/>
+      <c r="K160" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6301,33 +6284,33 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="15" t="inlineStr"/>
-      <c r="B162" s="15" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr"/>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Depot — Fauteuil</t>
         </is>
       </c>
-      <c r="C162" s="15" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D162" s="16" t="n">
+      <c r="D162" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E162" s="16" t="n"/>
-      <c r="F162" s="17" t="n"/>
-      <c r="G162" s="18" t="n">
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="4" t="n"/>
+      <c r="G162" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H162" s="15" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I162" s="6" t="n"/>
-      <c r="J162" s="19" t="inlineStr"/>
-      <c r="K162" s="20" t="inlineStr">
+      <c r="J162" s="7" t="inlineStr"/>
+      <c r="K162" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6367,37 +6350,37 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="15" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>IF-8012</t>
         </is>
       </c>
-      <c r="B164" s="15" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Canapé Chabanel — cuir beige — Fauteuil</t>
         </is>
       </c>
-      <c r="C164" s="15" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Fauteuils</t>
         </is>
       </c>
-      <c r="D164" s="16" t="n">
+      <c r="D164" s="3" t="n">
         <v>459.98</v>
       </c>
-      <c r="E164" s="16" t="n"/>
-      <c r="F164" s="17" t="n"/>
-      <c r="G164" s="18" t="n">
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="4" t="n"/>
+      <c r="G164" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H164" s="15" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I164" s="6" t="n"/>
-      <c r="J164" s="19" t="inlineStr"/>
-      <c r="K164" s="20" t="inlineStr">
+      <c r="J164" s="7" t="inlineStr"/>
+      <c r="K164" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6437,33 +6420,33 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="15" t="inlineStr"/>
-      <c r="B166" s="15" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr"/>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Jordyn – Blanc — Lit</t>
         </is>
       </c>
-      <c r="C166" s="15" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D166" s="16" t="n">
+      <c r="D166" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E166" s="16" t="n"/>
-      <c r="F166" s="17" t="n"/>
-      <c r="G166" s="18" t="n">
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="4" t="n"/>
+      <c r="G166" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H166" s="15" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I166" s="6" t="n"/>
-      <c r="J166" s="19" t="inlineStr"/>
-      <c r="K166" s="20" t="inlineStr">
+      <c r="J166" s="7" t="inlineStr"/>
+      <c r="K166" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6503,41 +6486,41 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>IF-5793</t>
         </is>
       </c>
-      <c r="B168" s="15" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Lit plateforme — Noir</t>
         </is>
       </c>
-      <c r="C168" s="15" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D168" s="16" t="n">
+      <c r="D168" s="3" t="n">
         <v>1259.98</v>
       </c>
-      <c r="E168" s="16" t="n">
+      <c r="E168" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="F168" s="17" t="n">
+      <c r="F168" s="4" t="n">
         <v>0.2612412412412413</v>
       </c>
-      <c r="G168" s="18" t="n">
+      <c r="G168" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H168" s="15" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I168" s="6" t="n"/>
-      <c r="J168" s="19" t="inlineStr"/>
-      <c r="K168" s="20" t="inlineStr">
+      <c r="J168" s="7" t="inlineStr"/>
+      <c r="K168" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6585,41 +6568,41 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="15" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>IF-5792</t>
         </is>
       </c>
-      <c r="B170" s="15" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Lit plateforme — Beige</t>
         </is>
       </c>
-      <c r="C170" s="15" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D170" s="16" t="n">
+      <c r="D170" s="3" t="n">
         <v>1259.98</v>
       </c>
-      <c r="E170" s="16" t="n">
+      <c r="E170" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="F170" s="17" t="n">
+      <c r="F170" s="4" t="n">
         <v>0.2612412412412413</v>
       </c>
-      <c r="G170" s="18" t="n">
+      <c r="G170" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H170" s="15" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I170" s="6" t="n"/>
-      <c r="J170" s="19" t="inlineStr"/>
-      <c r="K170" s="20" t="inlineStr">
+      <c r="J170" s="7" t="inlineStr"/>
+      <c r="K170" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6663,41 +6646,41 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="15" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>IF-5120</t>
         </is>
       </c>
-      <c r="B172" s="15" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Lit contemporain en velours gris</t>
         </is>
       </c>
-      <c r="C172" s="15" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D172" s="16" t="n">
+      <c r="D172" s="3" t="n">
         <v>1099.98</v>
       </c>
-      <c r="E172" s="16" t="n">
+      <c r="E172" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="F172" s="17" t="n">
+      <c r="F172" s="4" t="n">
         <v>4.238</v>
       </c>
-      <c r="G172" s="18" t="n">
+      <c r="G172" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="H172" s="15" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I172" s="6" t="n"/>
-      <c r="J172" s="19" t="inlineStr"/>
-      <c r="K172" s="20" t="inlineStr">
+      <c r="J172" s="7" t="inlineStr"/>
+      <c r="K172" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6745,33 +6728,33 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="15" t="inlineStr"/>
-      <c r="B174" s="15" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr"/>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Madisson 100 — Lit</t>
         </is>
       </c>
-      <c r="C174" s="15" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D174" s="16" t="n">
+      <c r="D174" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E174" s="16" t="n"/>
-      <c r="F174" s="17" t="n"/>
-      <c r="G174" s="18" t="n">
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H174" s="15" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I174" s="6" t="n"/>
-      <c r="J174" s="19" t="inlineStr"/>
-      <c r="K174" s="20" t="inlineStr">
+      <c r="J174" s="7" t="inlineStr"/>
+      <c r="K174" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6811,37 +6794,37 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="15" t="inlineStr"/>
-      <c r="B176" s="15" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr"/>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Lit plateforme moderne</t>
         </is>
       </c>
-      <c r="C176" s="15" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D176" s="16" t="n">
+      <c r="D176" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="E176" s="16" t="n">
+      <c r="E176" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="F176" s="17" t="n">
+      <c r="F176" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G176" s="18" t="n">
+      <c r="G176" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="H176" s="15" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I176" s="6" t="n"/>
-      <c r="J176" s="19" t="inlineStr"/>
-      <c r="K176" s="20" t="inlineStr">
+      <c r="J176" s="7" t="inlineStr"/>
+      <c r="K176" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6889,41 +6872,41 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="15" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>IF-5560</t>
         </is>
       </c>
-      <c r="B178" s="15" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Lit Ahuntsic — velours gris</t>
         </is>
       </c>
-      <c r="C178" s="15" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D178" s="16" t="n">
+      <c r="D178" s="3" t="n">
         <v>839.98</v>
       </c>
-      <c r="E178" s="16" t="n">
+      <c r="E178" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="F178" s="17" t="n">
+      <c r="F178" s="4" t="n">
         <v>-2.380952380950215e-05</v>
       </c>
-      <c r="G178" s="18" t="n">
+      <c r="G178" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="H178" s="15" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I178" s="6" t="n"/>
-      <c r="J178" s="19" t="inlineStr"/>
-      <c r="K178" s="20" t="inlineStr">
+      <c r="J178" s="7" t="inlineStr"/>
+      <c r="K178" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -6963,33 +6946,33 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="15" t="inlineStr"/>
-      <c r="B180" s="15" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr"/>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Harper "Seville" — Lit</t>
         </is>
       </c>
-      <c r="C180" s="15" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D180" s="16" t="n">
+      <c r="D180" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="E180" s="16" t="n"/>
-      <c r="F180" s="17" t="n"/>
-      <c r="G180" s="18" t="n">
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="4" t="n"/>
+      <c r="G180" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H180" s="15" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I180" s="6" t="n"/>
-      <c r="J180" s="19" t="inlineStr"/>
-      <c r="K180" s="20" t="inlineStr">
+      <c r="J180" s="7" t="inlineStr"/>
+      <c r="K180" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7029,37 +7012,37 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="15" t="inlineStr"/>
-      <c r="B182" s="15" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr"/>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Lit avec rangement hydraulique</t>
         </is>
       </c>
-      <c r="C182" s="15" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D182" s="16" t="n">
+      <c r="D182" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="E182" s="16" t="n">
+      <c r="E182" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="F182" s="17" t="n">
+      <c r="F182" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G182" s="18" t="n">
+      <c r="G182" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H182" s="15" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I182" s="6" t="n"/>
-      <c r="J182" s="19" t="inlineStr"/>
-      <c r="K182" s="20" t="inlineStr">
+      <c r="J182" s="7" t="inlineStr"/>
+      <c r="K182" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7103,37 +7086,37 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="15" t="inlineStr"/>
-      <c r="B184" s="15" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr"/>
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Lit Velours Gris avec Rangement</t>
         </is>
       </c>
-      <c r="C184" s="15" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D184" s="16" t="n">
+      <c r="D184" s="3" t="n">
         <v>699</v>
       </c>
-      <c r="E184" s="16" t="n">
+      <c r="E184" s="3" t="n">
         <v>699</v>
       </c>
-      <c r="F184" s="17" t="n">
+      <c r="F184" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G184" s="18" t="n">
+      <c r="G184" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H184" s="15" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I184" s="6" t="n"/>
-      <c r="J184" s="19" t="inlineStr"/>
-      <c r="K184" s="20" t="inlineStr">
+      <c r="J184" s="7" t="inlineStr"/>
+      <c r="K184" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7173,37 +7156,37 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="15" t="inlineStr"/>
-      <c r="B186" s="15" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr"/>
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Lit Moderne Bas</t>
         </is>
       </c>
-      <c r="C186" s="15" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D186" s="16" t="n">
+      <c r="D186" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="E186" s="16" t="n">
+      <c r="E186" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="F186" s="17" t="n">
+      <c r="F186" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G186" s="18" t="n">
+      <c r="G186" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H186" s="15" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I186" s="6" t="n"/>
-      <c r="J186" s="19" t="inlineStr"/>
-      <c r="K186" s="20" t="inlineStr">
+      <c r="J186" s="7" t="inlineStr"/>
+      <c r="K186" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7247,37 +7230,37 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="15" t="inlineStr"/>
-      <c r="B188" s="15" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr"/>
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Lit Papineau — tissu</t>
         </is>
       </c>
-      <c r="C188" s="15" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D188" s="16" t="n">
+      <c r="D188" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E188" s="16" t="n">
+      <c r="E188" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F188" s="17" t="n">
+      <c r="F188" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G188" s="18" t="n">
+      <c r="G188" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H188" s="15" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I188" s="6" t="n"/>
-      <c r="J188" s="19" t="inlineStr"/>
-      <c r="K188" s="20" t="inlineStr">
+      <c r="J188" s="7" t="inlineStr"/>
+      <c r="K188" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7317,41 +7300,41 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="15" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>IF-5295</t>
         </is>
       </c>
-      <c r="B190" s="15" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Lit plateforme — Gris (2)</t>
         </is>
       </c>
-      <c r="C190" s="15" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D190" s="16" t="n">
+      <c r="D190" s="3" t="n">
         <v>599.98</v>
       </c>
-      <c r="E190" s="16" t="n">
+      <c r="E190" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="F190" s="17" t="n">
+      <c r="F190" s="4" t="n">
         <v>0.034448275862069</v>
       </c>
-      <c r="G190" s="18" t="n">
+      <c r="G190" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="H190" s="15" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I190" s="6" t="n"/>
-      <c r="J190" s="19" t="inlineStr"/>
-      <c r="K190" s="20" t="inlineStr">
+      <c r="J190" s="7" t="inlineStr"/>
+      <c r="K190" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7395,37 +7378,37 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="15" t="inlineStr"/>
-      <c r="B192" s="15" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr"/>
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Velours Dusty Pink</t>
         </is>
       </c>
-      <c r="C192" s="15" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D192" s="16" t="n">
+      <c r="D192" s="3" t="n">
         <v>575.99</v>
       </c>
-      <c r="E192" s="16" t="n">
+      <c r="E192" s="3" t="n">
         <v>575.99</v>
       </c>
-      <c r="F192" s="17" t="n">
+      <c r="F192" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G192" s="18" t="n">
+      <c r="G192" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="H192" s="15" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I192" s="6" t="n"/>
-      <c r="J192" s="19" t="inlineStr"/>
-      <c r="K192" s="20" t="inlineStr">
+      <c r="J192" s="7" t="inlineStr"/>
+      <c r="K192" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7469,33 +7452,33 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr"/>
-      <c r="B194" s="15" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr"/>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Lucia — Blanc — Lit</t>
         </is>
       </c>
-      <c r="C194" s="15" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D194" s="16" t="n">
+      <c r="D194" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="E194" s="16" t="n"/>
-      <c r="F194" s="17" t="n"/>
-      <c r="G194" s="18" t="n">
+      <c r="E194" s="3" t="n"/>
+      <c r="F194" s="4" t="n"/>
+      <c r="G194" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="H194" s="15" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I194" s="6" t="n"/>
-      <c r="J194" s="19" t="inlineStr"/>
-      <c r="K194" s="20" t="inlineStr">
+      <c r="J194" s="7" t="inlineStr"/>
+      <c r="K194" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7539,41 +7522,41 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="15" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>IF-5408</t>
         </is>
       </c>
-      <c r="B196" s="15" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Lit avec rangement</t>
         </is>
       </c>
-      <c r="C196" s="15" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D196" s="16" t="n">
+      <c r="D196" s="3" t="n">
         <v>539.98</v>
       </c>
-      <c r="E196" s="16" t="n">
+      <c r="E196" s="3" t="n">
         <v>520</v>
       </c>
-      <c r="F196" s="17" t="n">
+      <c r="F196" s="4" t="n">
         <v>0.03842307692307696</v>
       </c>
-      <c r="G196" s="18" t="n">
+      <c r="G196" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H196" s="15" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I196" s="6" t="n"/>
-      <c r="J196" s="19" t="inlineStr"/>
-      <c r="K196" s="20" t="inlineStr">
+      <c r="J196" s="7" t="inlineStr"/>
+      <c r="K196" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7621,37 +7604,37 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="15" t="inlineStr"/>
-      <c r="B198" s="15" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr"/>
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Lit en tissu gris avec rangement hydraulique</t>
         </is>
       </c>
-      <c r="C198" s="15" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D198" s="16" t="n">
+      <c r="D198" s="3" t="n">
         <v>499.99</v>
       </c>
-      <c r="E198" s="16" t="n">
+      <c r="E198" s="3" t="n">
         <v>499.99</v>
       </c>
-      <c r="F198" s="17" t="n">
+      <c r="F198" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G198" s="18" t="n">
+      <c r="G198" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H198" s="15" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I198" s="6" t="n"/>
-      <c r="J198" s="19" t="inlineStr"/>
-      <c r="K198" s="20" t="inlineStr">
+      <c r="J198" s="7" t="inlineStr"/>
+      <c r="K198" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7695,41 +7678,41 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="15" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>IF-5710</t>
         </is>
       </c>
-      <c r="B200" s="15" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Lit Jeanne-Mance — tissu gris</t>
         </is>
       </c>
-      <c r="C200" s="15" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D200" s="16" t="n">
+      <c r="D200" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="E200" s="16" t="n">
+      <c r="E200" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="F200" s="17" t="n">
+      <c r="F200" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G200" s="18" t="n">
+      <c r="G200" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H200" s="15" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I200" s="6" t="n"/>
-      <c r="J200" s="19" t="inlineStr"/>
-      <c r="K200" s="20" t="inlineStr">
+      <c r="J200" s="7" t="inlineStr"/>
+      <c r="K200" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7773,37 +7756,37 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="15" t="inlineStr"/>
-      <c r="B202" s="15" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr"/>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Lit Queen en Velours Gris</t>
         </is>
       </c>
-      <c r="C202" s="15" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D202" s="16" t="n">
+      <c r="D202" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="E202" s="16" t="n">
+      <c r="E202" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="F202" s="17" t="n">
+      <c r="F202" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G202" s="18" t="n">
+      <c r="G202" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H202" s="15" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I202" s="6" t="n"/>
-      <c r="J202" s="19" t="inlineStr"/>
-      <c r="K202" s="20" t="inlineStr">
+      <c r="J202" s="7" t="inlineStr"/>
+      <c r="K202" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7847,41 +7830,41 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="15" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>IF-176</t>
         </is>
       </c>
-      <c r="B204" s="15" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>Lit Jarry — noir</t>
         </is>
       </c>
-      <c r="C204" s="15" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D204" s="16" t="n">
+      <c r="D204" s="3" t="n">
         <v>299.98</v>
       </c>
-      <c r="E204" s="16" t="n">
+      <c r="E204" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="F204" s="17" t="n">
+      <c r="F204" s="4" t="n">
         <v>0.3635454545454546</v>
       </c>
-      <c r="G204" s="18" t="n">
+      <c r="G204" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H204" s="15" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I204" s="6" t="n"/>
-      <c r="J204" s="19" t="inlineStr"/>
-      <c r="K204" s="20" t="inlineStr">
+      <c r="J204" s="7" t="inlineStr"/>
+      <c r="K204" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -7929,41 +7912,41 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="15" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>IF-174</t>
         </is>
       </c>
-      <c r="B206" s="15" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>Lit Everett — blanc</t>
         </is>
       </c>
-      <c r="C206" s="15" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D206" s="16" t="n">
+      <c r="D206" s="3" t="n">
         <v>279.98</v>
       </c>
-      <c r="E206" s="16" t="n">
+      <c r="E206" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="F206" s="17" t="n">
+      <c r="F206" s="4" t="n">
         <v>0.1199200000000001</v>
       </c>
-      <c r="G206" s="18" t="n">
+      <c r="G206" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H206" s="15" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I206" s="6" t="n"/>
-      <c r="J206" s="19" t="inlineStr"/>
-      <c r="K206" s="20" t="inlineStr">
+      <c r="J206" s="7" t="inlineStr"/>
+      <c r="K206" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8011,37 +7994,37 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="15" t="inlineStr"/>
-      <c r="B208" s="15" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr"/>
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>Matelas OrthoPedic Deluxe – Confort moyen</t>
         </is>
       </c>
-      <c r="C208" s="15" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>Lits</t>
         </is>
       </c>
-      <c r="D208" s="16" t="n">
+      <c r="D208" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E208" s="16" t="n">
+      <c r="E208" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="F208" s="17" t="n">
+      <c r="F208" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G208" s="18" t="n">
+      <c r="G208" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H208" s="15" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I208" s="6" t="n"/>
-      <c r="J208" s="19" t="inlineStr"/>
-      <c r="K208" s="20" t="inlineStr">
+      <c r="J208" s="7" t="inlineStr"/>
+      <c r="K208" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8085,37 +8068,37 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="15" t="inlineStr"/>
-      <c r="B210" s="15" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr"/>
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>Lit Superposé — Blanc</t>
         </is>
       </c>
-      <c r="C210" s="15" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>Lits superposés</t>
         </is>
       </c>
-      <c r="D210" s="16" t="n">
+      <c r="D210" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="E210" s="16" t="n">
+      <c r="E210" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="F210" s="17" t="n">
+      <c r="F210" s="4" t="n">
         <v>3.166666666666667</v>
       </c>
-      <c r="G210" s="18" t="n">
+      <c r="G210" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="H210" s="15" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I210" s="6" t="n"/>
-      <c r="J210" s="19" t="inlineStr"/>
-      <c r="K210" s="20" t="inlineStr">
+      <c r="J210" s="7" t="inlineStr"/>
+      <c r="K210" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8159,37 +8142,37 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="15" t="inlineStr"/>
-      <c r="B212" s="15" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr"/>
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>SOFIA – Pillow Top | Série Cuivre</t>
         </is>
       </c>
-      <c r="C212" s="15" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D212" s="16" t="n">
+      <c r="D212" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="E212" s="16" t="n">
+      <c r="E212" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="F212" s="17" t="n">
+      <c r="F212" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G212" s="18" t="n">
+      <c r="G212" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="H212" s="15" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I212" s="6" t="n"/>
-      <c r="J212" s="19" t="inlineStr"/>
-      <c r="K212" s="20" t="inlineStr">
+      <c r="J212" s="7" t="inlineStr"/>
+      <c r="K212" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8233,37 +8216,37 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="15" t="inlineStr"/>
-      <c r="B214" s="15" t="inlineStr">
+      <c r="A214" s="2" t="inlineStr"/>
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>Matelas Bella Euro top – Copper Series</t>
         </is>
       </c>
-      <c r="C214" s="15" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D214" s="16" t="n">
+      <c r="D214" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="E214" s="16" t="n">
+      <c r="E214" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="F214" s="17" t="n">
+      <c r="F214" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G214" s="18" t="n">
+      <c r="G214" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="H214" s="15" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I214" s="6" t="n"/>
-      <c r="J214" s="19" t="inlineStr"/>
-      <c r="K214" s="20" t="inlineStr">
+      <c r="J214" s="7" t="inlineStr"/>
+      <c r="K214" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8307,37 +8290,37 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="15" t="inlineStr"/>
-      <c r="B216" s="15" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr"/>
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>Matelas Christophe — tissu noir</t>
         </is>
       </c>
-      <c r="C216" s="15" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D216" s="16" t="n">
+      <c r="D216" s="3" t="n">
         <v>690</v>
       </c>
-      <c r="E216" s="16" t="n">
+      <c r="E216" s="3" t="n">
         <v>690</v>
       </c>
-      <c r="F216" s="17" t="n">
+      <c r="F216" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G216" s="18" t="n">
+      <c r="G216" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H216" s="15" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I216" s="6" t="n"/>
-      <c r="J216" s="19" t="inlineStr"/>
-      <c r="K216" s="20" t="inlineStr">
+      <c r="J216" s="7" t="inlineStr"/>
+      <c r="K216" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8381,37 +8364,37 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="15" t="inlineStr"/>
-      <c r="B218" s="15" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr"/>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>Matelas Alisha Hybrid – Gel Foam</t>
         </is>
       </c>
-      <c r="C218" s="15" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D218" s="16" t="n">
+      <c r="D218" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E218" s="16" t="n">
+      <c r="E218" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="F218" s="17" t="n">
+      <c r="F218" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G218" s="18" t="n">
+      <c r="G218" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H218" s="15" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I218" s="6" t="n"/>
-      <c r="J218" s="19" t="inlineStr"/>
-      <c r="K218" s="20" t="inlineStr">
+      <c r="J218" s="7" t="inlineStr"/>
+      <c r="K218" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8455,37 +8438,37 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr"/>
-      <c r="B220" s="15" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr"/>
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>Matelas Breeze Cool Max – Fermeté moyenne</t>
         </is>
       </c>
-      <c r="C220" s="15" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D220" s="16" t="n">
+      <c r="D220" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E220" s="16" t="n">
+      <c r="E220" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="F220" s="17" t="n">
+      <c r="F220" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G220" s="18" t="n">
+      <c r="G220" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H220" s="15" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I220" s="6" t="n"/>
-      <c r="J220" s="19" t="inlineStr"/>
-      <c r="K220" s="20" t="inlineStr">
+      <c r="J220" s="7" t="inlineStr"/>
+      <c r="K220" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8533,37 +8516,37 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="15" t="inlineStr"/>
-      <c r="B222" s="15" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr"/>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>Matelas DREAM-O-PEDIC &amp; Tissu bambou</t>
         </is>
       </c>
-      <c r="C222" s="15" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>Matelas</t>
         </is>
       </c>
-      <c r="D222" s="16" t="n">
+      <c r="D222" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E222" s="16" t="n">
+      <c r="E222" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="F222" s="17" t="n">
+      <c r="F222" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G222" s="18" t="n">
+      <c r="G222" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H222" s="15" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I222" s="6" t="n"/>
-      <c r="J222" s="19" t="inlineStr"/>
-      <c r="K222" s="20" t="inlineStr">
+      <c r="J222" s="7" t="inlineStr"/>
+      <c r="K222" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8607,37 +8590,37 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="15" t="inlineStr"/>
-      <c r="B224" s="15" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr"/>
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>Meuble Telé - 60" L</t>
         </is>
       </c>
-      <c r="C224" s="15" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>Meubles TV</t>
         </is>
       </c>
-      <c r="D224" s="16" t="n">
+      <c r="D224" s="3" t="n">
         <v>398.98</v>
       </c>
-      <c r="E224" s="16" t="n">
+      <c r="E224" s="3" t="n">
         <v>398.98</v>
       </c>
-      <c r="F224" s="17" t="n">
+      <c r="F224" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G224" s="18" t="n">
+      <c r="G224" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H224" s="15" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I224" s="6" t="n"/>
-      <c r="J224" s="19" t="inlineStr"/>
-      <c r="K224" s="20" t="inlineStr">
+      <c r="J224" s="7" t="inlineStr"/>
+      <c r="K224" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8681,37 +8664,37 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="15" t="inlineStr"/>
-      <c r="B226" s="15" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr"/>
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>Meuble Télé - 63" L</t>
         </is>
       </c>
-      <c r="C226" s="15" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>Meubles TV</t>
         </is>
       </c>
-      <c r="D226" s="16" t="n">
+      <c r="D226" s="3" t="n">
         <v>380</v>
       </c>
-      <c r="E226" s="16" t="n">
+      <c r="E226" s="3" t="n">
         <v>380</v>
       </c>
-      <c r="F226" s="17" t="n">
+      <c r="F226" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G226" s="18" t="n">
+      <c r="G226" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H226" s="15" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I226" s="6" t="n"/>
-      <c r="J226" s="19" t="inlineStr"/>
-      <c r="K226" s="20" t="inlineStr">
+      <c r="J226" s="7" t="inlineStr"/>
+      <c r="K226" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8755,37 +8738,37 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="15" t="inlineStr"/>
-      <c r="B228" s="15" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr"/>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>Meuble Télé - 60" L</t>
         </is>
       </c>
-      <c r="C228" s="15" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>Meubles TV</t>
         </is>
       </c>
-      <c r="D228" s="16" t="n">
+      <c r="D228" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="E228" s="16" t="n">
+      <c r="E228" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="F228" s="17" t="n">
+      <c r="F228" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G228" s="18" t="n">
+      <c r="G228" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H228" s="15" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I228" s="6" t="n"/>
-      <c r="J228" s="19" t="inlineStr"/>
-      <c r="K228" s="20" t="inlineStr">
+      <c r="J228" s="7" t="inlineStr"/>
+      <c r="K228" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8829,33 +8812,33 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="15" t="inlineStr"/>
-      <c r="B230" s="15" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr"/>
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>Kova — Poufs et ottomane</t>
         </is>
       </c>
-      <c r="C230" s="15" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>Poufs et ottomanes</t>
         </is>
       </c>
-      <c r="D230" s="16" t="n">
+      <c r="D230" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="E230" s="16" t="n"/>
-      <c r="F230" s="17" t="n"/>
-      <c r="G230" s="18" t="n">
+      <c r="E230" s="3" t="n"/>
+      <c r="F230" s="4" t="n"/>
+      <c r="G230" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H230" s="15" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I230" s="6" t="n"/>
-      <c r="J230" s="19" t="inlineStr"/>
-      <c r="K230" s="20" t="inlineStr">
+      <c r="J230" s="7" t="inlineStr"/>
+      <c r="K230" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8899,41 +8882,41 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="15" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>IF-8500</t>
         </is>
       </c>
-      <c r="B232" s="15" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>Sectionnel inclinable</t>
         </is>
       </c>
-      <c r="C232" s="15" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D232" s="16" t="n">
+      <c r="D232" s="3" t="n">
         <v>3999.98</v>
       </c>
-      <c r="E232" s="16" t="n">
+      <c r="E232" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="F232" s="17" t="n">
+      <c r="F232" s="4" t="n">
         <v>-4.999999999995453e-06</v>
       </c>
-      <c r="G232" s="18" t="n">
+      <c r="G232" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="H232" s="15" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I232" s="6" t="n"/>
-      <c r="J232" s="19" t="inlineStr"/>
-      <c r="K232" s="20" t="inlineStr">
+      <c r="J232" s="7" t="inlineStr"/>
+      <c r="K232" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -8981,41 +8964,41 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="15" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>IF-9095</t>
         </is>
       </c>
-      <c r="B234" s="15" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>chaise longue gauche (LHF) — Noir</t>
         </is>
       </c>
-      <c r="C234" s="15" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D234" s="16" t="n">
+      <c r="D234" s="3" t="n">
         <v>2999.98</v>
       </c>
-      <c r="E234" s="16" t="n">
+      <c r="E234" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F234" s="17" t="n">
+      <c r="F234" s="4" t="n">
         <v>-6.666666666660604e-06</v>
       </c>
-      <c r="G234" s="18" t="n">
+      <c r="G234" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="H234" s="15" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I234" s="6" t="n"/>
-      <c r="J234" s="19" t="inlineStr"/>
-      <c r="K234" s="20" t="inlineStr">
+      <c r="J234" s="7" t="inlineStr"/>
+      <c r="K234" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9059,37 +9042,37 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="15" t="inlineStr"/>
-      <c r="B236" s="15" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr"/>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>Vault</t>
         </is>
       </c>
-      <c r="C236" s="15" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D236" s="16" t="n">
+      <c r="D236" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="E236" s="16" t="n">
+      <c r="E236" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="F236" s="17" t="n">
+      <c r="F236" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G236" s="18" t="n">
+      <c r="G236" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="H236" s="15" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I236" s="6" t="n"/>
-      <c r="J236" s="19" t="inlineStr"/>
-      <c r="K236" s="20" t="inlineStr">
+      <c r="J236" s="7" t="inlineStr"/>
+      <c r="K236" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9133,37 +9116,37 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="15" t="inlineStr"/>
-      <c r="B238" s="15" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr"/>
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>Flex</t>
         </is>
       </c>
-      <c r="C238" s="15" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D238" s="16" t="n">
+      <c r="D238" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E238" s="16" t="n">
+      <c r="E238" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F238" s="17" t="n">
+      <c r="F238" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G238" s="18" t="n">
+      <c r="G238" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="H238" s="15" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I238" s="6" t="n"/>
-      <c r="J238" s="19" t="inlineStr"/>
-      <c r="K238" s="20" t="inlineStr">
+      <c r="J238" s="7" t="inlineStr"/>
+      <c r="K238" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9207,41 +9190,41 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="15" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>IF-9035</t>
         </is>
       </c>
-      <c r="B240" s="15" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>Sectionnel Fabre — tissu gris</t>
         </is>
       </c>
-      <c r="C240" s="15" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D240" s="16" t="n">
+      <c r="D240" s="3" t="n">
         <v>2399.98</v>
       </c>
-      <c r="E240" s="16" t="n">
+      <c r="E240" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F240" s="17" t="n">
+      <c r="F240" s="4" t="n">
         <v>-8.333333333325754e-06</v>
       </c>
-      <c r="G240" s="18" t="n">
+      <c r="G240" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="H240" s="15" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I240" s="6" t="n"/>
-      <c r="J240" s="19" t="inlineStr"/>
-      <c r="K240" s="20" t="inlineStr">
+      <c r="J240" s="7" t="inlineStr"/>
+      <c r="K240" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9285,41 +9268,41 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="15" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>IF-9050 / IF-9051</t>
         </is>
       </c>
-      <c r="B242" s="15" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>Sectionnel canapé-lit</t>
         </is>
       </c>
-      <c r="C242" s="15" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D242" s="16" t="n">
+      <c r="D242" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E242" s="16" t="n">
+      <c r="E242" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="F242" s="17" t="n">
+      <c r="F242" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G242" s="18" t="n">
+      <c r="G242" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="H242" s="15" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I242" s="6" t="n"/>
-      <c r="J242" s="19" t="inlineStr"/>
-      <c r="K242" s="20" t="inlineStr">
+      <c r="J242" s="7" t="inlineStr"/>
+      <c r="K242" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9367,37 +9350,37 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="15" t="inlineStr"/>
-      <c r="B244" s="15" t="inlineStr">
+      <c r="A244" s="2" t="inlineStr"/>
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>Drift</t>
         </is>
       </c>
-      <c r="C244" s="15" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D244" s="16" t="n">
+      <c r="D244" s="3" t="n">
         <v>1998.99</v>
       </c>
-      <c r="E244" s="16" t="n">
+      <c r="E244" s="3" t="n">
         <v>1998.99</v>
       </c>
-      <c r="F244" s="17" t="n">
+      <c r="F244" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G244" s="18" t="n">
+      <c r="G244" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="H244" s="15" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I244" s="6" t="n"/>
-      <c r="J244" s="19" t="inlineStr"/>
-      <c r="K244" s="20" t="inlineStr">
+      <c r="J244" s="7" t="inlineStr"/>
+      <c r="K244" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9445,33 +9428,33 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr"/>
-      <c r="B246" s="15" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr"/>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>Kova — Sectionnel</t>
         </is>
       </c>
-      <c r="C246" s="15" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D246" s="16" t="n">
+      <c r="D246" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="E246" s="16" t="n"/>
-      <c r="F246" s="17" t="n"/>
-      <c r="G246" s="18" t="n">
+      <c r="E246" s="3" t="n"/>
+      <c r="F246" s="4" t="n"/>
+      <c r="G246" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="H246" s="15" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I246" s="6" t="n"/>
-      <c r="J246" s="19" t="inlineStr"/>
-      <c r="K246" s="20" t="inlineStr">
+      <c r="J246" s="7" t="inlineStr"/>
+      <c r="K246" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9515,37 +9498,37 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="15" t="inlineStr"/>
-      <c r="B248" s="15" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr"/>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>Black Refuge</t>
         </is>
       </c>
-      <c r="C248" s="15" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D248" s="16" t="n">
+      <c r="D248" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="E248" s="16" t="n">
+      <c r="E248" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="F248" s="17" t="n">
+      <c r="F248" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G248" s="18" t="n">
+      <c r="G248" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="H248" s="15" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I248" s="6" t="n"/>
-      <c r="J248" s="19" t="inlineStr"/>
-      <c r="K248" s="20" t="inlineStr">
+      <c r="J248" s="7" t="inlineStr"/>
+      <c r="K248" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9589,37 +9572,37 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="15" t="inlineStr"/>
-      <c r="B250" s="15" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr"/>
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>Luno</t>
         </is>
       </c>
-      <c r="C250" s="15" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D250" s="16" t="n">
+      <c r="D250" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E250" s="16" t="n">
+      <c r="E250" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F250" s="17" t="n">
+      <c r="F250" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G250" s="18" t="n">
+      <c r="G250" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="H250" s="15" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I250" s="6" t="n"/>
-      <c r="J250" s="19" t="inlineStr"/>
-      <c r="K250" s="20" t="inlineStr">
+      <c r="J250" s="7" t="inlineStr"/>
+      <c r="K250" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9663,37 +9646,37 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="15" t="inlineStr"/>
-      <c r="B252" s="15" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr"/>
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>Sofa Lit - 8A14L83</t>
         </is>
       </c>
-      <c r="C252" s="15" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D252" s="16" t="n">
+      <c r="D252" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="E252" s="16" t="n">
+      <c r="E252" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="F252" s="17" t="n">
+      <c r="F252" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G252" s="18" t="n">
+      <c r="G252" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H252" s="15" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I252" s="6" t="n"/>
-      <c r="J252" s="19" t="inlineStr"/>
-      <c r="K252" s="20" t="inlineStr">
+      <c r="J252" s="7" t="inlineStr"/>
+      <c r="K252" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9737,37 +9720,37 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="15" t="inlineStr"/>
-      <c r="B254" s="15" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr"/>
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>Sofa Lit — Brun</t>
         </is>
       </c>
-      <c r="C254" s="15" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D254" s="16" t="n">
+      <c r="D254" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="E254" s="16" t="n">
+      <c r="E254" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="F254" s="17" t="n">
+      <c r="F254" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G254" s="18" t="n">
+      <c r="G254" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H254" s="15" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I254" s="6" t="n"/>
-      <c r="J254" s="19" t="inlineStr"/>
-      <c r="K254" s="20" t="inlineStr">
+      <c r="J254" s="7" t="inlineStr"/>
+      <c r="K254" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9811,37 +9794,37 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="15" t="inlineStr"/>
-      <c r="B256" s="15" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr"/>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>Sofa Lit — Gris</t>
         </is>
       </c>
-      <c r="C256" s="15" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D256" s="16" t="n">
+      <c r="D256" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="E256" s="16" t="n">
+      <c r="E256" s="3" t="n">
         <v>1050</v>
       </c>
-      <c r="F256" s="17" t="n">
+      <c r="F256" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G256" s="18" t="n">
+      <c r="G256" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H256" s="15" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I256" s="6" t="n"/>
-      <c r="J256" s="19" t="inlineStr"/>
-      <c r="K256" s="20" t="inlineStr">
+      <c r="J256" s="7" t="inlineStr"/>
+      <c r="K256" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9885,37 +9868,37 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="15" t="inlineStr"/>
-      <c r="B258" s="15" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr"/>
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>Sofa Chaise Longue — Gris</t>
         </is>
       </c>
-      <c r="C258" s="15" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D258" s="16" t="n">
+      <c r="D258" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E258" s="16" t="n">
+      <c r="E258" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F258" s="17" t="n">
+      <c r="F258" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G258" s="18" t="n">
+      <c r="G258" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="H258" s="15" t="inlineStr">
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I258" s="6" t="n"/>
-      <c r="J258" s="19" t="inlineStr"/>
-      <c r="K258" s="20" t="inlineStr">
+      <c r="J258" s="7" t="inlineStr"/>
+      <c r="K258" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -9959,37 +9942,37 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="15" t="inlineStr"/>
-      <c r="B260" s="15" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr"/>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>Sofa Chaise Longue — Brun (2)</t>
         </is>
       </c>
-      <c r="C260" s="15" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>Sectionnels</t>
         </is>
       </c>
-      <c r="D260" s="16" t="n">
+      <c r="D260" s="3" t="n">
         <v>798.99</v>
       </c>
-      <c r="E260" s="16" t="n">
+      <c r="E260" s="3" t="n">
         <v>798.99</v>
       </c>
-      <c r="F260" s="17" t="n">
+      <c r="F260" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G260" s="18" t="n">
+      <c r="G260" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="H260" s="15" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I260" s="6" t="n"/>
-      <c r="J260" s="19" t="inlineStr"/>
-      <c r="K260" s="20" t="inlineStr">
+      <c r="J260" s="7" t="inlineStr"/>
+      <c r="K260" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10029,33 +10012,33 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="15" t="inlineStr"/>
-      <c r="B262" s="15" t="inlineStr">
+      <c r="A262" s="2" t="inlineStr"/>
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>Chambre Moderne Blanche — Tables de chevet</t>
         </is>
       </c>
-      <c r="C262" s="15" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D262" s="16" t="n">
+      <c r="D262" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="E262" s="16" t="n"/>
-      <c r="F262" s="17" t="n"/>
-      <c r="G262" s="18" t="n">
+      <c r="E262" s="3" t="n"/>
+      <c r="F262" s="4" t="n"/>
+      <c r="G262" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H262" s="15" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I262" s="6" t="n"/>
-      <c r="J262" s="19" t="inlineStr"/>
-      <c r="K262" s="20" t="inlineStr">
+      <c r="J262" s="7" t="inlineStr"/>
+      <c r="K262" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10095,33 +10078,33 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="15" t="inlineStr"/>
-      <c r="B264" s="15" t="inlineStr">
+      <c r="A264" s="2" t="inlineStr"/>
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>Jordyn – Blanc — Tables de chevet</t>
         </is>
       </c>
-      <c r="C264" s="15" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D264" s="16" t="n">
+      <c r="D264" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E264" s="16" t="n"/>
-      <c r="F264" s="17" t="n"/>
-      <c r="G264" s="18" t="n">
+      <c r="E264" s="3" t="n"/>
+      <c r="F264" s="4" t="n"/>
+      <c r="G264" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H264" s="15" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I264" s="6" t="n"/>
-      <c r="J264" s="19" t="inlineStr"/>
-      <c r="K264" s="20" t="inlineStr">
+      <c r="J264" s="7" t="inlineStr"/>
+      <c r="K264" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10161,37 +10144,37 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="15" t="inlineStr"/>
-      <c r="B266" s="15" t="inlineStr">
+      <c r="A266" s="2" t="inlineStr"/>
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>Luccia – Table de chevet blanche</t>
         </is>
       </c>
-      <c r="C266" s="15" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D266" s="16" t="n">
+      <c r="D266" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="E266" s="16" t="n">
+      <c r="E266" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="F266" s="17" t="n">
+      <c r="F266" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G266" s="18" t="n">
+      <c r="G266" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H266" s="15" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I266" s="6" t="n"/>
-      <c r="J266" s="19" t="inlineStr"/>
-      <c r="K266" s="20" t="inlineStr">
+      <c r="J266" s="7" t="inlineStr"/>
+      <c r="K266" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10231,33 +10214,33 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="15" t="inlineStr"/>
-      <c r="B268" s="15" t="inlineStr">
+      <c r="A268" s="2" t="inlineStr"/>
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>Pompéi – Gris métallisé — Tables de chevet</t>
         </is>
       </c>
-      <c r="C268" s="15" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D268" s="16" t="n">
+      <c r="D268" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E268" s="16" t="n"/>
-      <c r="F268" s="17" t="n"/>
-      <c r="G268" s="18" t="n">
+      <c r="E268" s="3" t="n"/>
+      <c r="F268" s="4" t="n"/>
+      <c r="G268" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H268" s="15" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I268" s="6" t="n"/>
-      <c r="J268" s="19" t="inlineStr"/>
-      <c r="K268" s="20" t="inlineStr">
+      <c r="J268" s="7" t="inlineStr"/>
+      <c r="K268" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10297,33 +10280,33 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="15" t="inlineStr"/>
-      <c r="B270" s="15" t="inlineStr">
+      <c r="A270" s="2" t="inlineStr"/>
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>Madisson 100 — Tables de chevet</t>
         </is>
       </c>
-      <c r="C270" s="15" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D270" s="16" t="n">
+      <c r="D270" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E270" s="16" t="n"/>
-      <c r="F270" s="17" t="n"/>
-      <c r="G270" s="18" t="n">
+      <c r="E270" s="3" t="n"/>
+      <c r="F270" s="4" t="n"/>
+      <c r="G270" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H270" s="15" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I270" s="6" t="n"/>
-      <c r="J270" s="19" t="inlineStr"/>
-      <c r="K270" s="20" t="inlineStr">
+      <c r="J270" s="7" t="inlineStr"/>
+      <c r="K270" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10363,33 +10346,33 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr"/>
-      <c r="B272" s="15" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr"/>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>Dylan — Tables de chevet</t>
         </is>
       </c>
-      <c r="C272" s="15" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>Tables de chevet</t>
         </is>
       </c>
-      <c r="D272" s="16" t="n">
+      <c r="D272" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E272" s="16" t="n"/>
-      <c r="F272" s="17" t="n"/>
-      <c r="G272" s="18" t="n">
+      <c r="E272" s="3" t="n"/>
+      <c r="F272" s="4" t="n"/>
+      <c r="G272" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H272" s="15" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I272" s="6" t="n"/>
-      <c r="J272" s="19" t="inlineStr"/>
-      <c r="K272" s="20" t="inlineStr">
+      <c r="J272" s="7" t="inlineStr"/>
+      <c r="K272" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10429,33 +10412,33 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="15" t="inlineStr"/>
-      <c r="B274" s="15" t="inlineStr">
+      <c r="A274" s="2" t="inlineStr"/>
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>Monaco Dining Set — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C274" s="15" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D274" s="16" t="n">
+      <c r="D274" s="3" t="n">
         <v>1580</v>
       </c>
-      <c r="E274" s="16" t="n"/>
-      <c r="F274" s="17" t="n"/>
-      <c r="G274" s="18" t="n">
+      <c r="E274" s="3" t="n"/>
+      <c r="F274" s="4" t="n"/>
+      <c r="G274" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H274" s="15" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I274" s="6" t="n"/>
-      <c r="J274" s="19" t="inlineStr"/>
-      <c r="K274" s="20" t="inlineStr">
+      <c r="J274" s="7" t="inlineStr"/>
+      <c r="K274" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10499,37 +10482,37 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="15" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>T-1275</t>
         </is>
       </c>
-      <c r="B276" s="15" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>Gaspé — velours beige — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C276" s="15" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D276" s="16" t="n">
+      <c r="D276" s="3" t="n">
         <v>1199.98</v>
       </c>
-      <c r="E276" s="16" t="n"/>
-      <c r="F276" s="17" t="n"/>
-      <c r="G276" s="18" t="n">
+      <c r="E276" s="3" t="n"/>
+      <c r="F276" s="4" t="n"/>
+      <c r="G276" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="H276" s="15" t="inlineStr">
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I276" s="6" t="n"/>
-      <c r="J276" s="19" t="inlineStr"/>
-      <c r="K276" s="20" t="inlineStr">
+      <c r="J276" s="7" t="inlineStr"/>
+      <c r="K276" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10573,37 +10556,37 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="15" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>T-1274</t>
         </is>
       </c>
-      <c r="B278" s="15" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>Waverly — velours gris — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C278" s="15" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D278" s="16" t="n">
+      <c r="D278" s="3" t="n">
         <v>1199.98</v>
       </c>
-      <c r="E278" s="16" t="n"/>
-      <c r="F278" s="17" t="n"/>
-      <c r="G278" s="18" t="n">
+      <c r="E278" s="3" t="n"/>
+      <c r="F278" s="4" t="n"/>
+      <c r="G278" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="H278" s="15" t="inlineStr">
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I278" s="6" t="n"/>
-      <c r="J278" s="19" t="inlineStr"/>
-      <c r="K278" s="20" t="inlineStr">
+      <c r="J278" s="7" t="inlineStr"/>
+      <c r="K278" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10647,37 +10630,37 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="15" t="inlineStr">
+      <c r="A280" s="2" t="inlineStr">
         <is>
           <t>T-1415</t>
         </is>
       </c>
-      <c r="B280" s="15" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>Meuble Boyer — métal gris — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C280" s="15" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D280" s="16" t="n">
+      <c r="D280" s="3" t="n">
         <v>899.98</v>
       </c>
-      <c r="E280" s="16" t="n"/>
-      <c r="F280" s="17" t="n"/>
-      <c r="G280" s="18" t="n">
+      <c r="E280" s="3" t="n"/>
+      <c r="F280" s="4" t="n"/>
+      <c r="G280" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="H280" s="15" t="inlineStr">
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I280" s="6" t="n"/>
-      <c r="J280" s="19" t="inlineStr"/>
-      <c r="K280" s="20" t="inlineStr">
+      <c r="J280" s="7" t="inlineStr"/>
+      <c r="K280" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10721,37 +10704,37 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="15" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>T-1811 / C-1826</t>
         </is>
       </c>
-      <c r="B282" s="15" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>Christophe — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C282" s="15" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D282" s="16" t="n">
+      <c r="D282" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E282" s="16" t="n"/>
-      <c r="F282" s="17" t="n"/>
-      <c r="G282" s="18" t="n">
+      <c r="E282" s="3" t="n"/>
+      <c r="F282" s="4" t="n"/>
+      <c r="G282" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="H282" s="15" t="inlineStr">
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I282" s="6" t="n"/>
-      <c r="J282" s="19" t="inlineStr"/>
-      <c r="K282" s="20" t="inlineStr">
+      <c r="J282" s="7" t="inlineStr"/>
+      <c r="K282" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10795,37 +10778,37 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="15" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
         <is>
           <t>T-1510</t>
         </is>
       </c>
-      <c r="B284" s="15" t="inlineStr">
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>Meuble Beaubien — tissu gris — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C284" s="15" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D284" s="16" t="n">
+      <c r="D284" s="3" t="n">
         <v>439.98</v>
       </c>
-      <c r="E284" s="16" t="n"/>
-      <c r="F284" s="17" t="n"/>
-      <c r="G284" s="18" t="n">
+      <c r="E284" s="3" t="n"/>
+      <c r="F284" s="4" t="n"/>
+      <c r="G284" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H284" s="15" t="inlineStr">
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I284" s="6" t="n"/>
-      <c r="J284" s="19" t="inlineStr"/>
-      <c r="K284" s="20" t="inlineStr">
+      <c r="J284" s="7" t="inlineStr"/>
+      <c r="K284" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10869,37 +10852,37 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="15" t="inlineStr">
+      <c r="A286" s="2" t="inlineStr">
         <is>
           <t>T-1510</t>
         </is>
       </c>
-      <c r="B286" s="15" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>Meuble Fabre — velours beige — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C286" s="15" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D286" s="16" t="n">
+      <c r="D286" s="3" t="n">
         <v>439.98</v>
       </c>
-      <c r="E286" s="16" t="n"/>
-      <c r="F286" s="17" t="n"/>
-      <c r="G286" s="18" t="n">
+      <c r="E286" s="3" t="n"/>
+      <c r="F286" s="4" t="n"/>
+      <c r="G286" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H286" s="15" t="inlineStr">
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I286" s="6" t="n"/>
-      <c r="J286" s="19" t="inlineStr"/>
-      <c r="K286" s="20" t="inlineStr">
+      <c r="J286" s="7" t="inlineStr"/>
+      <c r="K286" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -10943,37 +10926,37 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="15" t="inlineStr">
+      <c r="A288" s="2" t="inlineStr">
         <is>
           <t>T-1449 &amp; C-1712</t>
         </is>
       </c>
-      <c r="B288" s="15" t="inlineStr">
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>Saint-Urbain — bois gris — Tables de salle à manger</t>
         </is>
       </c>
-      <c r="C288" s="15" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
         <is>
           <t>Tables de salle à manger</t>
         </is>
       </c>
-      <c r="D288" s="16" t="n">
+      <c r="D288" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E288" s="16" t="n"/>
-      <c r="F288" s="17" t="n"/>
-      <c r="G288" s="18" t="n">
+      <c r="E288" s="3" t="n"/>
+      <c r="F288" s="4" t="n"/>
+      <c r="G288" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H288" s="15" t="inlineStr">
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I288" s="6" t="n"/>
-      <c r="J288" s="19" t="inlineStr"/>
-      <c r="K288" s="20" t="inlineStr">
+      <c r="J288" s="7" t="inlineStr"/>
+      <c r="K288" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -11017,41 +11000,41 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="15" t="inlineStr">
+      <c r="A290" s="2" t="inlineStr">
         <is>
           <t>IF-3530</t>
         </is>
       </c>
-      <c r="B290" s="15" t="inlineStr">
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>Table basse moderne — Blanc</t>
         </is>
       </c>
-      <c r="C290" s="15" t="inlineStr">
+      <c r="C290" s="2" t="inlineStr">
         <is>
           <t>Tables de salon</t>
         </is>
       </c>
-      <c r="D290" s="16" t="n">
+      <c r="D290" s="3" t="n">
         <v>239.98</v>
       </c>
-      <c r="E290" s="16" t="n">
+      <c r="E290" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F290" s="17" t="n">
+      <c r="F290" s="4" t="n">
         <v>-8.333333333337597e-05</v>
       </c>
-      <c r="G290" s="18" t="n">
+      <c r="G290" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H290" s="15" t="inlineStr">
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I290" s="6" t="n"/>
-      <c r="J290" s="19" t="inlineStr"/>
-      <c r="K290" s="20" t="inlineStr">
+      <c r="J290" s="7" t="inlineStr"/>
+      <c r="K290" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -11095,41 +11078,41 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="15" t="inlineStr">
+      <c r="A292" s="2" t="inlineStr">
         <is>
           <t>IF-2631</t>
         </is>
       </c>
-      <c r="B292" s="15" t="inlineStr">
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>Table basse</t>
         </is>
       </c>
-      <c r="C292" s="15" t="inlineStr">
+      <c r="C292" s="2" t="inlineStr">
         <is>
           <t>Tables de salon</t>
         </is>
       </c>
-      <c r="D292" s="16" t="n">
+      <c r="D292" s="3" t="n">
         <v>199.98</v>
       </c>
-      <c r="E292" s="16" t="n">
+      <c r="E292" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="F292" s="17" t="n">
+      <c r="F292" s="4" t="n">
         <v>0.3331999999999999</v>
       </c>
-      <c r="G292" s="18" t="n">
+      <c r="G292" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H292" s="15" t="inlineStr">
+      <c r="H292" s="2" t="inlineStr">
         <is>
           <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I292" s="6" t="n"/>
-      <c r="J292" s="19" t="inlineStr"/>
-      <c r="K292" s="20" t="inlineStr">
+      <c r="J292" s="7" t="inlineStr"/>
+      <c r="K292" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -11488,7 +11471,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Révision des prix — Meuble Confort &amp; Style</t>
         </is>

--- a/web/exports/revision-prix.xlsx
+++ b/web/exports/revision-prix.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K293"/>
+  <dimension ref="A1:K294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
       <c r="A3" s="9" t="inlineStr"/>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Bureau Outremont — métal noir</t>
+          <t>Bureau - Espresso De Coin Cote Droit</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -769,7 +769,7 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bureau Christophe — bois gris</t>
+          <t>Bureau - Gris / Metal Noir En</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ATlas — Canapé</t>
+          <t>Atlas — Canapé</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>(Fabric-Power)</t>
+          <t>Canapé Ahuntsic — tissu gris</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -924,18 +924,14 @@
       <c r="D12" s="3" t="n">
         <v>1999.98</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.99998</v>
-      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="4" t="n"/>
       <c r="G12" s="5" t="n">
         <v>56</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -1211,10 +1207,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>IF 8120</t>
+        </is>
+      </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Volta — Canapé</t>
+          <t>Canapé Casgrain — cuir noir</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1223,12 +1223,12 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1740</v>
+        <v>1799.98</v>
       </c>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Nexo — Canapé</t>
+          <t>Volta — Canapé</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>980</v>
+        <v>1740</v>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1277,10 +1277,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Milo — Canapé</t>
+          <t>Canapé Christophe — velours noir</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1289,12 +1293,12 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>980</v>
+        <v>1159.98</v>
       </c>
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -1310,14 +1314,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir — Canapé</t>
+          <t>Sofa Lit - 8A14L83</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1326,16 +1326,20 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="4" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I24" s="6" t="n"/>
@@ -1350,7 +1354,7 @@
       <c r="A25" s="9" t="inlineStr"/>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Hudson — Canapé</t>
+          <t>Sofa Lit</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1359,16 +1363,20 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>860</v>
-      </c>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="11" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I25" s="6" t="n"/>
@@ -1383,7 +1391,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Depot — Canapé</t>
+          <t>Sofa Lit — Brun</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1392,16 +1400,20 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>860</v>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="4" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I26" s="6" t="n"/>
@@ -1416,7 +1428,7 @@
       <c r="A27" s="9" t="inlineStr"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Clarence — Canapé</t>
+          <t>Sofa Lit (2)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1425,16 +1437,20 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>840</v>
-      </c>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="11" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I27" s="6" t="n"/>
@@ -1446,14 +1462,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Canapé</t>
+          <t>Sofa Lit — Gris</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1462,16 +1474,20 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="4" t="n"/>
+        <v>1050</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G28" s="5" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I28" s="6" t="n"/>
@@ -1483,14 +1499,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>IF-8012</t>
-        </is>
-      </c>
+      <c r="A29" s="9" t="inlineStr"/>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige — Canapé</t>
+          <t>Sofa-Lit</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1499,16 +1511,20 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>459.98</v>
-      </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="11" t="n"/>
+        <v>999</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I29" s="6" t="n"/>
@@ -1523,21 +1539,21 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Prestige — Causeuse</t>
+          <t>Nexo — Canapé</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2000</v>
+        <v>980</v>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="5" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1556,21 +1572,21 @@
       <c r="A31" s="9" t="inlineStr"/>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Elite — Causeuse</t>
+          <t>Milo — Canapé</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1700</v>
+        <v>980</v>
       </c>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="12" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
@@ -1586,24 +1602,28 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>IF-8012</t>
+        </is>
+      </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Royal — Causeuse</t>
+          <t>Canapé Chabanel — cuir beige</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1700</v>
+        <v>980</v>
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1622,21 +1642,21 @@
       <c r="A33" s="9" t="inlineStr"/>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Véga — Causeuse</t>
+          <t>Hudson — Canapé</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1700</v>
+        <v>860</v>
       </c>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="12" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -1655,21 +1675,21 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Opéra — Causeuse</t>
+          <t>Depot — Canapé</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1700</v>
+        <v>860</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="5" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1688,21 +1708,21 @@
       <c r="A35" s="9" t="inlineStr"/>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Sérénity — Causeuse</t>
+          <t>Clarence — Canapé</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Causeuses</t>
+          <t>Canapés</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1700</v>
+        <v>840</v>
       </c>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="12" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -1721,7 +1741,7 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Nuvola — Causeuse</t>
+          <t>Prestige — Causeuse</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1730,12 +1750,12 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1754,7 +1774,7 @@
       <c r="A37" s="9" t="inlineStr"/>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>ATlas — Causeuse</t>
+          <t>Elite — Causeuse</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -1763,12 +1783,12 @@
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1560</v>
+        <v>1700</v>
       </c>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="11" t="n"/>
       <c r="G37" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -1787,7 +1807,7 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Nexus — Causeuse</t>
+          <t>Royal — Causeuse</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1796,12 +1816,12 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -1820,7 +1840,7 @@
       <c r="A39" s="9" t="inlineStr"/>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Skyline — Causeuse</t>
+          <t>Véga — Causeuse</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -1829,12 +1849,12 @@
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="11" t="n"/>
       <c r="G39" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -1853,7 +1873,7 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Zénith — Causeuse</t>
+          <t>Opéra — Causeuse</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1862,12 +1882,12 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -1886,7 +1906,7 @@
       <c r="A41" s="9" t="inlineStr"/>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Volta — Causeuse</t>
+          <t>Sérénity — Causeuse</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1895,12 +1915,12 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -1919,7 +1939,7 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Nexo — Causeuse</t>
+          <t>Nuvola — Causeuse</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1928,12 +1948,12 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>760</v>
+        <v>1700</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="5" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -1952,7 +1972,7 @@
       <c r="A43" s="9" t="inlineStr"/>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Milo — Causeuse</t>
+          <t>Atlas — Causeuse</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -1961,12 +1981,12 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>760</v>
+        <v>1560</v>
       </c>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="11" t="n"/>
       <c r="G43" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -1982,14 +2002,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Causeuse</t>
+          <t>Nexus — Causeuse</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1998,12 +2014,12 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="5" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2038,7 @@
       <c r="A45" s="9" t="inlineStr"/>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Hudson — Causeuse</t>
+          <t>Skyline — Causeuse</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -2031,12 +2047,12 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>660</v>
+        <v>1500</v>
       </c>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="12" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -2055,7 +2071,7 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Clarence — Causeuse</t>
+          <t>Zénith — Causeuse</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2064,12 +2080,12 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>660</v>
+        <v>1500</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2088,7 +2104,7 @@
       <c r="A47" s="9" t="inlineStr"/>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Depot — Causeuse</t>
+          <t>Volta — Causeuse</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -2097,12 +2113,12 @@
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>660</v>
+        <v>1400</v>
       </c>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="12" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
@@ -2120,12 +2136,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IF-8012</t>
+          <t>IF-8007</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige — Causeuse</t>
+          <t>Canapé Christophe — velours noir — Causeuse</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2134,12 +2150,12 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>459.98</v>
+        <v>940</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2158,21 +2174,21 @@
       <c r="A49" s="9" t="inlineStr"/>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Nexo — Chaise</t>
+          <t>Nexo — Causeuse</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>460</v>
+        <v>760</v>
       </c>
       <c r="E49" s="10" t="n"/>
       <c r="F49" s="11" t="n"/>
       <c r="G49" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
@@ -2188,36 +2204,28 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>C-1285</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Chaise Casgrain — velours beige</t>
+          <t>Milo — Causeuse</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="4" t="n"/>
       <c r="G50" s="5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I50" s="6" t="n"/>
@@ -2231,34 +2239,30 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>C-1453</t>
+          <t>IF-8012</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Chaise en velours crème — Beige (2)</t>
+          <t>Canapé Chabanel — cuir beige — Causeuse</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>0.1538461538461539</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="11" t="n"/>
       <c r="G51" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I51" s="6" t="n"/>
@@ -2270,36 +2274,28 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>C-1263</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Chaise cadre chrome poli</t>
+          <t>Hudson — Causeuse</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="4" t="n"/>
       <c r="G52" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I52" s="6" t="n"/>
@@ -2311,28 +2307,24 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>T-1275</t>
-        </is>
-      </c>
+      <c r="A53" s="9" t="inlineStr"/>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Gaspé — velours beige — Chaise</t>
+          <t>Clarence — Causeuse</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="11" t="n"/>
       <c r="G53" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
@@ -2348,28 +2340,24 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>T-1274</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Casgrain — velours gris — Chaise</t>
+          <t>Depot — Causeuse</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Chaises</t>
+          <t>Causeuses</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2387,12 +2375,12 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>C-1285</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Waverly — velours gris — Chaise</t>
+          <t>Chaise Casgrain — velours beige</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -2401,16 +2389,20 @@
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>290</v>
-      </c>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="11" t="n"/>
+        <v>350</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I55" s="6" t="n"/>
@@ -2422,10 +2414,14 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>C-1253</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Monaco Dining Set — Chaise</t>
+          <t>Chaise en velours crème — Beige</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2434,16 +2430,20 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="4" t="n"/>
+        <v>340</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I56" s="6" t="n"/>
@@ -2455,10 +2455,14 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr"/>
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>C-1453</t>
+        </is>
+      </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Chaise en pattes chromées</t>
+          <t>Chaise en velours crème — Beige (2)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -2467,20 +2471,20 @@
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>260</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I57" s="6" t="n"/>
@@ -2492,10 +2496,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>C-1263</t>
+        </is>
+      </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chaise avec pattes chromées</t>
+          <t>Chaise cadre chrome poli</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2504,20 +2512,20 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I58" s="6" t="n"/>
@@ -2531,12 +2539,12 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>T-1402</t>
+          <t>T-1275</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris — Chaise</t>
+          <t>Gaspé — velours beige — Chaise</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -2545,12 +2553,12 @@
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="E59" s="10" t="n"/>
       <c r="F59" s="11" t="n"/>
       <c r="G59" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
@@ -2568,12 +2576,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>C-1546</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Chaise moderne</t>
+          <t>Casgrain — velours gris — Chaise</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2582,20 +2590,16 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="4" t="n"/>
       <c r="G60" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I60" s="6" t="n"/>
@@ -2609,12 +2613,12 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>T-1545</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Meuble Iberville — métal noir — Chaise</t>
+          <t>Waverly — velours gris — Chaise</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -2623,12 +2627,12 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="E61" s="10" t="n"/>
       <c r="F61" s="11" t="n"/>
       <c r="G61" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
@@ -2644,14 +2648,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>T-1811 / C-1835</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Drolet — Chaise</t>
+          <t>Monaco Dining Set — Chaise</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -2681,14 +2681,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>T-1811 / C-1826</t>
-        </is>
-      </c>
+      <c r="A63" s="9" t="inlineStr"/>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Christophe — Chaise</t>
+          <t>Chaise en pattes chromées</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -2697,16 +2693,20 @@
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>170</v>
-      </c>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="11" t="n"/>
+        <v>260</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G63" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I63" s="6" t="n"/>
@@ -2718,14 +2718,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>C-1416</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Chaise moderne en PU</t>
+          <t>Chaise avec pattes chromées</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2734,20 +2730,20 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.07142857142857142</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I64" s="6" t="n"/>
@@ -2761,12 +2757,12 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>T-1415</t>
+          <t>T-1402</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris — Chaise</t>
+          <t>Chaise Christophe — métal gris</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -2775,12 +2771,12 @@
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E65" s="10" t="n"/>
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
@@ -2798,12 +2794,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>C-1541</t>
+          <t>C-1546</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Chaise moderne en PU gris</t>
+          <t>Chaise moderne</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2812,16 +2808,16 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -2839,12 +2835,12 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Meuble Beaubien — tissu gris — Chaise</t>
+          <t>Iberville — métal noir — Chaise</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -2853,12 +2849,12 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="E67" s="10" t="n"/>
       <c r="F67" s="11" t="n"/>
       <c r="G67" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -2876,12 +2872,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1811 / C-1835</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Meuble Papineau — tissu gris — Chaise</t>
+          <t>Drolet — Chaise</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2890,12 +2886,12 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -2913,12 +2909,12 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1811 / C-1826</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Meuble Fabre — velours beige — Chaise</t>
+          <t>Christophe — Chaise</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -2927,12 +2923,12 @@
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="11" t="n"/>
       <c r="G69" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
@@ -2950,12 +2946,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>T-1540</t>
+          <t>C-1416</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Meuble Chabanel — métal gris — Chaise</t>
+          <t>Chaise moderne en PU</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2964,16 +2960,20 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="4" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
       <c r="G70" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I70" s="6" t="n"/>
@@ -2987,12 +2987,12 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>T-1079 / C-1084</t>
+          <t>T-1415</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Gaspé — tissu gris — Chaise</t>
+          <t>Boyer — métal gris — Chaise</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -3001,12 +3001,12 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>C-1541</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Marquette — verre blanc — Chaise</t>
+          <t>Chaise moderne en PU gris</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3038,16 +3038,20 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="4" t="n"/>
+        <v>145</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I72" s="6" t="n"/>
@@ -3061,12 +3065,12 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>T-1449 &amp; C-1712</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Saint-Urbain — bois gris — Chaise</t>
+          <t>Beaubien — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -3075,12 +3079,12 @@
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
@@ -3096,32 +3100,32 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>New York D/M – Commode avec miroir</t>
+          <t>Papineau — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1660</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>1660</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="4" t="n"/>
       <c r="G74" s="5" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I74" s="6" t="n"/>
@@ -3133,24 +3137,28 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr"/>
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Commode</t>
+          <t>Fabre — velours beige — Chaise</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>1030</v>
+        <v>145</v>
       </c>
       <c r="E75" s="10" t="n"/>
       <c r="F75" s="11" t="n"/>
       <c r="G75" s="12" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
@@ -3166,24 +3174,28 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>T-1540</t>
+        </is>
+      </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Commode</t>
+          <t>Chabanel — métal gris — Chaise</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>800</v>
+        <v>145</v>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="5" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3199,24 +3211,28 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr"/>
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>T-1079 / C-1084</t>
+        </is>
+      </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Commode</t>
+          <t>Gaspé — tissu gris — Chaise</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>720</v>
+        <v>115</v>
       </c>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="11" t="n"/>
       <c r="G77" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
@@ -3232,24 +3248,28 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>T-1442 / C-1878</t>
+        </is>
+      </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Commode</t>
+          <t>Marquette — verre blanc — Chaise</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>720</v>
+        <v>100</v>
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3265,24 +3285,28 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr"/>
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>T-1449 &amp; C-1712</t>
+        </is>
+      </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Amelia-Black — Commode</t>
+          <t>Saint-Urbain — bois gris — Chaise</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Commodes</t>
+          <t>Chaises</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -3301,7 +3325,7 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Madisson 100 — Commode</t>
+          <t>New York D/M – Commode avec miroir</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3310,16 +3334,20 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="4" t="n"/>
+        <v>1660</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1660</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" s="5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I80" s="6" t="n"/>
@@ -3334,7 +3362,7 @@
       <c r="A81" s="9" t="inlineStr"/>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Dylan — Commode</t>
+          <t>Harper "Seville" — Commode</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -3343,12 +3371,12 @@
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>580</v>
+        <v>1030</v>
       </c>
       <c r="E81" s="10" t="n"/>
       <c r="F81" s="11" t="n"/>
       <c r="G81" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -3367,7 +3395,7 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Commode</t>
+          <t>Chambre Moderne Blanche — Commode</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3376,12 +3404,12 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>530</v>
+        <v>800</v>
       </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3428,7 @@
       <c r="A83" s="9" t="inlineStr"/>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Commode</t>
+          <t>Ava Jordyn – Gris — Commode</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -3409,12 +3437,12 @@
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>520</v>
+        <v>720</v>
       </c>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="11" t="n"/>
       <c r="G83" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
@@ -3433,7 +3461,7 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Commode</t>
+          <t>Jordyn – Blanc — Commode</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3442,12 +3470,12 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>460</v>
+        <v>720</v>
       </c>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3466,7 +3494,7 @@
       <c r="A85" s="9" t="inlineStr"/>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Olivia “Austin — Commode</t>
+          <t>Amelia-Black — Commode</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -3475,12 +3503,12 @@
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="11" t="n"/>
       <c r="G85" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
@@ -3496,36 +3524,28 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>T-1442</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Meuble Cartier — verre gris</t>
+          <t>Madisson 100 — Commode</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>999.98</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>-1.999999999998181e-05</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="4" t="n"/>
       <c r="G86" s="5" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I86" s="6" t="n"/>
@@ -3540,29 +3560,25 @@
       <c r="A87" s="9" t="inlineStr"/>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Vase décoratif circulaire noir – Design moderne</t>
+          <t>Dylan — Commode</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Décoration</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>45.99</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>45.99</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="11" t="n"/>
       <c r="G87" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I87" s="6" t="n"/>
@@ -3577,29 +3593,25 @@
       <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche</t>
+          <t>Pompéi – Gris métallisé — Commode</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>370</v>
-      </c>
-      <c r="F88" s="4" t="n">
-        <v>12.51351351351351</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="4" t="n"/>
       <c r="G88" s="5" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
@@ -3614,29 +3626,25 @@
       <c r="A89" s="9" t="inlineStr"/>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris</t>
+          <t>Lucia — Blanc — Commode</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="F89" s="11" t="n">
-        <v>11</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="11" t="n"/>
       <c r="G89" s="12" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I89" s="6" t="n"/>
@@ -3651,29 +3659,25 @@
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc</t>
+          <t>Luna Riley – Finition argentée — Commode</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="F90" s="4" t="n">
-        <v>11</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="4" t="n"/>
       <c r="G90" s="5" t="n">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I90" s="6" t="n"/>
@@ -3688,29 +3692,25 @@
       <c r="A91" s="9" t="inlineStr"/>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Logan – Silver</t>
+          <t>Olivia “Austin — Commode</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Commodes</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>880</v>
-      </c>
-      <c r="F91" s="11" t="n">
-        <v>2.636363636363636</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="11" t="n"/>
       <c r="G91" s="12" t="n">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I91" s="6" t="n"/>
@@ -3725,25 +3725,25 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Amelia-Black</t>
+          <t>SOFIA – Pillow Top | Série Cuivre</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Décoration</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3000</v>
+        <v>920</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>370</v>
+        <v>920</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>7.108108108108108</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -3762,25 +3762,25 @@
       <c r="A93" s="9" t="inlineStr"/>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé</t>
+          <t>Vase décoratif circulaire noir – Design moderne</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de chambre</t>
+          <t>Décoration</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>2500</v>
+        <v>45.99</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>240</v>
+        <v>45.99</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>9.416666666666666</v>
+        <v>0</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Madisson 100</t>
+          <t>Chambre Moderne Blanche</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>2299.98</v>
+        <v>5000</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>220</v>
+        <v>370</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>9.454454545454546</v>
+        <v>12.51351351351351</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
       <c r="A95" s="9" t="inlineStr"/>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Ava Jordyn – Gris</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -3845,16 +3845,16 @@
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>2200</v>
+        <v>4200</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>9.476190476190476</v>
+        <v>11</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Harper "Seville"</t>
+          <t>Jordyn – Blanc</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3882,16 +3882,16 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>2015</v>
+        <v>4200</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>6.070175438596491</v>
+        <v>11</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
       <c r="A97" s="9" t="inlineStr"/>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée</t>
+          <t>Logan – Silver</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -3919,16 +3919,16 @@
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>1999</v>
+        <v>3200</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>220</v>
+        <v>880</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>8.086363636363636</v>
+        <v>2.636363636363636</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Olivia “Austin</t>
+          <t>Amelia-Black</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3956,16 +3956,16 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>1920</v>
+        <v>3000</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>8.142857142857142</v>
+        <v>7.108108108108108</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       <c r="A99" s="9" t="inlineStr"/>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Lit Queen / Chene Rustique / Tiroir</t>
+          <t>Pompéi – Gris métallisé</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -3993,16 +3993,16 @@
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1828</v>
+        <v>2500</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1828</v>
+        <v>240</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0</v>
+        <v>9.416666666666666</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lit Queen avec Rangement</t>
+          <t>Madisson 100</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4030,16 +4030,16 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>1828</v>
+        <v>2299.98</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>1828</v>
+        <v>220</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0</v>
+        <v>9.454454545454546</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       <c r="A101" s="9" t="inlineStr"/>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Lit Queen / Beige / Chene Gris</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -4067,16 +4067,16 @@
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>1608</v>
+        <v>2200</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>1608</v>
+        <v>210</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0</v>
+        <v>9.476190476190476</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
@@ -4092,14 +4092,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>I-5230Q</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Chambre</t>
+          <t>Harper "Seville"</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4108,16 +4104,16 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>1608</v>
+        <v>2015</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1608</v>
+        <v>285</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0</v>
+        <v>6.070175438596491</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4136,7 +4132,7 @@
       <c r="A103" s="9" t="inlineStr"/>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Luna Riley – Finition argentée</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -4145,16 +4141,16 @@
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>1320</v>
+        <v>1999</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>1320</v>
+        <v>220</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0</v>
+        <v>8.086363636363636</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
@@ -4173,7 +4169,7 @@
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Lucia — Blanc</t>
+          <t>Olivia “Austin</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4182,16 +4178,20 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="4" t="n"/>
+        <v>1920</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>8.142857142857142</v>
+      </c>
       <c r="G104" s="5" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I104" s="6" t="n"/>
@@ -4206,7 +4206,7 @@
       <c r="A105" s="9" t="inlineStr"/>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Chêne Blanchi Rustique</t>
+          <t>Lit Queen / Chene Rustique / Tiroir</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -4215,16 +4215,16 @@
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>1258</v>
+        <v>1828</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>1258</v>
+        <v>1828</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -4243,25 +4243,25 @@
       <c r="A106" s="2" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Monaco Dining Set</t>
+          <t>Lit Queen avec Rangement</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>2999.98</v>
+        <v>1828</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>270</v>
+        <v>1828</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.11103703703704</v>
+        <v>0</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4277,32 +4277,32 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>T-1274</t>
-        </is>
-      </c>
+      <c r="A107" s="9" t="inlineStr"/>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Casgrain — velours gris</t>
+          <t>Lit Queen / Beige / Chene Gris</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>2939.98</v>
-      </c>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="11" t="n"/>
+        <v>1608</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>1608</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G107" s="12" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I107" s="6" t="n"/>
@@ -4316,30 +4316,34 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>I-5230Q</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Waverly — velours gris</t>
+          <t>Ensemble Chambre</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>2939.98</v>
-      </c>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="4" t="n"/>
+        <v>1608</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>1608</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G108" s="5" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I108" s="6" t="n"/>
@@ -4351,36 +4355,32 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>IF-1620</t>
-        </is>
-      </c>
+      <c r="A109" s="9" t="inlineStr"/>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Meuble Drolet — tissu</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>2399.98</v>
+        <v>1320</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>2299.98</v>
+        <v>1320</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.04347863894468647</v>
+        <v>0</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I109" s="6" t="n"/>
@@ -4395,29 +4395,25 @@
       <c r="A110" s="2" t="inlineStr"/>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Table A Manger - Noyer Brun</t>
+          <t>Lucia — Blanc</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>1899.99</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>1899.99</v>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>1299</v>
+      </c>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="4" t="n"/>
       <c r="G110" s="5" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I110" s="6" t="n"/>
@@ -4429,32 +4425,32 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>T-1415</t>
-        </is>
-      </c>
+      <c r="A111" s="9" t="inlineStr"/>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris</t>
+          <t>Chêne Blanchi Rustique</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salle à manger</t>
+          <t>Ensembles de chambre</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>1799.98</v>
-      </c>
-      <c r="E111" s="10" t="n"/>
-      <c r="F111" s="11" t="n"/>
+        <v>1258</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>1258</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G111" s="12" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I111" s="6" t="n"/>
@@ -4466,14 +4462,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>T-1540</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="inlineStr"/>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Meuble Chabanel — métal gris</t>
+          <t>Monaco Dining Set</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4482,16 +4474,20 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>1539.98</v>
-      </c>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="4" t="n"/>
+        <v>2999.98</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>10.11103703703704</v>
+      </c>
       <c r="G112" s="5" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I112" s="6" t="n"/>
@@ -4505,12 +4501,12 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>T-1402</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris</t>
+          <t>Ensemble de salle à manger Casgrain — velours gris</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -4519,12 +4515,12 @@
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>1399.98</v>
+        <v>2940</v>
       </c>
       <c r="E113" s="10" t="n"/>
       <c r="F113" s="11" t="n"/>
       <c r="G113" s="12" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
@@ -4542,12 +4538,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>T-1811 / C-1835</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Drolet</t>
+          <t>Ensemble de salle à manger Waverly — velours gris</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4556,20 +4552,16 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1280</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="F114" s="4" t="n">
-        <v>6.529411764705882</v>
-      </c>
+        <v>2939.98</v>
+      </c>
+      <c r="E114" s="3" t="n"/>
+      <c r="F114" s="4" t="n"/>
       <c r="G114" s="5" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I114" s="6" t="n"/>
@@ -4583,12 +4575,12 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>T-1811 / C-1826</t>
+          <t>IF-1620</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Christophe</t>
+          <t>Ensemble de salle à manger Drolet — tissu</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -4597,20 +4589,20 @@
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>1280</v>
+        <v>2399.98</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>170</v>
+        <v>2299.98</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>6.529411764705882</v>
+        <v>0.04347863894468647</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I115" s="6" t="n"/>
@@ -4622,14 +4614,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>T-1545</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="inlineStr"/>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Meuble Iberville — métal noir</t>
+          <t>Table A Manger - Noyer Brun</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4638,16 +4626,20 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1099.98</v>
-      </c>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="4" t="n"/>
+        <v>1899.99</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G116" s="5" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I116" s="6" t="n"/>
@@ -4661,12 +4653,12 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>T-1415</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Marquette — verre blanc</t>
+          <t>Ensemble de salle à manger Boyer — métal gris</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -4675,12 +4667,12 @@
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>1000</v>
+        <v>1799.98</v>
       </c>
       <c r="E117" s="10" t="n"/>
       <c r="F117" s="11" t="n"/>
       <c r="G117" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
@@ -4698,12 +4690,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>T-1448</t>
+          <t>T-1540</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Meuble Lachine — verre beige</t>
+          <t>Ensemble de salle à manger Chabanel — métal gris</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4712,20 +4704,16 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>939.98</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F118" s="4" t="n">
-        <v>-0.5480865384615384</v>
-      </c>
+        <v>1539.98</v>
+      </c>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="4" t="n"/>
       <c r="G118" s="5" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I118" s="6" t="n"/>
@@ -4739,12 +4727,12 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>T-1449 &amp; C-1712</t>
+          <t>T-1402</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Saint-Urbain — bois gris</t>
+          <t>Ensemble Christophe — métal gris</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -4753,12 +4741,12 @@
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>699</v>
+        <v>1399.98</v>
       </c>
       <c r="E119" s="10" t="n"/>
       <c r="F119" s="11" t="n"/>
       <c r="G119" s="12" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
@@ -4776,12 +4764,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>T-1079 / C-1084</t>
+          <t>T-1811 / C-1835</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Ensemble de salle à manger Gaspé — tissu gris</t>
+          <t>Ensemble de salle à manger Drolet</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4790,16 +4778,20 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>660</v>
-      </c>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="4" t="n"/>
+        <v>1280</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>6.529411764705882</v>
+      </c>
       <c r="G120" s="5" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I120" s="6" t="n"/>
@@ -4813,12 +4805,12 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1811 / C-1826</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Meuble Beaubien — tissu gris</t>
+          <t>Ensemble de salle à manger Christophe</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
@@ -4827,16 +4819,20 @@
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>439.98</v>
-      </c>
-      <c r="E121" s="10" t="n"/>
-      <c r="F121" s="11" t="n"/>
+        <v>1280</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>6.529411764705882</v>
+      </c>
       <c r="G121" s="12" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I121" s="6" t="n"/>
@@ -4850,12 +4846,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Meuble Papineau — tissu gris</t>
+          <t>Ensemble de salle à manger Iberville — métal noir</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4864,12 +4860,12 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>439.98</v>
+        <v>1099.98</v>
       </c>
       <c r="E122" s="3" t="n"/>
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="5" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -4887,12 +4883,12 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1442 / C-1878</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Meuble Fabre — velours beige</t>
+          <t>Ensemble de salle à manger Marquette — verre blanc</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -4901,12 +4897,12 @@
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>439.98</v>
+        <v>1000</v>
       </c>
       <c r="E123" s="10" t="n"/>
       <c r="F123" s="11" t="n"/>
       <c r="G123" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
@@ -4924,12 +4920,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>IF-1056</t>
+          <t>T-1442</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Ensemble salle à manger 5 pièces</t>
+          <t>Ensemble de salle à manger Cartier — verre gris</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4938,16 +4934,16 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>399.98</v>
+        <v>999.98</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>0.1428000000000001</v>
+        <v>-1.999999999998181e-05</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -4963,10 +4959,14 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr"/>
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>T-1448</t>
+        </is>
+      </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Table et 4 chaises</t>
+          <t>Meuble Lachine — verre beige</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -4975,20 +4975,20 @@
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>299</v>
+        <v>939.98</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>299</v>
+        <v>2080</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>0</v>
+        <v>-0.5480865384615384</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I125" s="6" t="n"/>
@@ -5000,10 +5000,14 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>T-1449 &amp; C-1712</t>
+        </is>
+      </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Table et 4 chaises (2)</t>
+          <t>Ensemble de salle à manger Saint-Urbain — bois gris</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5012,20 +5016,16 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="4" t="n"/>
       <c r="G126" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I126" s="6" t="n"/>
@@ -5037,10 +5037,14 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr"/>
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>T-1079 / C-1084</t>
+        </is>
+      </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Table et 4 chaises (3)</t>
+          <t>Ensemble de salle à manger Gaspé — tissu gris</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -5049,20 +5053,16 @@
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="F127" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="E127" s="10" t="n"/>
+      <c r="F127" s="11" t="n"/>
       <c r="G127" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I127" s="6" t="n"/>
@@ -5074,32 +5074,32 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Ensemble de salle à manger Beaubien — tissu gris</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F128" s="4" t="n">
-        <v>3.666666666666667</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="4" t="n"/>
       <c r="G128" s="5" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I128" s="6" t="n"/>
@@ -5111,32 +5111,32 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr"/>
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Véga</t>
+          <t>Ensemble de salle à manger Papineau — tissu gris</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F129" s="11" t="n">
-        <v>3.666666666666667</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="11" t="n"/>
       <c r="G129" s="12" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I129" s="6" t="n"/>
@@ -5148,32 +5148,32 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>T-1510</t>
+        </is>
+      </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Nexus</t>
+          <t>Ensemble de salle à manger Fabre — velours beige</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F130" s="4" t="n">
-        <v>3.666666666666667</v>
-      </c>
+        <v>439.98</v>
+      </c>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="4" t="n"/>
       <c r="G130" s="5" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I130" s="6" t="n"/>
@@ -5185,32 +5185,36 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr"/>
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>IF-1056</t>
+        </is>
+      </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Zénith</t>
+          <t>Ensemble salle à manger 5 pièces</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>4200</v>
+        <v>399.98</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>20</v>
+        <v>0.1428000000000001</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I131" s="6" t="n"/>
@@ -5225,25 +5229,25 @@
       <c r="A132" s="2" t="inlineStr"/>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Sérénity</t>
+          <t>Table et 4 chaises</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>4200</v>
+        <v>299</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>900</v>
+        <v>299</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>3.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5259,32 +5263,32 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A133" s="9" t="inlineStr"/>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir</t>
+          <t>Table et 4 chaises (2)</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>4199.98</v>
-      </c>
-      <c r="E133" s="10" t="n"/>
-      <c r="F133" s="11" t="n"/>
+        <v>299</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>299</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G133" s="12" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I133" s="6" t="n"/>
@@ -5299,25 +5303,25 @@
       <c r="A134" s="2" t="inlineStr"/>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Table et 4 chaises (3)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Ensembles de salon</t>
+          <t>Ensembles de salle à manger</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>4000</v>
+        <v>299</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>900</v>
+        <v>299</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>3.444444444444445</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5336,7 +5340,7 @@
       <c r="A135" s="9" t="inlineStr"/>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Opéra</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -5345,16 +5349,16 @@
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E135" s="10" t="n">
         <v>900</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>3.444444444444445</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -5373,7 +5377,7 @@
       <c r="A136" s="2" t="inlineStr"/>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Skyline</t>
+          <t>Véga</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5382,16 +5386,16 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E136" s="3" t="n">
         <v>900</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>3.444444444444445</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5410,7 +5414,7 @@
       <c r="A137" s="9" t="inlineStr"/>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Nuvola</t>
+          <t>Nexus</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -5419,16 +5423,16 @@
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="E137" s="10" t="n">
         <v>900</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3.444444444444445</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
@@ -5447,7 +5451,7 @@
       <c r="A138" s="2" t="inlineStr"/>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Zénith</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5456,16 +5460,16 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>860</v>
+        <v>200</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>3.418604651162791</v>
+        <v>20</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -5481,14 +5485,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A139" s="9" t="inlineStr"/>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir</t>
+          <t>Sérénity</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -5497,16 +5497,20 @@
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>2599.98</v>
-      </c>
-      <c r="E139" s="10" t="n"/>
-      <c r="F139" s="11" t="n"/>
+        <v>4200</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>3.666666666666667</v>
+      </c>
       <c r="G139" s="12" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I139" s="6" t="n"/>
@@ -5518,10 +5522,14 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>IF 8120</t>
+        </is>
+      </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Ensemble Casgrain — cuir noir</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5530,20 +5538,16 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>460</v>
-      </c>
-      <c r="F140" s="4" t="n">
-        <v>3.782608695652174</v>
-      </c>
+        <v>4199.98</v>
+      </c>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="4" t="n"/>
       <c r="G140" s="5" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I140" s="6" t="n"/>
@@ -5555,14 +5559,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>IF-8012</t>
-        </is>
-      </c>
+      <c r="A141" s="9" t="inlineStr"/>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
@@ -5571,16 +5571,20 @@
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>2199.98</v>
-      </c>
-      <c r="E141" s="10" t="n"/>
-      <c r="F141" s="11" t="n"/>
+        <v>4000</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>3.444444444444445</v>
+      </c>
       <c r="G141" s="12" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I141" s="6" t="n"/>
@@ -5595,7 +5599,7 @@
       <c r="A142" s="2" t="inlineStr"/>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Opéra</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5604,16 +5608,16 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>2.75</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -5632,7 +5636,7 @@
       <c r="A143" s="9" t="inlineStr"/>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>Clarence</t>
+          <t>Skyline</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
@@ -5641,16 +5645,16 @@
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>2.6</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
@@ -5669,7 +5673,7 @@
       <c r="A144" s="2" t="inlineStr"/>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Depot</t>
+          <t>Nuvola</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5678,16 +5682,16 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>2.75</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -5706,25 +5710,29 @@
       <c r="A145" s="9" t="inlineStr"/>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>Prestige — Fauteuil</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>1550</v>
-      </c>
-      <c r="E145" s="10" t="n"/>
-      <c r="F145" s="11" t="n"/>
+        <v>3800</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>860</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>3.418604651162791</v>
+      </c>
       <c r="G145" s="12" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I145" s="6" t="n"/>
@@ -5738,34 +5746,30 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>IF-8162</t>
+          <t>IF-8007</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Fauteuil inclinable électrique</t>
+          <t>Ensemble Christophe — velours noir</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2599.98</v>
+      </c>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="4" t="n"/>
       <c r="G146" s="5" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I146" s="6" t="n"/>
@@ -5780,25 +5784,29 @@
       <c r="A147" s="9" t="inlineStr"/>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Elite — Fauteuil</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="E147" s="10" t="n"/>
-      <c r="F147" s="11" t="n"/>
+        <v>2200</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>460</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>3.782608695652174</v>
+      </c>
       <c r="G147" s="12" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I147" s="6" t="n"/>
@@ -5810,24 +5818,28 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>IF-8012</t>
+        </is>
+      </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Royal — Fauteuil</t>
+          <t>Ensemble Chabanel — cuir beige</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>900</v>
+        <v>2199.98</v>
       </c>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="4" t="n"/>
       <c r="G148" s="5" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -5846,25 +5858,29 @@
       <c r="A149" s="9" t="inlineStr"/>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Véga — Fauteuil</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="E149" s="10" t="n"/>
-      <c r="F149" s="11" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G149" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I149" s="6" t="n"/>
@@ -5879,25 +5895,29 @@
       <c r="A150" s="2" t="inlineStr"/>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Opéra — Fauteuil</t>
+          <t>Clarence</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E150" s="3" t="n"/>
-      <c r="F150" s="4" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>2.6</v>
+      </c>
       <c r="G150" s="5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I150" s="6" t="n"/>
@@ -5912,25 +5932,29 @@
       <c r="A151" s="9" t="inlineStr"/>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>Nexus — Fauteuil</t>
+          <t>Depot</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Fauteuils</t>
+          <t>Ensembles de salon</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="E151" s="10" t="n"/>
-      <c r="F151" s="11" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G151" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I151" s="6" t="n"/>
@@ -5945,7 +5969,7 @@
       <c r="A152" s="2" t="inlineStr"/>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Skyline — Fauteuil</t>
+          <t>Prestige — Fauteuil</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -5954,12 +5978,12 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="4" t="n"/>
       <c r="G152" s="5" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -5975,10 +5999,14 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="inlineStr"/>
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>IF-8030</t>
+        </is>
+      </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>Zénith — Fauteuil</t>
+          <t>Canapé Ahuntsic — tissu gris — Fauteuil</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
@@ -5987,12 +6015,12 @@
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E153" s="10" t="n"/>
       <c r="F153" s="11" t="n"/>
       <c r="G153" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
@@ -6008,10 +6036,14 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr"/>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>IF-8162</t>
+        </is>
+      </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Sérénity — Fauteuil</t>
+          <t>Fauteuil inclinable électrique</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -6022,14 +6054,18 @@
       <c r="D154" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E154" s="3" t="n"/>
-      <c r="F154" s="4" t="n"/>
+      <c r="E154" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G154" s="5" t="n">
         <v>25</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I154" s="6" t="n"/>
@@ -6044,7 +6080,7 @@
       <c r="A155" s="9" t="inlineStr"/>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>Nuvola — Fauteuil</t>
+          <t>Elite — Fauteuil</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -6074,14 +6110,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>IF 8120</t>
-        </is>
-      </c>
+      <c r="A156" s="2" t="inlineStr"/>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Canapé Casgrain — cuir noir — Fauteuil</t>
+          <t>Royal — Fauteuil</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -6114,7 +6146,7 @@
       <c r="A157" s="9" t="inlineStr"/>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>Volta — Fauteuil</t>
+          <t>Véga — Fauteuil</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -6123,12 +6155,12 @@
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="E157" s="10" t="n"/>
       <c r="F157" s="11" t="n"/>
       <c r="G157" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
@@ -6144,14 +6176,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A158" s="2" t="inlineStr"/>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Fauteuil</t>
+          <t>Opéra — Fauteuil</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -6160,12 +6188,12 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6184,7 +6212,7 @@
       <c r="A159" s="9" t="inlineStr"/>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>Clarence — Fauteuil</t>
+          <t>Nexus — Fauteuil</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -6193,12 +6221,12 @@
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E159" s="10" t="n"/>
       <c r="F159" s="11" t="n"/>
       <c r="G159" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
@@ -6217,7 +6245,7 @@
       <c r="A160" s="2" t="inlineStr"/>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Fauteuil-Lit Convertible</t>
+          <t>Skyline — Fauteuil</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -6226,20 +6254,16 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>499</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>499</v>
-      </c>
-      <c r="F160" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="4" t="n"/>
       <c r="G160" s="5" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I160" s="6" t="n"/>
@@ -6254,7 +6278,7 @@
       <c r="A161" s="9" t="inlineStr"/>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Hudson — Fauteuil</t>
+          <t>Zénith — Fauteuil</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -6263,12 +6287,12 @@
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="E161" s="10" t="n"/>
       <c r="F161" s="11" t="n"/>
       <c r="G161" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
@@ -6287,7 +6311,7 @@
       <c r="A162" s="2" t="inlineStr"/>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Depot — Fauteuil</t>
+          <t>Sérénity — Fauteuil</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -6296,12 +6320,12 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="E162" s="3" t="n"/>
       <c r="F162" s="4" t="n"/>
       <c r="G162" s="5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -6320,7 +6344,7 @@
       <c r="A163" s="9" t="inlineStr"/>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Milo — Fauteuil</t>
+          <t>Nuvola — Fauteuil</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -6329,12 +6353,12 @@
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>460</v>
+        <v>900</v>
       </c>
       <c r="E163" s="10" t="n"/>
       <c r="F163" s="11" t="n"/>
       <c r="G163" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
@@ -6352,12 +6376,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>IF-8012</t>
+          <t>IF 8120</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Canapé Chabanel — cuir beige — Fauteuil</t>
+          <t>Canapé Casgrain — cuir noir — Fauteuil</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6366,12 +6390,12 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>459.98</v>
+        <v>900</v>
       </c>
       <c r="E164" s="3" t="n"/>
       <c r="F164" s="4" t="n"/>
       <c r="G164" s="5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -6390,21 +6414,21 @@
       <c r="A165" s="9" t="inlineStr"/>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Lit</t>
+          <t>Volta — Fauteuil</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>1800</v>
+        <v>860</v>
       </c>
       <c r="E165" s="10" t="n"/>
       <c r="F165" s="11" t="n"/>
       <c r="G165" s="12" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
@@ -6420,24 +6444,28 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Lit</t>
+          <t>Canapé Christophe — velours noir — Fauteuil</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="E166" s="3" t="n"/>
       <c r="F166" s="4" t="n"/>
       <c r="G166" s="5" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -6456,21 +6484,21 @@
       <c r="A167" s="9" t="inlineStr"/>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Lit</t>
+          <t>Clarence — Fauteuil</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="E167" s="10" t="n"/>
       <c r="F167" s="11" t="n"/>
       <c r="G167" s="12" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
@@ -6486,36 +6514,32 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>IF-5793</t>
-        </is>
-      </c>
+      <c r="A168" s="2" t="inlineStr"/>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Lit plateforme — Noir</t>
+          <t>Fauteuil-Lit Convertible</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>1259.98</v>
+        <v>499</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>0.2612412412412413</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I168" s="6" t="n"/>
@@ -6527,36 +6551,28 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>IF-5790</t>
-        </is>
-      </c>
+      <c r="A169" s="9" t="inlineStr"/>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Lit plateforme — Gris</t>
+          <t>Hudson — Fauteuil</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>1259.98</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>999</v>
-      </c>
-      <c r="F169" s="11" t="n">
-        <v>0.2612412412412413</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="E169" s="10" t="n"/>
+      <c r="F169" s="11" t="n"/>
       <c r="G169" s="12" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I169" s="6" t="n"/>
@@ -6568,36 +6584,28 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>IF-5792</t>
-        </is>
-      </c>
+      <c r="A170" s="2" t="inlineStr"/>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Lit plateforme — Beige</t>
+          <t>Depot — Fauteuil</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>1259.98</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>999</v>
-      </c>
-      <c r="F170" s="4" t="n">
-        <v>0.2612412412412413</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="4" t="n"/>
       <c r="G170" s="5" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I170" s="6" t="n"/>
@@ -6612,29 +6620,25 @@
       <c r="A171" s="9" t="inlineStr"/>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>velours gris avec ailes</t>
+          <t>Nexo — Fauteuil</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F171" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E171" s="10" t="n"/>
+      <c r="F171" s="11" t="n"/>
       <c r="G171" s="12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I171" s="6" t="n"/>
@@ -6646,36 +6650,28 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>IF-5120</t>
-        </is>
-      </c>
+      <c r="A172" s="2" t="inlineStr"/>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Lit contemporain en velours gris</t>
+          <t>Milo — Fauteuil</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>1099.98</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="F172" s="4" t="n">
-        <v>4.238</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="4" t="n"/>
       <c r="G172" s="5" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I172" s="6" t="n"/>
@@ -6689,34 +6685,30 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>IF-5940</t>
+          <t>IF-8012</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Lit moderne</t>
+          <t>Canapé Chabanel — cuir beige — Fauteuil</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>Lits</t>
+          <t>Fauteuils</t>
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>999.98</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F173" s="11" t="n">
-        <v>0.1110888888888889</v>
-      </c>
+        <v>459.98</v>
+      </c>
+      <c r="E173" s="10" t="n"/>
+      <c r="F173" s="11" t="n"/>
       <c r="G173" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I173" s="6" t="n"/>
@@ -6731,7 +6723,7 @@
       <c r="A174" s="2" t="inlineStr"/>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Madisson 100 — Lit</t>
+          <t>Ava Jordyn – Gris — Lit</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6740,12 +6732,12 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E174" s="3" t="n"/>
       <c r="F174" s="4" t="n"/>
       <c r="G174" s="5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -6764,7 +6756,7 @@
       <c r="A175" s="9" t="inlineStr"/>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Logan – Silver — Lit</t>
+          <t>Jordyn – Blanc — Lit</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -6773,12 +6765,12 @@
         </is>
       </c>
       <c r="D175" s="10" t="n">
-        <v>880</v>
+        <v>1800</v>
       </c>
       <c r="E175" s="10" t="n"/>
       <c r="F175" s="11" t="n"/>
       <c r="G175" s="12" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
@@ -6797,7 +6789,7 @@
       <c r="A176" s="2" t="inlineStr"/>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Lit plateforme moderne</t>
+          <t>Chambre Moderne Blanche — Lit</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6806,20 +6798,16 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>840</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>840</v>
-      </c>
-      <c r="F176" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="4" t="n"/>
       <c r="G176" s="5" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I176" s="6" t="n"/>
@@ -6833,12 +6821,12 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>IF-5565</t>
+          <t>IF-5793</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>Lit plateforme — Beige (2)</t>
+          <t>Lit plateforme — Noir</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -6847,16 +6835,16 @@
         </is>
       </c>
       <c r="D177" s="10" t="n">
-        <v>839.98</v>
+        <v>1259.98</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>840</v>
+        <v>999</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>-2.380952380950215e-05</v>
+        <v>0.2612412412412413</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
@@ -6874,12 +6862,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>IF-5560</t>
+          <t>IF-5790</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Lit Ahuntsic — velours gris</t>
+          <t>Lit plateforme — Gris</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6888,16 +6876,16 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>839.98</v>
+        <v>1259.98</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>840</v>
+        <v>999</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>-2.380952380950215e-05</v>
+        <v>0.2612412412412413</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -6913,10 +6901,14 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="inlineStr"/>
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>IF-5792</t>
+        </is>
+      </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Lit</t>
+          <t>Lit plateforme — Beige</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -6925,16 +6917,20 @@
         </is>
       </c>
       <c r="D179" s="10" t="n">
-        <v>720</v>
-      </c>
-      <c r="E179" s="10" t="n"/>
-      <c r="F179" s="11" t="n"/>
+        <v>1259.98</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>0.2612412412412413</v>
+      </c>
       <c r="G179" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I179" s="6" t="n"/>
@@ -6949,7 +6945,7 @@
       <c r="A180" s="2" t="inlineStr"/>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Lit</t>
+          <t>velours gris avec ailes</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6958,16 +6954,20 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="4" t="n"/>
+        <v>1100</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G180" s="5" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I180" s="6" t="n"/>
@@ -6979,10 +6979,14 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="inlineStr"/>
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>IF-5120</t>
+        </is>
+      </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Lit</t>
+          <t>Lit contemporain en velours gris</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -6991,16 +6995,20 @@
         </is>
       </c>
       <c r="D181" s="10" t="n">
-        <v>700</v>
-      </c>
-      <c r="E181" s="10" t="n"/>
-      <c r="F181" s="11" t="n"/>
+        <v>1099.98</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>4.238</v>
+      </c>
       <c r="G181" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I181" s="6" t="n"/>
@@ -7012,10 +7020,14 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr"/>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>IF-5940</t>
+        </is>
+      </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Lit avec rangement hydraulique</t>
+          <t>Lit moderne</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -7024,20 +7036,20 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>700</v>
+        <v>999.98</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0</v>
+        <v>0.1110888888888889</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I182" s="6" t="n"/>
@@ -7052,7 +7064,7 @@
       <c r="A183" s="9" t="inlineStr"/>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>Lit en Velours</t>
+          <t>Madisson 100 — Lit</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -7061,20 +7073,16 @@
         </is>
       </c>
       <c r="D183" s="10" t="n">
-        <v>699</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>699</v>
-      </c>
-      <c r="F183" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="E183" s="10" t="n"/>
+      <c r="F183" s="11" t="n"/>
       <c r="G183" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I183" s="6" t="n"/>
@@ -7089,7 +7097,7 @@
       <c r="A184" s="2" t="inlineStr"/>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Lit Velours Gris avec Rangement</t>
+          <t>Logan – Silver — Lit</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -7098,20 +7106,16 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>699</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>699</v>
-      </c>
-      <c r="F184" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="4" t="n"/>
       <c r="G184" s="5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I184" s="6" t="n"/>
@@ -7126,7 +7130,7 @@
       <c r="A185" s="9" t="inlineStr"/>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>Amelia-Black — Lit</t>
+          <t>Lit plateforme moderne</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -7135,16 +7139,20 @@
         </is>
       </c>
       <c r="D185" s="10" t="n">
-        <v>680</v>
-      </c>
-      <c r="E185" s="10" t="n"/>
-      <c r="F185" s="11" t="n"/>
+        <v>840</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>840</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G185" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I185" s="6" t="n"/>
@@ -7156,10 +7164,14 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr"/>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>IF-5565</t>
+        </is>
+      </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Lit Moderne Bas</t>
+          <t>Lit plateforme — Beige (2)</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -7168,20 +7180,20 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>650</v>
+        <v>839.98</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>650</v>
+        <v>840</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>0</v>
+        <v>-2.380952380950215e-05</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I186" s="6" t="n"/>
@@ -7193,10 +7205,14 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr"/>
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>IF-5560</t>
+        </is>
+      </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>Lit Wing en Velours Noir</t>
+          <t>Lit Ahuntsic — velours gris</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -7205,20 +7221,20 @@
         </is>
       </c>
       <c r="D187" s="10" t="n">
-        <v>650</v>
+        <v>839.98</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>650</v>
+        <v>840</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>0</v>
+        <v>-2.380952380950215e-05</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I187" s="6" t="n"/>
@@ -7233,7 +7249,7 @@
       <c r="A188" s="2" t="inlineStr"/>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Lit Papineau — tissu</t>
+          <t>Pompéi – Gris métallisé — Lit</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -7242,20 +7258,16 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="F188" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>720</v>
+      </c>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="4" t="n"/>
       <c r="G188" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I188" s="6" t="n"/>
@@ -7270,7 +7282,7 @@
       <c r="A189" s="9" t="inlineStr"/>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Lit</t>
+          <t>Harper "Seville" — Lit</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
@@ -7279,12 +7291,12 @@
         </is>
       </c>
       <c r="D189" s="10" t="n">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="E189" s="10" t="n"/>
       <c r="F189" s="11" t="n"/>
       <c r="G189" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
@@ -7300,14 +7312,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>IF-5295</t>
-        </is>
-      </c>
+      <c r="A190" s="2" t="inlineStr"/>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Lit plateforme — Gris (2)</t>
+          <t>Teddy Bear Blanc — Lit</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -7316,20 +7324,16 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>599.98</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>580</v>
-      </c>
-      <c r="F190" s="4" t="n">
-        <v>0.034448275862069</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E190" s="3" t="n"/>
+      <c r="F190" s="4" t="n"/>
       <c r="G190" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I190" s="6" t="n"/>
@@ -7344,7 +7348,7 @@
       <c r="A191" s="9" t="inlineStr"/>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>Lit avec tiroirs de rangement</t>
+          <t>Lit avec rangement hydraulique</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
@@ -7353,16 +7357,16 @@
         </is>
       </c>
       <c r="D191" s="10" t="n">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="F191" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
@@ -7381,7 +7385,7 @@
       <c r="A192" s="2" t="inlineStr"/>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Velours Dusty Pink</t>
+          <t>Lit en Velours</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -7390,16 +7394,16 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>575.99</v>
+        <v>699</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>575.99</v>
+        <v>699</v>
       </c>
       <c r="F192" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -7418,7 +7422,7 @@
       <c r="A193" s="9" t="inlineStr"/>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>Velours Bleu Royal</t>
+          <t>Lit Velours Gris avec Rangement</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
@@ -7427,16 +7431,16 @@
         </is>
       </c>
       <c r="D193" s="10" t="n">
-        <v>560</v>
+        <v>699</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>560</v>
+        <v>699</v>
       </c>
       <c r="F193" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
@@ -7455,7 +7459,7 @@
       <c r="A194" s="2" t="inlineStr"/>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Lit</t>
+          <t>Amelia-Black — Lit</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -7464,12 +7468,12 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="E194" s="3" t="n"/>
       <c r="F194" s="4" t="n"/>
       <c r="G194" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -7488,7 +7492,7 @@
       <c r="A195" s="9" t="inlineStr"/>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>Luxora LED Storage Bed</t>
+          <t>Lit Moderne Bas</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
@@ -7497,16 +7501,16 @@
         </is>
       </c>
       <c r="D195" s="10" t="n">
-        <v>559.98</v>
+        <v>650</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>559.98</v>
+        <v>650</v>
       </c>
       <c r="F195" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
@@ -7522,14 +7526,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>IF-5408</t>
-        </is>
-      </c>
+      <c r="A196" s="2" t="inlineStr"/>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Lit avec rangement</t>
+          <t>Lit Wing en Velours Noir</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -7538,20 +7538,20 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>539.98</v>
+        <v>650</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>520</v>
+        <v>650</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>0.03842307692307696</v>
+        <v>0</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I196" s="6" t="n"/>
@@ -7563,14 +7563,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="9" t="inlineStr">
-        <is>
-          <t>IF-5407</t>
-        </is>
-      </c>
+      <c r="A197" s="9" t="inlineStr"/>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>Lit Fabre — velours beige</t>
+          <t>Luna Riley – Finition argentée — Lit</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
@@ -7579,20 +7575,16 @@
         </is>
       </c>
       <c r="D197" s="10" t="n">
-        <v>539.98</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>520</v>
-      </c>
-      <c r="F197" s="11" t="n">
-        <v>0.03842307692307696</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="E197" s="10" t="n"/>
+      <c r="F197" s="11" t="n"/>
       <c r="G197" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I197" s="6" t="n"/>
@@ -7607,7 +7599,7 @@
       <c r="A198" s="2" t="inlineStr"/>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Lit en tissu gris avec rangement hydraulique</t>
+          <t>Lit avec tiroirs de rangement</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -7616,16 +7608,16 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>499.99</v>
+        <v>599</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>499.99</v>
+        <v>599</v>
       </c>
       <c r="F198" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -7641,10 +7633,14 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="9" t="inlineStr"/>
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>IF-5295</t>
+        </is>
+      </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>Lit King en Velours Bleu</t>
+          <t>Lit plateforme — Gris (2)</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
@@ -7653,20 +7649,20 @@
         </is>
       </c>
       <c r="D199" s="10" t="n">
-        <v>480</v>
+        <v>579.98</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>480</v>
+        <v>580</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>0</v>
+        <v>-3.44827586206583e-05</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I199" s="6" t="n"/>
@@ -7678,14 +7674,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>IF-5710</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="inlineStr"/>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Lit Jeanne-Mance — tissu gris</t>
+          <t>Velours Dusty Pink</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -7694,16 +7686,16 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>450</v>
+        <v>575.99</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>450</v>
+        <v>575.99</v>
       </c>
       <c r="F200" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -7722,7 +7714,7 @@
       <c r="A201" s="9" t="inlineStr"/>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>Lit en Velours Gris</t>
+          <t>Velours Bleu Royal</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
@@ -7731,16 +7723,16 @@
         </is>
       </c>
       <c r="D201" s="10" t="n">
-        <v>340</v>
+        <v>560</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>340</v>
+        <v>560</v>
       </c>
       <c r="F201" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
@@ -7759,7 +7751,7 @@
       <c r="A202" s="2" t="inlineStr"/>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Lit Queen en Velours Gris</t>
+          <t>Lucia — Blanc — Lit</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -7768,20 +7760,16 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="F202" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="E202" s="3" t="n"/>
+      <c r="F202" s="4" t="n"/>
       <c r="G202" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I202" s="6" t="n"/>
@@ -7796,7 +7784,7 @@
       <c r="A203" s="9" t="inlineStr"/>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>Matelas Ortho Care – Confort Semi-Ferme</t>
+          <t>Luxora LED Storage Bed</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
@@ -7805,16 +7793,16 @@
         </is>
       </c>
       <c r="D203" s="10" t="n">
-        <v>320</v>
+        <v>559.98</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>320</v>
+        <v>559.98</v>
       </c>
       <c r="F203" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
@@ -7832,12 +7820,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>IF-176</t>
+          <t>IF-5408</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Lit Jarry — noir</t>
+          <t>Lit avec rangement</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -7846,16 +7834,16 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>299.98</v>
+        <v>539.98</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>220</v>
+        <v>520</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>0.3635454545454546</v>
+        <v>0.03842307692307696</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -7873,12 +7861,12 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>IF-5430</t>
+          <t>IF-5407</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>Lit Verdun — tissu gris</t>
+          <t>Lit Fabre — velours beige</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
@@ -7887,16 +7875,16 @@
         </is>
       </c>
       <c r="D205" s="10" t="n">
-        <v>299.98</v>
+        <v>539.98</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>250</v>
+        <v>520</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>0.1999200000000001</v>
+        <v>0.03842307692307696</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
@@ -7912,14 +7900,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>IF-174</t>
-        </is>
-      </c>
+      <c r="A206" s="2" t="inlineStr"/>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Lit Everett — blanc</t>
+          <t>Lit en tissu gris avec rangement hydraulique</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -7928,20 +7912,20 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>279.98</v>
+        <v>499.99</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>250</v>
+        <v>499.99</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>0.1199200000000001</v>
+        <v>0</v>
       </c>
       <c r="G206" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I206" s="6" t="n"/>
@@ -7953,14 +7937,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="9" t="inlineStr">
-        <is>
-          <t>IF-175</t>
-        </is>
-      </c>
+      <c r="A207" s="9" t="inlineStr"/>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>Lit Dante — noir</t>
+          <t>Lit King en Velours Bleu</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
@@ -7969,20 +7949,20 @@
         </is>
       </c>
       <c r="D207" s="10" t="n">
-        <v>259.98</v>
+        <v>480</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>0.1817272727272728</v>
+        <v>0</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I207" s="6" t="n"/>
@@ -7994,10 +7974,14 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr"/>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>IF-5710</t>
+        </is>
+      </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Matelas OrthoPedic Deluxe – Confort moyen</t>
+          <t>Lit Jeanne-Mance — tissu gris</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -8006,16 +7990,16 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="F208" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -8034,25 +8018,25 @@
       <c r="A209" s="9" t="inlineStr"/>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>Lit Superposé — Noir</t>
+          <t>Lit en Velours Gris</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D209" s="10" t="n">
-        <v>780</v>
+        <v>340</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>180</v>
+        <v>340</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
@@ -8071,25 +8055,25 @@
       <c r="A210" s="2" t="inlineStr"/>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Lit Superposé — Blanc</t>
+          <t>Lit Queen en Velours Gris</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>750</v>
+        <v>340</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>180</v>
+        <v>340</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>3.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -8105,32 +8089,36 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="9" t="inlineStr"/>
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>IF-176</t>
+        </is>
+      </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>Lit Superposé — Gris</t>
+          <t>Lit Jarry — noir</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>Lits superposés</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D211" s="10" t="n">
-        <v>750</v>
+        <v>279.98</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>3.166666666666667</v>
+        <v>0.2726363636363637</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I211" s="6" t="n"/>
@@ -8142,32 +8130,36 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr"/>
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>IF-174</t>
+        </is>
+      </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SOFIA – Pillow Top | Série Cuivre</t>
+          <t>Lit Everett — blanc</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>920</v>
+        <v>279.98</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>920</v>
+        <v>250</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>0</v>
+        <v>0.1199200000000001</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I212" s="6" t="n"/>
@@ -8179,32 +8171,36 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="9" t="inlineStr"/>
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>IF-5430</t>
+        </is>
+      </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>SOFIA – Tight Top | Série Cuivre</t>
+          <t>Lit Verdun — tissu gris</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D213" s="10" t="n">
-        <v>760</v>
+        <v>279.98</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>760</v>
+        <v>250</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>0</v>
+        <v>0.1199200000000001</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I213" s="6" t="n"/>
@@ -8216,32 +8212,36 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr"/>
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>IF-175</t>
+        </is>
+      </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Matelas Bella Euro top – Copper Series</t>
+          <t>Lit Dante — noir</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>750</v>
+        <v>259.98</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>750</v>
+        <v>220</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>0</v>
+        <v>0.1817272727272728</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I214" s="6" t="n"/>
@@ -8256,25 +8256,25 @@
       <c r="A215" s="9" t="inlineStr"/>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>Matelas Jeanne-Mance — tissu</t>
+          <t>Lit Superposé — Noir</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D215" s="10" t="n">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>740</v>
+        <v>180</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="G215" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
@@ -8293,25 +8293,25 @@
       <c r="A216" s="2" t="inlineStr"/>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Matelas Christophe — tissu noir</t>
+          <t>Lit Superposé — Blanc</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>690</v>
+        <v>180</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -8330,25 +8330,25 @@
       <c r="A217" s="9" t="inlineStr"/>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>Matelas Hailey Euro Deluxe 4</t>
+          <t>Lit Superposé — Gris</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>Matelas</t>
+          <t>Lits superposés</t>
         </is>
       </c>
       <c r="D217" s="10" t="n">
-        <v>560</v>
+        <v>750</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Matelas Alisha Hybrid – Gel Foam</t>
+          <t>SOFIA – Tight Top | Série Cuivre</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="F218" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G218" s="5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       <c r="A219" s="9" t="inlineStr"/>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>Matelas Fabre — tissu</t>
+          <t>Matelas Bella Euro top – Copper Series</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
@@ -8413,16 +8413,16 @@
         </is>
       </c>
       <c r="D219" s="10" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="F219" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Matelas Breeze Cool Max – Fermeté moyenne</t>
+          <t>Healthy Beds</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -8450,16 +8450,16 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="F220" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -8475,14 +8475,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="9" t="inlineStr">
-        <is>
-          <t>C-1253</t>
-        </is>
-      </c>
+      <c r="A221" s="9" t="inlineStr"/>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>Chaise en velours crème — Beige</t>
+          <t>Matelas Bella Tight Top</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
@@ -8491,20 +8487,20 @@
         </is>
       </c>
       <c r="D221" s="10" t="n">
-        <v>340</v>
+        <v>690</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>340</v>
+        <v>690</v>
       </c>
       <c r="F221" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I221" s="6" t="n"/>
@@ -8519,7 +8515,7 @@
       <c r="A222" s="2" t="inlineStr"/>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Matelas DREAM-O-PEDIC &amp; Tissu bambou</t>
+          <t>Matelas Spine Comfort</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -8528,16 +8524,16 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>250</v>
+        <v>640</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>250</v>
+        <v>640</v>
       </c>
       <c r="F222" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G222" s="5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -8556,7 +8552,7 @@
       <c r="A223" s="9" t="inlineStr"/>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>Matelas Rest-O-Pedic — | SEMI-FERME</t>
+          <t>Matelas Hailey Euro Deluxe 4</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
@@ -8565,16 +8561,16 @@
         </is>
       </c>
       <c r="D223" s="10" t="n">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="F223" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
@@ -8593,25 +8589,25 @@
       <c r="A224" s="2" t="inlineStr"/>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Meuble Telé - 60" L</t>
+          <t>Matelas Alisha Hybrid – Gel Foam</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>398.98</v>
+        <v>500</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>398.98</v>
+        <v>500</v>
       </c>
       <c r="F224" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -8630,25 +8626,25 @@
       <c r="A225" s="9" t="inlineStr"/>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>Meuble Télé - 72" L — Brun (2)</t>
+          <t>Matelas High Density Tight Top 8’’</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D225" s="10" t="n">
-        <v>395</v>
+        <v>440</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>395</v>
+        <v>440</v>
       </c>
       <c r="F225" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
@@ -8667,19 +8663,19 @@
       <c r="A226" s="2" t="inlineStr"/>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Meuble Télé - 63" L</t>
+          <t>Matelas Breeze Cool Max – Fermeté moyenne</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F226" s="4" t="n">
         <v>0</v>
@@ -8704,25 +8700,25 @@
       <c r="A227" s="9" t="inlineStr"/>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>Meuble Télé - 72" L — Brun</t>
+          <t>Matelas Ortho Care – Confort Semi-Ferme</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D227" s="10" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="F227" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
@@ -8741,25 +8737,25 @@
       <c r="A228" s="2" t="inlineStr"/>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Meuble Télé - 60" L</t>
+          <t>Matelas DREAM-O-PEDIC &amp; Tissu bambou</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="F228" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G228" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -8778,25 +8774,25 @@
       <c r="A229" s="9" t="inlineStr"/>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>Meuble Télé- 72" L</t>
+          <t>Matelas Rest-O-Pedic — | SEMI-FERME</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Meubles TV</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D229" s="10" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="F229" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
@@ -8815,25 +8811,29 @@
       <c r="A230" s="2" t="inlineStr"/>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Kova — Poufs et ottomane</t>
+          <t>Matelas OrthoPedic Deluxe – Confort moyen</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Poufs et ottomanes</t>
+          <t>Matelas</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="E230" s="3" t="n"/>
-      <c r="F230" s="4" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F230" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G230" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I230" s="6" t="n"/>
@@ -8845,32 +8845,32 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="inlineStr">
-        <is>
-          <t>IF-8007</t>
-        </is>
-      </c>
+      <c r="A231" s="9" t="inlineStr"/>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>Canapé Christophe — velours noir — Poufs et ottomane</t>
+          <t>Meuble Telé - 60" L</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>Poufs et ottomanes</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D231" s="10" t="n">
-        <v>280</v>
-      </c>
-      <c r="E231" s="10" t="n"/>
-      <c r="F231" s="11" t="n"/>
+        <v>398.98</v>
+      </c>
+      <c r="E231" s="10" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="F231" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G231" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I231" s="6" t="n"/>
@@ -8882,36 +8882,32 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>IF-8500</t>
-        </is>
-      </c>
+      <c r="A232" s="2" t="inlineStr"/>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Sectionnel inclinable</t>
+          <t>Meuble Télé - 72" L — Brun (2)</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>3999.98</v>
+        <v>395</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>4000</v>
+        <v>395</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>-4.999999999995453e-06</v>
+        <v>0</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I232" s="6" t="n"/>
@@ -8923,36 +8919,32 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="9" t="inlineStr">
-        <is>
-          <t>IF-9090</t>
-        </is>
-      </c>
+      <c r="A233" s="9" t="inlineStr"/>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>chaise longue gauche (LHF) — Gris</t>
+          <t>Meuble Télé - 63" L</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D233" s="10" t="n">
-        <v>3299.98</v>
+        <v>380</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>3000</v>
+        <v>380</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>0.09999333333333334</v>
+        <v>0</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I233" s="6" t="n"/>
@@ -8964,36 +8956,32 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>IF-9095</t>
-        </is>
-      </c>
+      <c r="A234" s="2" t="inlineStr"/>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>chaise longue gauche (LHF) — Noir</t>
+          <t>Meuble Télé - 72" L — Brun</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>2999.98</v>
+        <v>350</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>3000</v>
+        <v>350</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>-6.666666666660604e-06</v>
+        <v>0</v>
       </c>
       <c r="G234" s="5" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I234" s="6" t="n"/>
@@ -9008,25 +8996,25 @@
       <c r="A235" s="9" t="inlineStr"/>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Meuble Télé - 60" L</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D235" s="10" t="n">
-        <v>2500</v>
+        <v>310</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>2500</v>
+        <v>310</v>
       </c>
       <c r="F235" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G235" s="12" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
@@ -9045,25 +9033,25 @@
       <c r="A236" s="2" t="inlineStr"/>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Vault</t>
+          <t>Meuble Télé- 72" L</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Meubles TV</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>2500</v>
+        <v>290</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>2500</v>
+        <v>290</v>
       </c>
       <c r="F236" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -9082,29 +9070,25 @@
       <c r="A237" s="9" t="inlineStr"/>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Kova — Poufs et ottomane</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Poufs et ottomanes</t>
         </is>
       </c>
       <c r="D237" s="10" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E237" s="10" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F237" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="E237" s="10" t="n"/>
+      <c r="F237" s="11" t="n"/>
       <c r="G237" s="12" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I237" s="6" t="n"/>
@@ -9116,32 +9100,32 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="inlineStr"/>
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>IF-8007</t>
+        </is>
+      </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Canapé Christophe — velours noir — Poufs et ottomane</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Sectionnels</t>
+          <t>Poufs et ottomanes</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F238" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="E238" s="3" t="n"/>
+      <c r="F238" s="4" t="n"/>
       <c r="G238" s="5" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I238" s="6" t="n"/>
@@ -9153,10 +9137,14 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="inlineStr"/>
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>IF-8500</t>
+        </is>
+      </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>Solace</t>
+          <t>Sectionnel inclinable</t>
         </is>
       </c>
       <c r="C239" s="9" t="inlineStr">
@@ -9165,20 +9153,20 @@
         </is>
       </c>
       <c r="D239" s="10" t="n">
-        <v>2400</v>
+        <v>3999.98</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>2400</v>
+        <v>4000</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>0</v>
+        <v>-4.999999999995453e-06</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I239" s="6" t="n"/>
@@ -9192,12 +9180,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>IF-9035</t>
+          <t>IF-9090</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Sectionnel Fabre — tissu gris</t>
+          <t>chaise longue gauche — Gris</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -9206,16 +9194,16 @@
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>2399.98</v>
+        <v>3299.98</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>-8.333333333325754e-06</v>
+        <v>0.09999333333333334</v>
       </c>
       <c r="G240" s="5" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -9231,10 +9219,14 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="9" t="inlineStr"/>
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>IF-9095</t>
+        </is>
+      </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>Stash</t>
+          <t>chaise longue gauche — Noir</t>
         </is>
       </c>
       <c r="C241" s="9" t="inlineStr">
@@ -9243,20 +9235,20 @@
         </is>
       </c>
       <c r="D241" s="10" t="n">
-        <v>2300</v>
+        <v>2999.98</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>0</v>
+        <v>-6.666666666660604e-06</v>
       </c>
       <c r="G241" s="12" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I241" s="6" t="n"/>
@@ -9268,14 +9260,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>IF-9050 / IF-9051</t>
-        </is>
-      </c>
+      <c r="A242" s="2" t="inlineStr"/>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Sectionnel canapé-lit</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -9284,16 +9272,16 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="F242" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G242" s="5" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -9309,14 +9297,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>IF-9085 / IF-9086</t>
-        </is>
-      </c>
+      <c r="A243" s="9" t="inlineStr"/>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel Drolet — bouclé gris</t>
+          <t>Vault</t>
         </is>
       </c>
       <c r="C243" s="9" t="inlineStr">
@@ -9325,16 +9309,16 @@
         </is>
       </c>
       <c r="D243" s="10" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="F243" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
@@ -9353,7 +9337,7 @@
       <c r="A244" s="2" t="inlineStr"/>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -9362,16 +9346,16 @@
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>1998.99</v>
+        <v>2400</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>1998.99</v>
+        <v>2400</v>
       </c>
       <c r="F244" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -9387,14 +9371,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="9" t="inlineStr">
-        <is>
-          <t>IF-9075 / IF-9076</t>
-        </is>
-      </c>
+      <c r="A245" s="9" t="inlineStr"/>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>Sectionnel Iberville — tissu brun</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C245" s="9" t="inlineStr">
@@ -9403,16 +9383,16 @@
         </is>
       </c>
       <c r="D245" s="10" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="F245" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
@@ -9431,7 +9411,7 @@
       <c r="A246" s="2" t="inlineStr"/>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Kova — Sectionnel</t>
+          <t>Solace</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -9440,16 +9420,20 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E246" s="3" t="n"/>
-      <c r="F246" s="4" t="n"/>
+        <v>2400</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F246" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G246" s="5" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I246" s="6" t="n"/>
@@ -9461,10 +9445,14 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="9" t="inlineStr"/>
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>IF-9035</t>
+        </is>
+      </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>Grey Refuge</t>
+          <t>Sectionnel Fabre — tissu gris</t>
         </is>
       </c>
       <c r="C247" s="9" t="inlineStr">
@@ -9473,20 +9461,20 @@
         </is>
       </c>
       <c r="D247" s="10" t="n">
-        <v>1400</v>
+        <v>2399.98</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>0</v>
+        <v>-8.333333333325754e-06</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I247" s="6" t="n"/>
@@ -9501,7 +9489,7 @@
       <c r="A248" s="2" t="inlineStr"/>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Black Refuge</t>
+          <t>Stash</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -9510,16 +9498,16 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="F248" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G248" s="5" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -9535,10 +9523,14 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="9" t="inlineStr"/>
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>IF-9050 / IF-9051</t>
+        </is>
+      </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>Nido</t>
+          <t>Sectionnel canapé-lit</t>
         </is>
       </c>
       <c r="C249" s="9" t="inlineStr">
@@ -9547,16 +9539,16 @@
         </is>
       </c>
       <c r="D249" s="10" t="n">
-        <v>1398.99</v>
+        <v>2200</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>1398.99</v>
+        <v>2200</v>
       </c>
       <c r="F249" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H249" s="9" t="inlineStr">
         <is>
@@ -9572,10 +9564,14 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr"/>
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>IF-9085 / IF-9086</t>
+        </is>
+      </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Luno</t>
+          <t>Sectionnel Drolet — bouclé gris</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -9584,16 +9580,16 @@
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="F250" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -9612,7 +9608,7 @@
       <c r="A251" s="9" t="inlineStr"/>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>Refuge</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C251" s="9" t="inlineStr">
@@ -9621,16 +9617,16 @@
         </is>
       </c>
       <c r="D251" s="10" t="n">
-        <v>1199.98</v>
+        <v>1998.99</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>1199.98</v>
+        <v>1998.99</v>
       </c>
       <c r="F251" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="H251" s="9" t="inlineStr">
         <is>
@@ -9646,10 +9642,14 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr"/>
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>IF-9075 / IF-9076</t>
+        </is>
+      </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Sofa Lit - 8A14L83</t>
+          <t>Sectionnel Iberville — tissu brun</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -9658,16 +9658,16 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="F252" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
       <c r="A253" s="9" t="inlineStr"/>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>Sofa Lit</t>
+          <t>Kova — Sectionnel</t>
         </is>
       </c>
       <c r="C253" s="9" t="inlineStr">
@@ -9695,20 +9695,16 @@
         </is>
       </c>
       <c r="D253" s="10" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E253" s="10" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F253" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="E253" s="10" t="n"/>
+      <c r="F253" s="11" t="n"/>
       <c r="G253" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H253" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I253" s="6" t="n"/>
@@ -9723,7 +9719,7 @@
       <c r="A254" s="2" t="inlineStr"/>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Sofa Lit — Brun</t>
+          <t>Grey Refuge</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -9732,16 +9728,16 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="F254" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9756,7 @@
       <c r="A255" s="9" t="inlineStr"/>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>Sofa Lit (2)</t>
+          <t>Black Refuge</t>
         </is>
       </c>
       <c r="C255" s="9" t="inlineStr">
@@ -9769,16 +9765,16 @@
         </is>
       </c>
       <c r="D255" s="10" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="E255" s="10" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="F255" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H255" s="9" t="inlineStr">
         <is>
@@ -9797,7 +9793,7 @@
       <c r="A256" s="2" t="inlineStr"/>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Sofa Lit — Gris</t>
+          <t>Nido</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -9806,16 +9802,16 @@
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>1050</v>
+        <v>1398.99</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>1050</v>
+        <v>1398.99</v>
       </c>
       <c r="F256" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -9834,7 +9830,7 @@
       <c r="A257" s="9" t="inlineStr"/>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>Sofa-Lit</t>
+          <t>Luno</t>
         </is>
       </c>
       <c r="C257" s="9" t="inlineStr">
@@ -9843,16 +9839,16 @@
         </is>
       </c>
       <c r="D257" s="10" t="n">
-        <v>999</v>
+        <v>1200</v>
       </c>
       <c r="E257" s="10" t="n">
-        <v>999</v>
+        <v>1200</v>
       </c>
       <c r="F257" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
@@ -9871,7 +9867,7 @@
       <c r="A258" s="2" t="inlineStr"/>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Gris</t>
+          <t>Refuge</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -9880,16 +9876,16 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>800</v>
+        <v>1199.98</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>800</v>
+        <v>1199.98</v>
       </c>
       <c r="F258" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -9908,7 +9904,7 @@
       <c r="A259" s="9" t="inlineStr"/>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Brun</t>
+          <t>Sofa Chaise Longue — Gris</t>
         </is>
       </c>
       <c r="C259" s="9" t="inlineStr">
@@ -9917,10 +9913,10 @@
         </is>
       </c>
       <c r="D259" s="10" t="n">
-        <v>798.99</v>
+        <v>800</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>798.99</v>
+        <v>800</v>
       </c>
       <c r="F259" s="11" t="n">
         <v>0</v>
@@ -9945,7 +9941,7 @@
       <c r="A260" s="2" t="inlineStr"/>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Sofa Chaise Longue — Brun (2)</t>
+          <t>Sofa Chaise Longue — Brun</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -9982,25 +9978,29 @@
       <c r="A261" s="9" t="inlineStr"/>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>Amelia-Black — Tables de chevet</t>
+          <t>Sofa Chaise Longue — Brun (2)</t>
         </is>
       </c>
       <c r="C261" s="9" t="inlineStr">
         <is>
-          <t>Tables de chevet</t>
+          <t>Sectionnels</t>
         </is>
       </c>
       <c r="D261" s="10" t="n">
-        <v>370</v>
-      </c>
-      <c r="E261" s="10" t="n"/>
-      <c r="F261" s="11" t="n"/>
+        <v>798.99</v>
+      </c>
+      <c r="E261" s="10" t="n">
+        <v>798.99</v>
+      </c>
+      <c r="F261" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G261" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I261" s="6" t="n"/>
@@ -10015,7 +10015,7 @@
       <c r="A262" s="2" t="inlineStr"/>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Chambre Moderne Blanche — Tables de chevet</t>
+          <t>Amelia-Black — Tables de chevet</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -10048,7 +10048,7 @@
       <c r="A263" s="9" t="inlineStr"/>
       <c r="B263" s="9" t="inlineStr">
         <is>
-          <t>Ava Jordyn – Gris — Tables de chevet</t>
+          <t>Chambre Moderne Blanche — Tables de chevet</t>
         </is>
       </c>
       <c r="C263" s="9" t="inlineStr">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="D263" s="10" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="E263" s="10" t="n"/>
       <c r="F263" s="11" t="n"/>
@@ -10081,7 +10081,7 @@
       <c r="A264" s="2" t="inlineStr"/>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Jordyn – Blanc — Tables de chevet</t>
+          <t>Ava Jordyn – Gris — Tables de chevet</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       <c r="A265" s="9" t="inlineStr"/>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>Harper "Seville" — Tables de chevet</t>
+          <t>Jordyn – Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C265" s="9" t="inlineStr">
@@ -10123,12 +10123,12 @@
         </is>
       </c>
       <c r="D265" s="10" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="E265" s="10" t="n"/>
       <c r="F265" s="11" t="n"/>
       <c r="G265" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
       <c r="A266" s="2" t="inlineStr"/>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Luccia – Table de chevet blanche</t>
+          <t>Harper "Seville" — Tables de chevet</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -10156,20 +10156,16 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="F266" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="E266" s="3" t="n"/>
+      <c r="F266" s="4" t="n"/>
       <c r="G266" s="5" t="n">
         <v>8</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I266" s="6" t="n"/>
@@ -10184,7 +10180,7 @@
       <c r="A267" s="9" t="inlineStr"/>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>Lucia — Blanc — Tables de chevet</t>
+          <t>Luccia – Table de chevet blanche</t>
         </is>
       </c>
       <c r="C267" s="9" t="inlineStr">
@@ -10195,14 +10191,18 @@
       <c r="D267" s="10" t="n">
         <v>270</v>
       </c>
-      <c r="E267" s="10" t="n"/>
-      <c r="F267" s="11" t="n"/>
+      <c r="E267" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="F267" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="G267" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>Nouvelle fiche — pièce d’un ensemble</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I267" s="6" t="n"/>
@@ -10217,7 +10217,7 @@
       <c r="A268" s="2" t="inlineStr"/>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Pompéi – Gris métallisé — Tables de chevet</t>
+          <t>Lucia — Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E268" s="3" t="n"/>
       <c r="F268" s="4" t="n"/>
       <c r="G268" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
       <c r="A269" s="9" t="inlineStr"/>
       <c r="B269" s="9" t="inlineStr">
         <is>
-          <t>Luna Riley – Finition argentée — Tables de chevet</t>
+          <t>Pompéi – Gris métallisé — Tables de chevet</t>
         </is>
       </c>
       <c r="C269" s="9" t="inlineStr">
@@ -10259,12 +10259,12 @@
         </is>
       </c>
       <c r="D269" s="10" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E269" s="10" t="n"/>
       <c r="F269" s="11" t="n"/>
       <c r="G269" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
       <c r="A270" s="2" t="inlineStr"/>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Madisson 100 — Tables de chevet</t>
+          <t>Luna Riley – Finition argentée — Tables de chevet</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -10316,7 +10316,7 @@
       <c r="A271" s="9" t="inlineStr"/>
       <c r="B271" s="9" t="inlineStr">
         <is>
-          <t>Olivia “Austin — Tables de chevet</t>
+          <t>Madisson 100 — Tables de chevet</t>
         </is>
       </c>
       <c r="C271" s="9" t="inlineStr">
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="D271" s="10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E271" s="10" t="n"/>
       <c r="F271" s="11" t="n"/>
@@ -10349,7 +10349,7 @@
       <c r="A272" s="2" t="inlineStr"/>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Dylan — Tables de chevet</t>
+          <t>Olivia “Austin — Tables de chevet</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       <c r="A273" s="9" t="inlineStr"/>
       <c r="B273" s="9" t="inlineStr">
         <is>
-          <t>Teddy Bear Blanc — Tables de chevet</t>
+          <t>Dylan — Tables de chevet</t>
         </is>
       </c>
       <c r="C273" s="9" t="inlineStr">
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="D273" s="10" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E273" s="10" t="n"/>
       <c r="F273" s="11" t="n"/>
@@ -10415,21 +10415,21 @@
       <c r="A274" s="2" t="inlineStr"/>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Monaco Dining Set — Tables de salle à manger</t>
+          <t>Teddy Bear Blanc — Tables de chevet</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Tables de salle à manger</t>
+          <t>Tables de chevet</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
-        <v>1580</v>
+        <v>200</v>
       </c>
       <c r="E274" s="3" t="n"/>
       <c r="F274" s="4" t="n"/>
       <c r="G274" s="5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -10445,14 +10445,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="9" t="inlineStr">
-        <is>
-          <t>T-1540</t>
-        </is>
-      </c>
+      <c r="A275" s="9" t="inlineStr"/>
       <c r="B275" s="9" t="inlineStr">
         <is>
-          <t>Meuble Chabanel — métal gris — Tables de salle à manger</t>
+          <t>Monaco Dining Set — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C275" s="9" t="inlineStr">
@@ -10461,12 +10457,12 @@
         </is>
       </c>
       <c r="D275" s="10" t="n">
-        <v>1539.98</v>
+        <v>1580</v>
       </c>
       <c r="E275" s="10" t="n"/>
       <c r="F275" s="11" t="n"/>
       <c r="G275" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H275" s="9" t="inlineStr">
         <is>
@@ -10484,12 +10480,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>T-1275</t>
+          <t>T-1540</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Gaspé — velours beige — Tables de salle à manger</t>
+          <t>Chabanel — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -10498,12 +10494,12 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>1199.98</v>
+        <v>1539.98</v>
       </c>
       <c r="E276" s="3" t="n"/>
       <c r="F276" s="4" t="n"/>
       <c r="G276" s="5" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -10521,12 +10517,12 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>T-1274</t>
+          <t>T-1275</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
         <is>
-          <t>Casgrain — velours gris — Tables de salle à manger</t>
+          <t>Gaspé — velours beige — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C277" s="9" t="inlineStr">
@@ -10535,12 +10531,12 @@
         </is>
       </c>
       <c r="D277" s="10" t="n">
-        <v>1199.98</v>
+        <v>1259.98</v>
       </c>
       <c r="E277" s="10" t="n"/>
       <c r="F277" s="11" t="n"/>
       <c r="G277" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H277" s="9" t="inlineStr">
         <is>
@@ -10563,7 +10559,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Waverly — velours gris — Tables de salle à manger</t>
+          <t>Casgrain — velours gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -10572,12 +10568,12 @@
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>1199.98</v>
+        <v>1259.98</v>
       </c>
       <c r="E278" s="3" t="n"/>
       <c r="F278" s="4" t="n"/>
       <c r="G278" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -10595,12 +10591,12 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>T-1545</t>
+          <t>T-1274</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
         <is>
-          <t>Meuble Iberville — métal noir — Tables de salle à manger</t>
+          <t>Waverly — velours gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C279" s="9" t="inlineStr">
@@ -10609,12 +10605,12 @@
         </is>
       </c>
       <c r="D279" s="10" t="n">
-        <v>1099.98</v>
+        <v>1259.98</v>
       </c>
       <c r="E279" s="10" t="n"/>
       <c r="F279" s="11" t="n"/>
       <c r="G279" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H279" s="9" t="inlineStr">
         <is>
@@ -10632,12 +10628,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>T-1415</t>
+          <t>T-1545</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Meuble Boyer — métal gris — Tables de salle à manger</t>
+          <t>Iberville — métal noir — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -10646,12 +10642,12 @@
         </is>
       </c>
       <c r="D280" s="3" t="n">
-        <v>899.98</v>
+        <v>1099.98</v>
       </c>
       <c r="E280" s="3" t="n"/>
       <c r="F280" s="4" t="n"/>
       <c r="G280" s="5" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -10669,12 +10665,12 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>T-1811 / C-1835</t>
+          <t>T-1415</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
         <is>
-          <t>Drolet — Tables de salle à manger</t>
+          <t>Boyer — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C281" s="9" t="inlineStr">
@@ -10683,12 +10679,12 @@
         </is>
       </c>
       <c r="D281" s="10" t="n">
-        <v>600</v>
+        <v>899.98</v>
       </c>
       <c r="E281" s="10" t="n"/>
       <c r="F281" s="11" t="n"/>
       <c r="G281" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
@@ -10706,12 +10702,12 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>T-1811 / C-1826</t>
+          <t>T-1811 / C-1835</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Christophe — Tables de salle à manger</t>
+          <t>Drolet — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -10743,12 +10739,12 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>T-1402</t>
+          <t>T-1811 / C-1826</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
         <is>
-          <t>Chaise Christophe — métal gris — Tables de salle à manger</t>
+          <t>Christophe — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C283" s="9" t="inlineStr">
@@ -10757,7 +10753,7 @@
         </is>
       </c>
       <c r="D283" s="10" t="n">
-        <v>599.98</v>
+        <v>600</v>
       </c>
       <c r="E283" s="10" t="n"/>
       <c r="F283" s="11" t="n"/>
@@ -10780,12 +10776,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>T-1510</t>
+          <t>T-1402</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Meuble Beaubien — tissu gris — Tables de salle à manger</t>
+          <t>Chaise Christophe — métal gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -10794,12 +10790,12 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>439.98</v>
+        <v>599.98</v>
       </c>
       <c r="E284" s="3" t="n"/>
       <c r="F284" s="4" t="n"/>
       <c r="G284" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -10822,7 +10818,7 @@
       </c>
       <c r="B285" s="9" t="inlineStr">
         <is>
-          <t>Meuble Papineau — tissu gris — Tables de salle à manger</t>
+          <t>Beaubien — tissu gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C285" s="9" t="inlineStr">
@@ -10859,7 +10855,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Meuble Fabre — velours beige — Tables de salle à manger</t>
+          <t>Papineau — tissu gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -10891,12 +10887,12 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>T-1442 / C-1878</t>
+          <t>T-1510</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
         <is>
-          <t>Marquette — verre blanc — Tables de salle à manger</t>
+          <t>Fabre — velours beige — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C287" s="9" t="inlineStr">
@@ -10905,7 +10901,7 @@
         </is>
       </c>
       <c r="D287" s="10" t="n">
-        <v>420</v>
+        <v>439.98</v>
       </c>
       <c r="E287" s="10" t="n"/>
       <c r="F287" s="11" t="n"/>
@@ -10928,12 +10924,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>T-1449 &amp; C-1712</t>
+          <t>T-1442 / C-1878</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Saint-Urbain — bois gris — Tables de salle à manger</t>
+          <t>Marquette — verre blanc — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -10942,12 +10938,12 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="4" t="n"/>
       <c r="G288" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -10965,12 +10961,12 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>T-1079 / C-1084</t>
+          <t>T-1449 &amp; C-1712</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
         <is>
-          <t>Gaspé — tissu gris — Tables de salle à manger</t>
+          <t>Saint-Urbain — bois gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C289" s="9" t="inlineStr">
@@ -11002,34 +10998,30 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>IF-3530</t>
+          <t>T-1079 / C-1084</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Table basse moderne — Blanc</t>
+          <t>Gaspé — tissu gris — Tables de salle à manger</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Tables de salon</t>
+          <t>Tables de salle à manger</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>239.98</v>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="F290" s="4" t="n">
-        <v>-8.333333333337597e-05</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="E290" s="3" t="n"/>
+      <c r="F290" s="4" t="n"/>
       <c r="G290" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Nouvelle fiche — pièce d’un ensemble</t>
         </is>
       </c>
       <c r="I290" s="6" t="n"/>
@@ -11041,10 +11033,14 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="9" t="inlineStr"/>
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>IF-3530</t>
+        </is>
+      </c>
       <c r="B291" s="9" t="inlineStr">
         <is>
-          <t>Ensemble de 2 tables modernes</t>
+          <t>Table basse moderne — Blanc</t>
         </is>
       </c>
       <c r="C291" s="9" t="inlineStr">
@@ -11053,20 +11049,20 @@
         </is>
       </c>
       <c r="D291" s="10" t="n">
-        <v>200</v>
+        <v>239.98</v>
       </c>
       <c r="E291" s="10" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>0</v>
+        <v>-8.333333333337597e-05</v>
       </c>
       <c r="G291" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H291" s="9" t="inlineStr">
         <is>
-          <t>Prix boutique actuel</t>
+          <t>Liste du fournisseur</t>
         </is>
       </c>
       <c r="I291" s="6" t="n"/>
@@ -11078,14 +11074,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>IF-2631</t>
-        </is>
-      </c>
+      <c r="A292" s="2" t="inlineStr"/>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Table basse</t>
+          <t>Ensemble de 2 tables modernes</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -11094,20 +11086,20 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>199.98</v>
+        <v>200</v>
       </c>
       <c r="E292" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F292" s="4" t="n">
-        <v>0.3331999999999999</v>
+        <v>0</v>
       </c>
       <c r="G292" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>Liste du fournisseur</t>
+          <t>Prix boutique actuel</t>
         </is>
       </c>
       <c r="I292" s="6" t="n"/>
@@ -11121,12 +11113,12 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>IF-3225</t>
+          <t>IF-2631</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
         <is>
-          <t>Table basse moderne — Beige</t>
+          <t>Table basse</t>
         </is>
       </c>
       <c r="C293" s="9" t="inlineStr">
@@ -11154,6 +11146,47 @@
       <c r="I293" s="6" t="n"/>
       <c r="J293" s="13" t="inlineStr"/>
       <c r="K293" s="14" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>IF-3225</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Table basse moderne — Beige</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Tables de salon</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F294" s="4" t="n">
+        <v>0.3331999999999999</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>Liste du fournisseur</t>
+        </is>
+      </c>
+      <c r="I294" s="6" t="n"/>
+      <c r="J294" s="7" t="inlineStr"/>
+      <c r="K294" s="8" t="inlineStr">
         <is>
           <t>Voir</t>
         </is>
@@ -11453,6 +11486,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K291" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K294" r:id="rId293"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11483,7 +11517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>292 produits. Les lignes surlignées demandent une vérification.</t>
+          <t>293 produits. Les lignes surlignées demandent une vérification.</t>
         </is>
       </c>
     </row>
